--- a/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -794,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7193800</v>
+        <v>7312300</v>
       </c>
       <c r="E8" s="3">
-        <v>5736100</v>
+        <v>5830600</v>
       </c>
       <c r="F8" s="3">
-        <v>6274100</v>
+        <v>6377500</v>
       </c>
       <c r="G8" s="3">
-        <v>7044000</v>
+        <v>7160100</v>
       </c>
       <c r="H8" s="3">
-        <v>7602300</v>
+        <v>7727600</v>
       </c>
       <c r="I8" s="3">
-        <v>8342400</v>
+        <v>8479900</v>
       </c>
       <c r="J8" s="3">
-        <v>7762300</v>
+        <v>7890200</v>
       </c>
       <c r="K8" s="3">
         <v>6820900</v>
@@ -886,25 +886,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3153800</v>
+        <v>3205700</v>
       </c>
       <c r="E9" s="3">
-        <v>3301400</v>
+        <v>3355800</v>
       </c>
       <c r="F9" s="3">
-        <v>3270100</v>
+        <v>3324000</v>
       </c>
       <c r="G9" s="3">
-        <v>3569600</v>
+        <v>3628400</v>
       </c>
       <c r="H9" s="3">
-        <v>3134100</v>
+        <v>3185800</v>
       </c>
       <c r="I9" s="3">
-        <v>3612500</v>
+        <v>3672000</v>
       </c>
       <c r="J9" s="3">
-        <v>3267900</v>
+        <v>3321800</v>
       </c>
       <c r="K9" s="3">
         <v>2912600</v>
@@ -978,25 +978,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4040000</v>
+        <v>4106600</v>
       </c>
       <c r="E10" s="3">
-        <v>2434800</v>
+        <v>2474900</v>
       </c>
       <c r="F10" s="3">
-        <v>3004000</v>
+        <v>3053500</v>
       </c>
       <c r="G10" s="3">
-        <v>3474400</v>
+        <v>3531600</v>
       </c>
       <c r="H10" s="3">
-        <v>4468200</v>
+        <v>4541800</v>
       </c>
       <c r="I10" s="3">
-        <v>4729900</v>
+        <v>4807900</v>
       </c>
       <c r="J10" s="3">
-        <v>4494400</v>
+        <v>4568400</v>
       </c>
       <c r="K10" s="3">
         <v>3908400</v>
@@ -1380,25 +1380,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1117400</v>
+        <v>1135800</v>
       </c>
       <c r="E15" s="3">
-        <v>1015600</v>
+        <v>1032400</v>
       </c>
       <c r="F15" s="3">
-        <v>1030900</v>
+        <v>1047900</v>
       </c>
       <c r="G15" s="3">
-        <v>2274800</v>
+        <v>2312300</v>
       </c>
       <c r="H15" s="3">
-        <v>1057100</v>
+        <v>1074500</v>
       </c>
       <c r="I15" s="3">
-        <v>990900</v>
+        <v>1007200</v>
       </c>
       <c r="J15" s="3">
-        <v>1022900</v>
+        <v>1039800</v>
       </c>
       <c r="K15" s="3">
         <v>1090600</v>
@@ -1503,25 +1503,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4633200</v>
+        <v>4709600</v>
       </c>
       <c r="E17" s="3">
-        <v>4520500</v>
+        <v>4595000</v>
       </c>
       <c r="F17" s="3">
-        <v>4492900</v>
+        <v>4567000</v>
       </c>
       <c r="G17" s="3">
-        <v>6214500</v>
+        <v>6316900</v>
       </c>
       <c r="H17" s="3">
-        <v>4316300</v>
+        <v>4387400</v>
       </c>
       <c r="I17" s="3">
-        <v>4683400</v>
+        <v>4760600</v>
       </c>
       <c r="J17" s="3">
-        <v>4806300</v>
+        <v>4885500</v>
       </c>
       <c r="K17" s="3">
         <v>4250400</v>
@@ -1595,25 +1595,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2560500</v>
+        <v>2602700</v>
       </c>
       <c r="E18" s="3">
-        <v>1215600</v>
+        <v>1235600</v>
       </c>
       <c r="F18" s="3">
-        <v>1781200</v>
+        <v>1810500</v>
       </c>
       <c r="G18" s="3">
-        <v>829500</v>
+        <v>843200</v>
       </c>
       <c r="H18" s="3">
-        <v>3286100</v>
+        <v>3340200</v>
       </c>
       <c r="I18" s="3">
-        <v>3659000</v>
+        <v>3719300</v>
       </c>
       <c r="J18" s="3">
-        <v>2956000</v>
+        <v>3004700</v>
       </c>
       <c r="K18" s="3">
         <v>2570500</v>
@@ -1721,25 +1721,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-136700</v>
+        <v>-138900</v>
       </c>
       <c r="E20" s="3">
-        <v>202100</v>
+        <v>205400</v>
       </c>
       <c r="F20" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="G20" s="3">
-        <v>280600</v>
+        <v>285300</v>
       </c>
       <c r="H20" s="3">
-        <v>-439800</v>
+        <v>-447100</v>
       </c>
       <c r="I20" s="3">
-        <v>-247900</v>
+        <v>-252000</v>
       </c>
       <c r="J20" s="3">
-        <v>126500</v>
+        <v>128600</v>
       </c>
       <c r="K20" s="3">
         <v>104400</v>
@@ -1813,25 +1813,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3541300</v>
+        <v>3599600</v>
       </c>
       <c r="E21" s="3">
-        <v>2433300</v>
+        <v>2473400</v>
       </c>
       <c r="F21" s="3">
-        <v>2806300</v>
+        <v>2852500</v>
       </c>
       <c r="G21" s="3">
-        <v>3385000</v>
+        <v>3440700</v>
       </c>
       <c r="H21" s="3">
-        <v>3903300</v>
+        <v>3967600</v>
       </c>
       <c r="I21" s="3">
-        <v>4402000</v>
+        <v>4474600</v>
       </c>
       <c r="J21" s="3">
-        <v>4105400</v>
+        <v>4173100</v>
       </c>
       <c r="K21" s="3">
         <v>3765500</v>
@@ -1905,25 +1905,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>136000</v>
+        <v>138200</v>
       </c>
       <c r="E22" s="3">
-        <v>129400</v>
+        <v>131500</v>
       </c>
       <c r="F22" s="3">
-        <v>112000</v>
+        <v>113800</v>
       </c>
       <c r="G22" s="3">
-        <v>143200</v>
+        <v>145600</v>
       </c>
       <c r="H22" s="3">
-        <v>109100</v>
+        <v>110800</v>
       </c>
       <c r="I22" s="3">
-        <v>116300</v>
+        <v>118200</v>
       </c>
       <c r="J22" s="3">
-        <v>118500</v>
+        <v>120500</v>
       </c>
       <c r="K22" s="3">
         <v>150300</v>
@@ -1997,25 +1997,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2287900</v>
+        <v>2325600</v>
       </c>
       <c r="E23" s="3">
-        <v>1288300</v>
+        <v>1309500</v>
       </c>
       <c r="F23" s="3">
-        <v>1663400</v>
+        <v>1690800</v>
       </c>
       <c r="G23" s="3">
-        <v>966900</v>
+        <v>982900</v>
       </c>
       <c r="H23" s="3">
-        <v>2737200</v>
+        <v>2782300</v>
       </c>
       <c r="I23" s="3">
-        <v>3294800</v>
+        <v>3349100</v>
       </c>
       <c r="J23" s="3">
-        <v>2964000</v>
+        <v>3012900</v>
       </c>
       <c r="K23" s="3">
         <v>2524600</v>
@@ -2089,25 +2089,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>583800</v>
+        <v>593400</v>
       </c>
       <c r="E24" s="3">
-        <v>224600</v>
+        <v>228300</v>
       </c>
       <c r="F24" s="3">
-        <v>355500</v>
+        <v>361400</v>
       </c>
       <c r="G24" s="3">
-        <v>-138100</v>
+        <v>-140400</v>
       </c>
       <c r="H24" s="3">
-        <v>691400</v>
+        <v>702800</v>
       </c>
       <c r="I24" s="3">
-        <v>748800</v>
+        <v>761200</v>
       </c>
       <c r="J24" s="3">
-        <v>709600</v>
+        <v>721300</v>
       </c>
       <c r="K24" s="3">
         <v>648600</v>
@@ -2273,25 +2273,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1704100</v>
+        <v>1732200</v>
       </c>
       <c r="E26" s="3">
-        <v>1063600</v>
+        <v>1081100</v>
       </c>
       <c r="F26" s="3">
-        <v>1307900</v>
+        <v>1329400</v>
       </c>
       <c r="G26" s="3">
-        <v>1105100</v>
+        <v>1123300</v>
       </c>
       <c r="H26" s="3">
-        <v>2045800</v>
+        <v>2079500</v>
       </c>
       <c r="I26" s="3">
-        <v>2546000</v>
+        <v>2587900</v>
       </c>
       <c r="J26" s="3">
-        <v>2254500</v>
+        <v>2291600</v>
       </c>
       <c r="K26" s="3">
         <v>1876100</v>
@@ -2365,25 +2365,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1704100</v>
+        <v>1732200</v>
       </c>
       <c r="E27" s="3">
-        <v>1063600</v>
+        <v>1081100</v>
       </c>
       <c r="F27" s="3">
-        <v>1307900</v>
+        <v>1329400</v>
       </c>
       <c r="G27" s="3">
-        <v>1105100</v>
+        <v>1123300</v>
       </c>
       <c r="H27" s="3">
-        <v>2045800</v>
+        <v>2079500</v>
       </c>
       <c r="I27" s="3">
-        <v>2546000</v>
+        <v>2587900</v>
       </c>
       <c r="J27" s="3">
-        <v>2254500</v>
+        <v>2291600</v>
       </c>
       <c r="K27" s="3">
         <v>1876100</v>
@@ -2825,25 +2825,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>136700</v>
+        <v>138900</v>
       </c>
       <c r="E32" s="3">
-        <v>-202100</v>
+        <v>-205400</v>
       </c>
       <c r="F32" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="G32" s="3">
-        <v>-280600</v>
+        <v>-285300</v>
       </c>
       <c r="H32" s="3">
-        <v>439800</v>
+        <v>447100</v>
       </c>
       <c r="I32" s="3">
-        <v>247900</v>
+        <v>252000</v>
       </c>
       <c r="J32" s="3">
-        <v>-126500</v>
+        <v>-128600</v>
       </c>
       <c r="K32" s="3">
         <v>-104400</v>
@@ -2917,25 +2917,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1704100</v>
+        <v>1732200</v>
       </c>
       <c r="E33" s="3">
-        <v>1063600</v>
+        <v>1081100</v>
       </c>
       <c r="F33" s="3">
-        <v>1307900</v>
+        <v>1329400</v>
       </c>
       <c r="G33" s="3">
-        <v>1105100</v>
+        <v>1123300</v>
       </c>
       <c r="H33" s="3">
-        <v>2045800</v>
+        <v>2079500</v>
       </c>
       <c r="I33" s="3">
-        <v>2546000</v>
+        <v>2587900</v>
       </c>
       <c r="J33" s="3">
-        <v>2254500</v>
+        <v>2291600</v>
       </c>
       <c r="K33" s="3">
         <v>1876100</v>
@@ -3101,25 +3101,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1704100</v>
+        <v>1732200</v>
       </c>
       <c r="E35" s="3">
-        <v>1063600</v>
+        <v>1081100</v>
       </c>
       <c r="F35" s="3">
-        <v>1307900</v>
+        <v>1329400</v>
       </c>
       <c r="G35" s="3">
-        <v>1105100</v>
+        <v>1123300</v>
       </c>
       <c r="H35" s="3">
-        <v>2045800</v>
+        <v>2079500</v>
       </c>
       <c r="I35" s="3">
-        <v>2546000</v>
+        <v>2587900</v>
       </c>
       <c r="J35" s="3">
-        <v>2254500</v>
+        <v>2291600</v>
       </c>
       <c r="K35" s="3">
         <v>1876100</v>
@@ -3358,25 +3358,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>90900</v>
+        <v>92400</v>
       </c>
       <c r="E41" s="3">
-        <v>88700</v>
+        <v>90200</v>
       </c>
       <c r="F41" s="3">
-        <v>66900</v>
+        <v>68000</v>
       </c>
       <c r="G41" s="3">
-        <v>668800</v>
+        <v>679900</v>
       </c>
       <c r="H41" s="3">
-        <v>410800</v>
+        <v>417500</v>
       </c>
       <c r="I41" s="3">
-        <v>169400</v>
+        <v>172200</v>
       </c>
       <c r="J41" s="3">
-        <v>90900</v>
+        <v>92400</v>
       </c>
       <c r="K41" s="3">
         <v>550800</v>
@@ -3450,25 +3450,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>410800</v>
+        <v>417500</v>
       </c>
       <c r="E42" s="3">
-        <v>381000</v>
+        <v>387200</v>
       </c>
       <c r="F42" s="3">
-        <v>351900</v>
+        <v>357700</v>
       </c>
       <c r="G42" s="3">
-        <v>357000</v>
+        <v>362800</v>
       </c>
       <c r="H42" s="3">
-        <v>293000</v>
+        <v>297800</v>
       </c>
       <c r="I42" s="3">
-        <v>266800</v>
+        <v>271200</v>
       </c>
       <c r="J42" s="3">
-        <v>285000</v>
+        <v>289700</v>
       </c>
       <c r="K42" s="3">
         <v>228800</v>
@@ -3542,25 +3542,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3070900</v>
+        <v>3121500</v>
       </c>
       <c r="E43" s="3">
-        <v>2028400</v>
+        <v>2061800</v>
       </c>
       <c r="F43" s="3">
-        <v>2473300</v>
+        <v>2514000</v>
       </c>
       <c r="G43" s="3">
-        <v>2584500</v>
+        <v>2627100</v>
       </c>
       <c r="H43" s="3">
-        <v>2844100</v>
+        <v>2890900</v>
       </c>
       <c r="I43" s="3">
-        <v>3646000</v>
+        <v>3706000</v>
       </c>
       <c r="J43" s="3">
-        <v>3422000</v>
+        <v>3478400</v>
       </c>
       <c r="K43" s="3">
         <v>2303300</v>
@@ -3634,25 +3634,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1580500</v>
+        <v>1606600</v>
       </c>
       <c r="E44" s="3">
-        <v>1429300</v>
+        <v>1452900</v>
       </c>
       <c r="F44" s="3">
-        <v>1395900</v>
+        <v>1418900</v>
       </c>
       <c r="G44" s="3">
-        <v>1319500</v>
+        <v>1341300</v>
       </c>
       <c r="H44" s="3">
-        <v>1334800</v>
+        <v>1356800</v>
       </c>
       <c r="I44" s="3">
-        <v>1393700</v>
+        <v>1416600</v>
       </c>
       <c r="J44" s="3">
-        <v>1233000</v>
+        <v>1253300</v>
       </c>
       <c r="K44" s="3">
         <v>1146100</v>
@@ -3726,25 +3726,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>309000</v>
+        <v>314100</v>
       </c>
       <c r="E45" s="3">
-        <v>403500</v>
+        <v>410100</v>
       </c>
       <c r="F45" s="3">
-        <v>223200</v>
+        <v>226900</v>
       </c>
       <c r="G45" s="3">
-        <v>200700</v>
+        <v>204000</v>
       </c>
       <c r="H45" s="3">
-        <v>315500</v>
+        <v>320700</v>
       </c>
       <c r="I45" s="3">
-        <v>291500</v>
+        <v>296300</v>
       </c>
       <c r="J45" s="3">
-        <v>215200</v>
+        <v>218700</v>
       </c>
       <c r="K45" s="3">
         <v>170300</v>
@@ -3818,25 +3818,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5462000</v>
+        <v>5552000</v>
       </c>
       <c r="E46" s="3">
-        <v>4330800</v>
+        <v>4402200</v>
       </c>
       <c r="F46" s="3">
-        <v>4511100</v>
+        <v>4585400</v>
       </c>
       <c r="G46" s="3">
-        <v>5130500</v>
+        <v>5215100</v>
       </c>
       <c r="H46" s="3">
-        <v>5198100</v>
+        <v>5283800</v>
       </c>
       <c r="I46" s="3">
-        <v>5767400</v>
+        <v>5862400</v>
       </c>
       <c r="J46" s="3">
-        <v>5246100</v>
+        <v>5332600</v>
       </c>
       <c r="K46" s="3">
         <v>4399200</v>
@@ -4002,25 +4002,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>49630100</v>
+        <v>50447900</v>
       </c>
       <c r="E48" s="3">
-        <v>49901200</v>
+        <v>50723500</v>
       </c>
       <c r="F48" s="3">
-        <v>49747100</v>
+        <v>50566900</v>
       </c>
       <c r="G48" s="3">
-        <v>49823400</v>
+        <v>50644500</v>
       </c>
       <c r="H48" s="3">
-        <v>50776600</v>
+        <v>51613300</v>
       </c>
       <c r="I48" s="3">
-        <v>50724900</v>
+        <v>51560800</v>
       </c>
       <c r="J48" s="3">
-        <v>51012800</v>
+        <v>51853500</v>
       </c>
       <c r="K48" s="3">
         <v>51942200</v>
@@ -4370,25 +4370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>388200</v>
+        <v>394600</v>
       </c>
       <c r="E52" s="3">
-        <v>409300</v>
+        <v>416100</v>
       </c>
       <c r="F52" s="3">
-        <v>456600</v>
+        <v>464100</v>
       </c>
       <c r="G52" s="3">
-        <v>402000</v>
+        <v>408700</v>
       </c>
       <c r="H52" s="3">
-        <v>353300</v>
+        <v>359100</v>
       </c>
       <c r="I52" s="3">
-        <v>335200</v>
+        <v>340700</v>
       </c>
       <c r="J52" s="3">
-        <v>456600</v>
+        <v>464100</v>
       </c>
       <c r="K52" s="3">
         <v>418300</v>
@@ -4554,25 +4554,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>55480300</v>
+        <v>56394500</v>
       </c>
       <c r="E54" s="3">
-        <v>54641300</v>
+        <v>55541700</v>
       </c>
       <c r="F54" s="3">
-        <v>54714800</v>
+        <v>55616400</v>
       </c>
       <c r="G54" s="3">
-        <v>55356000</v>
+        <v>56268200</v>
       </c>
       <c r="H54" s="3">
-        <v>56328000</v>
+        <v>57256200</v>
       </c>
       <c r="I54" s="3">
-        <v>56827500</v>
+        <v>57763900</v>
       </c>
       <c r="J54" s="3">
-        <v>56715500</v>
+        <v>57650100</v>
       </c>
       <c r="K54" s="3">
         <v>56759700</v>
@@ -4714,25 +4714,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>897900</v>
+        <v>912700</v>
       </c>
       <c r="E57" s="3">
-        <v>814300</v>
+        <v>827700</v>
       </c>
       <c r="F57" s="3">
-        <v>887000</v>
+        <v>901600</v>
       </c>
       <c r="G57" s="3">
-        <v>974900</v>
+        <v>991000</v>
       </c>
       <c r="H57" s="3">
-        <v>919700</v>
+        <v>934800</v>
       </c>
       <c r="I57" s="3">
-        <v>836100</v>
+        <v>849800</v>
       </c>
       <c r="J57" s="3">
-        <v>700800</v>
+        <v>712400</v>
       </c>
       <c r="K57" s="3">
         <v>594500</v>
@@ -4806,25 +4806,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1323200</v>
+        <v>1345000</v>
       </c>
       <c r="E58" s="3">
-        <v>1851000</v>
+        <v>1881500</v>
       </c>
       <c r="F58" s="3">
-        <v>898600</v>
+        <v>913400</v>
       </c>
       <c r="G58" s="3">
-        <v>471100</v>
+        <v>478900</v>
       </c>
       <c r="H58" s="3">
-        <v>1135600</v>
+        <v>1154300</v>
       </c>
       <c r="I58" s="3">
-        <v>1076700</v>
+        <v>1094400</v>
       </c>
       <c r="J58" s="3">
-        <v>2127200</v>
+        <v>2162300</v>
       </c>
       <c r="K58" s="3">
         <v>877300</v>
@@ -4898,25 +4898,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3777500</v>
+        <v>3839800</v>
       </c>
       <c r="E59" s="3">
-        <v>3564500</v>
+        <v>3623300</v>
       </c>
       <c r="F59" s="3">
-        <v>3669900</v>
+        <v>3730400</v>
       </c>
       <c r="G59" s="3">
-        <v>4843300</v>
+        <v>4923200</v>
       </c>
       <c r="H59" s="3">
-        <v>4578700</v>
+        <v>4654200</v>
       </c>
       <c r="I59" s="3">
-        <v>4860800</v>
+        <v>4940900</v>
       </c>
       <c r="J59" s="3">
-        <v>4202800</v>
+        <v>4272100</v>
       </c>
       <c r="K59" s="3">
         <v>4023100</v>
@@ -4990,25 +4990,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5998600</v>
+        <v>6097400</v>
       </c>
       <c r="E60" s="3">
-        <v>6229700</v>
+        <v>6332400</v>
       </c>
       <c r="F60" s="3">
-        <v>5455500</v>
+        <v>5545400</v>
       </c>
       <c r="G60" s="3">
-        <v>6289400</v>
+        <v>6393000</v>
       </c>
       <c r="H60" s="3">
-        <v>6634000</v>
+        <v>6743300</v>
       </c>
       <c r="I60" s="3">
-        <v>6773600</v>
+        <v>6885200</v>
       </c>
       <c r="J60" s="3">
-        <v>7030900</v>
+        <v>7146800</v>
       </c>
       <c r="K60" s="3">
         <v>5495000</v>
@@ -5082,25 +5082,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8221800</v>
+        <v>8357200</v>
       </c>
       <c r="E61" s="3">
-        <v>8093800</v>
+        <v>8227200</v>
       </c>
       <c r="F61" s="3">
-        <v>8958900</v>
+        <v>9106600</v>
       </c>
       <c r="G61" s="3">
-        <v>8969100</v>
+        <v>9116900</v>
       </c>
       <c r="H61" s="3">
-        <v>9390800</v>
+        <v>9545500</v>
       </c>
       <c r="I61" s="3">
-        <v>9224300</v>
+        <v>9376300</v>
       </c>
       <c r="J61" s="3">
-        <v>9114500</v>
+        <v>9264700</v>
       </c>
       <c r="K61" s="3">
         <v>11174300</v>
@@ -5174,25 +5174,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12445700</v>
+        <v>12650800</v>
       </c>
       <c r="E62" s="3">
-        <v>12223200</v>
+        <v>12424600</v>
       </c>
       <c r="F62" s="3">
-        <v>12248700</v>
+        <v>12450500</v>
       </c>
       <c r="G62" s="3">
-        <v>12343900</v>
+        <v>12547300</v>
       </c>
       <c r="H62" s="3">
-        <v>12575800</v>
+        <v>12783000</v>
       </c>
       <c r="I62" s="3">
-        <v>12229000</v>
+        <v>12430600</v>
       </c>
       <c r="J62" s="3">
-        <v>12587500</v>
+        <v>12794900</v>
       </c>
       <c r="K62" s="3">
         <v>12737900</v>
@@ -5542,25 +5542,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>26666000</v>
+        <v>27105400</v>
       </c>
       <c r="E66" s="3">
-        <v>26546800</v>
+        <v>26984200</v>
       </c>
       <c r="F66" s="3">
-        <v>26663100</v>
+        <v>27102500</v>
       </c>
       <c r="G66" s="3">
-        <v>27602400</v>
+        <v>28057200</v>
       </c>
       <c r="H66" s="3">
-        <v>28600600</v>
+        <v>29071900</v>
       </c>
       <c r="I66" s="3">
-        <v>28226900</v>
+        <v>28692000</v>
       </c>
       <c r="J66" s="3">
-        <v>28732900</v>
+        <v>29206400</v>
       </c>
       <c r="K66" s="3">
         <v>29407100</v>
@@ -6036,25 +6036,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>20917500</v>
+        <v>21262200</v>
       </c>
       <c r="E72" s="3">
-        <v>20307600</v>
+        <v>20642200</v>
       </c>
       <c r="F72" s="3">
-        <v>20270500</v>
+        <v>20604500</v>
       </c>
       <c r="G72" s="3">
-        <v>20117800</v>
+        <v>20449300</v>
       </c>
       <c r="H72" s="3">
-        <v>20172300</v>
+        <v>20504800</v>
       </c>
       <c r="I72" s="3">
-        <v>21041900</v>
+        <v>21388600</v>
       </c>
       <c r="J72" s="3">
-        <v>20402800</v>
+        <v>20739000</v>
       </c>
       <c r="K72" s="3">
         <v>19825400</v>
@@ -6404,25 +6404,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>28814300</v>
+        <v>29289100</v>
       </c>
       <c r="E76" s="3">
-        <v>28094600</v>
+        <v>28557500</v>
       </c>
       <c r="F76" s="3">
-        <v>28051700</v>
+        <v>28513900</v>
       </c>
       <c r="G76" s="3">
-        <v>27753600</v>
+        <v>28210900</v>
       </c>
       <c r="H76" s="3">
-        <v>27727400</v>
+        <v>28184300</v>
       </c>
       <c r="I76" s="3">
-        <v>28600600</v>
+        <v>29071900</v>
       </c>
       <c r="J76" s="3">
-        <v>27982600</v>
+        <v>28443700</v>
       </c>
       <c r="K76" s="3">
         <v>27352600</v>
@@ -6685,25 +6685,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1704100</v>
+        <v>1732200</v>
       </c>
       <c r="E81" s="3">
-        <v>1063600</v>
+        <v>1081100</v>
       </c>
       <c r="F81" s="3">
-        <v>1307900</v>
+        <v>1329400</v>
       </c>
       <c r="G81" s="3">
-        <v>1105100</v>
+        <v>1123300</v>
       </c>
       <c r="H81" s="3">
-        <v>2045800</v>
+        <v>2079500</v>
       </c>
       <c r="I81" s="3">
-        <v>2546000</v>
+        <v>2587900</v>
       </c>
       <c r="J81" s="3">
-        <v>2254500</v>
+        <v>2291600</v>
       </c>
       <c r="K81" s="3">
         <v>1876100</v>
@@ -6811,25 +6811,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1117400</v>
+        <v>1135800</v>
       </c>
       <c r="E83" s="3">
-        <v>1015600</v>
+        <v>1032400</v>
       </c>
       <c r="F83" s="3">
-        <v>1030900</v>
+        <v>1047900</v>
       </c>
       <c r="G83" s="3">
-        <v>2274800</v>
+        <v>2312300</v>
       </c>
       <c r="H83" s="3">
-        <v>1057100</v>
+        <v>1074500</v>
       </c>
       <c r="I83" s="3">
-        <v>990900</v>
+        <v>1007200</v>
       </c>
       <c r="J83" s="3">
-        <v>1022900</v>
+        <v>1039800</v>
       </c>
       <c r="K83" s="3">
         <v>1090600</v>
@@ -7363,25 +7363,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2543100</v>
+        <v>2585000</v>
       </c>
       <c r="E89" s="3">
-        <v>1995600</v>
+        <v>2028500</v>
       </c>
       <c r="F89" s="3">
-        <v>941500</v>
+        <v>957000</v>
       </c>
       <c r="G89" s="3">
-        <v>3303500</v>
+        <v>3358000</v>
       </c>
       <c r="H89" s="3">
-        <v>4433300</v>
+        <v>4506400</v>
       </c>
       <c r="I89" s="3">
-        <v>4286500</v>
+        <v>4357100</v>
       </c>
       <c r="J89" s="3">
-        <v>2074200</v>
+        <v>2108300</v>
       </c>
       <c r="K89" s="3">
         <v>3488600</v>
@@ -7765,25 +7765,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-871700</v>
+        <v>-886000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1134100</v>
+        <v>-1152800</v>
       </c>
       <c r="F94" s="3">
-        <v>-838200</v>
+        <v>-852100</v>
       </c>
       <c r="G94" s="3">
-        <v>-917500</v>
+        <v>-932600</v>
       </c>
       <c r="H94" s="3">
-        <v>-820800</v>
+        <v>-834300</v>
       </c>
       <c r="I94" s="3">
-        <v>-977800</v>
+        <v>-993900</v>
       </c>
       <c r="J94" s="3">
-        <v>-909500</v>
+        <v>-924500</v>
       </c>
       <c r="K94" s="3">
         <v>-1195700</v>
@@ -7891,25 +7891,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-715400</v>
+        <v>-727200</v>
       </c>
       <c r="E96" s="3">
-        <v>-719000</v>
+        <v>-730900</v>
       </c>
       <c r="F96" s="3">
-        <v>-681900</v>
+        <v>-693200</v>
       </c>
       <c r="G96" s="3">
-        <v>-606300</v>
+        <v>-616300</v>
       </c>
       <c r="H96" s="3">
-        <v>-1840800</v>
+        <v>-1871100</v>
       </c>
       <c r="I96" s="3">
-        <v>-633200</v>
+        <v>-643700</v>
       </c>
       <c r="J96" s="3">
-        <v>-500900</v>
+        <v>-509200</v>
       </c>
       <c r="K96" s="3">
         <v>-408700</v>
@@ -8259,25 +8259,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1669200</v>
+        <v>-1696700</v>
       </c>
       <c r="E100" s="3">
-        <v>-839700</v>
+        <v>-853500</v>
       </c>
       <c r="F100" s="3">
-        <v>-705200</v>
+        <v>-716800</v>
       </c>
       <c r="G100" s="3">
-        <v>-2128000</v>
+        <v>-2163000</v>
       </c>
       <c r="H100" s="3">
-        <v>-3371100</v>
+        <v>-3426700</v>
       </c>
       <c r="I100" s="3">
-        <v>-3230100</v>
+        <v>-3283300</v>
       </c>
       <c r="J100" s="3">
-        <v>-1614700</v>
+        <v>-1641300</v>
       </c>
       <c r="K100" s="3">
         <v>-2403900</v>
@@ -8446,22 +8446,22 @@
         <v>2200</v>
       </c>
       <c r="E102" s="3">
-        <v>21800</v>
+        <v>22200</v>
       </c>
       <c r="F102" s="3">
-        <v>-602000</v>
+        <v>-611900</v>
       </c>
       <c r="G102" s="3">
-        <v>258100</v>
+        <v>262300</v>
       </c>
       <c r="H102" s="3">
-        <v>241400</v>
+        <v>245300</v>
       </c>
       <c r="I102" s="3">
-        <v>78500</v>
+        <v>79800</v>
       </c>
       <c r="J102" s="3">
-        <v>-450000</v>
+        <v>-457400</v>
       </c>
       <c r="K102" s="3">
         <v>-111100</v>

--- a/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>CNQ</t>
   </si>
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7312300</v>
+        <v>6007900</v>
       </c>
       <c r="E8" s="3">
-        <v>5830600</v>
+        <v>6961800</v>
       </c>
       <c r="F8" s="3">
-        <v>6377500</v>
+        <v>7211100</v>
       </c>
       <c r="G8" s="3">
-        <v>7160100</v>
+        <v>5749900</v>
       </c>
       <c r="H8" s="3">
-        <v>7727600</v>
+        <v>6289200</v>
       </c>
       <c r="I8" s="3">
+        <v>7061000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>7620600</v>
+      </c>
+      <c r="K8" s="3">
         <v>8479900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>7890200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>6820900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5711800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4719000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4779000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3882700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3452900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2253000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3531300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4600800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5106900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4410800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4040000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2817600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4286700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>4480600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4120800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3872100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3323600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2910600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2797900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2656500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1793800</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3205700</v>
+        <v>3236400</v>
       </c>
       <c r="E9" s="3">
-        <v>3355800</v>
+        <v>3210200</v>
       </c>
       <c r="F9" s="3">
-        <v>3324000</v>
+        <v>3161400</v>
       </c>
       <c r="G9" s="3">
-        <v>3628400</v>
+        <v>3309300</v>
       </c>
       <c r="H9" s="3">
-        <v>3185800</v>
+        <v>3278000</v>
       </c>
       <c r="I9" s="3">
+        <v>3578200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3141700</v>
+      </c>
+      <c r="K9" s="3">
         <v>3672000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3321800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2912600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2428100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2354100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2378700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2281800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1951100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1701300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2445200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2388900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2332900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2005500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1977700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1895900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1901000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2080700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2094300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2102400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1830800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1529400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1339800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1267600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1104700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4106600</v>
+        <v>2771500</v>
       </c>
       <c r="E10" s="3">
-        <v>2474900</v>
+        <v>3751700</v>
       </c>
       <c r="F10" s="3">
-        <v>3053500</v>
+        <v>4049700</v>
       </c>
       <c r="G10" s="3">
-        <v>3531600</v>
+        <v>2440600</v>
       </c>
       <c r="H10" s="3">
-        <v>4541800</v>
+        <v>3011200</v>
       </c>
       <c r="I10" s="3">
+        <v>3482700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4479000</v>
+      </c>
+      <c r="K10" s="3">
         <v>4807900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4568400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3908400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3283700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2364900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2400400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1600900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1501800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>551700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1086100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2211900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2774000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2405200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2062300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>921700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2385700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2399900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2026500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1769700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1492900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1381300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1458100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1389000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>689100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,52 +1315,58 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-354100</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
-        <v>-167900</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>-167900</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1338,11 +1377,11 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1374,100 +1413,112 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1135800</v>
+        <v>1117200</v>
       </c>
       <c r="E15" s="3">
-        <v>1032400</v>
+        <v>1502000</v>
       </c>
       <c r="F15" s="3">
-        <v>1047900</v>
+        <v>1120100</v>
       </c>
       <c r="G15" s="3">
-        <v>2312300</v>
+        <v>1018100</v>
       </c>
       <c r="H15" s="3">
-        <v>1074500</v>
+        <v>1033400</v>
       </c>
       <c r="I15" s="3">
+        <v>2280300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1059600</v>
+      </c>
+      <c r="K15" s="3">
         <v>1007200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1039800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1090600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1068100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>1003800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1027700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>1249600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1122400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>1101000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1227300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>1208500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1182200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>1036500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>972300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>1010700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>949100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>956000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>946300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>1046400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>945900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>900500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>997900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>959500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4709600</v>
+        <v>4730400</v>
       </c>
       <c r="E17" s="3">
-        <v>4595000</v>
+        <v>4906700</v>
       </c>
       <c r="F17" s="3">
-        <v>4567000</v>
+        <v>4644400</v>
       </c>
       <c r="G17" s="3">
-        <v>6316900</v>
+        <v>4531400</v>
       </c>
       <c r="H17" s="3">
-        <v>4387400</v>
+        <v>4503700</v>
       </c>
       <c r="I17" s="3">
+        <v>6229400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4326600</v>
+      </c>
+      <c r="K17" s="3">
         <v>4760600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4885500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4250400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3283700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3553200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3601600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3580900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3176200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2929400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3623100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3836000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3641200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3139600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3085400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2898200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2878400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3261100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3069900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3316900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2948600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2437300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2453000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2352300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2186400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2602700</v>
+        <v>1277500</v>
       </c>
       <c r="E18" s="3">
-        <v>1235600</v>
+        <v>2055100</v>
       </c>
       <c r="F18" s="3">
-        <v>1810500</v>
+        <v>2566700</v>
       </c>
       <c r="G18" s="3">
-        <v>843200</v>
+        <v>1218500</v>
       </c>
       <c r="H18" s="3">
-        <v>3340200</v>
+        <v>1785500</v>
       </c>
       <c r="I18" s="3">
+        <v>831500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3294000</v>
+      </c>
+      <c r="K18" s="3">
         <v>3719300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3004700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2570500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2428100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1165800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1177400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>301800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>276800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-676400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-91800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>764900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1465800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1271200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>954600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-80700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1408300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1219500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1050900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>555200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>375100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>473300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>344900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>304200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-392600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1780,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-138900</v>
+        <v>-150900</v>
       </c>
       <c r="E20" s="3">
-        <v>205400</v>
+        <v>225900</v>
       </c>
       <c r="F20" s="3">
-        <v>-5900</v>
+        <v>-137000</v>
       </c>
       <c r="G20" s="3">
-        <v>285300</v>
+        <v>202600</v>
       </c>
       <c r="H20" s="3">
-        <v>-447100</v>
+        <v>-5800</v>
       </c>
       <c r="I20" s="3">
+        <v>281300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-440900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-252000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>128600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>104400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-215600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>406400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>182300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>478200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>176300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>355500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-877300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>104500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-143400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>114200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>131600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-422400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>281200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-21100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-249900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>90800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>343100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>494200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>14600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>57600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-59900</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3599600</v>
+        <v>2243900</v>
       </c>
       <c r="E21" s="3">
-        <v>2473400</v>
+        <v>3783000</v>
       </c>
       <c r="F21" s="3">
-        <v>2852500</v>
+        <v>3549800</v>
       </c>
       <c r="G21" s="3">
-        <v>3440700</v>
+        <v>2439200</v>
       </c>
       <c r="H21" s="3">
-        <v>3967600</v>
+        <v>2813000</v>
       </c>
       <c r="I21" s="3">
+        <v>3393100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>3912700</v>
+      </c>
+      <c r="K21" s="3">
         <v>4474600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>4173100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3765500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3280700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2576100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2387300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2029500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1575400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>780000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>258200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2077800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2504600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2421900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2058500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>507600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2638600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>2154500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1747200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1692300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>1664100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>1868000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>1357500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>1321400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>138200</v>
+        <v>100600</v>
       </c>
       <c r="E22" s="3">
-        <v>131500</v>
+        <v>125300</v>
       </c>
       <c r="F22" s="3">
-        <v>113800</v>
+        <v>136300</v>
       </c>
       <c r="G22" s="3">
-        <v>145600</v>
+        <v>129700</v>
       </c>
       <c r="H22" s="3">
-        <v>110800</v>
+        <v>112200</v>
       </c>
       <c r="I22" s="3">
+        <v>143600</v>
+      </c>
+      <c r="J22" s="3">
+        <v>109300</v>
+      </c>
+      <c r="K22" s="3">
         <v>118200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>120500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>150300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>131900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>128000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>133800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>192700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>133400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>156200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>161700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>228400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>191500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>156200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>147000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>181100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>130800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>143000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>143000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>198000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>136200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>107900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>102900</v>
       </c>
-      <c r="AE22" s="3" t="s">
+      <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3" t="s">
+      <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2325600</v>
+        <v>1026100</v>
       </c>
       <c r="E23" s="3">
-        <v>1309500</v>
+        <v>2155700</v>
       </c>
       <c r="F23" s="3">
-        <v>1690800</v>
+        <v>2293400</v>
       </c>
       <c r="G23" s="3">
-        <v>982900</v>
+        <v>1291400</v>
       </c>
       <c r="H23" s="3">
-        <v>2782300</v>
+        <v>1667400</v>
       </c>
       <c r="I23" s="3">
+        <v>969300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>2743800</v>
+      </c>
+      <c r="K23" s="3">
         <v>3349100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>3012900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2524600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2080700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1444300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1225900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>587300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>319700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-477100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1130800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>640900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1130800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1229200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>939200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-684200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1558800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1055400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>657900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>448000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>582000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>859600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>256600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>361800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-452500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>593400</v>
+        <v>306800</v>
       </c>
       <c r="E24" s="3">
-        <v>228300</v>
+        <v>241200</v>
       </c>
       <c r="F24" s="3">
-        <v>361400</v>
+        <v>585200</v>
       </c>
       <c r="G24" s="3">
-        <v>-140400</v>
+        <v>225200</v>
       </c>
       <c r="H24" s="3">
-        <v>702800</v>
+        <v>356400</v>
       </c>
       <c r="I24" s="3">
+        <v>-138500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>693100</v>
+      </c>
+      <c r="K24" s="3">
         <v>761200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>721300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>648600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>449600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>322600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>230000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>7700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>6900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-233900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-124800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>175400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>279400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-1015900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>199400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-93600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>249300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>316200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>219100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>153300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>72900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>61800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>68400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-73000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1732200</v>
+        <v>719300</v>
       </c>
       <c r="E26" s="3">
-        <v>1081100</v>
+        <v>1914500</v>
       </c>
       <c r="F26" s="3">
-        <v>1329400</v>
+        <v>1708200</v>
       </c>
       <c r="G26" s="3">
-        <v>1123300</v>
+        <v>1066200</v>
       </c>
       <c r="H26" s="3">
-        <v>2079500</v>
+        <v>1311000</v>
       </c>
       <c r="I26" s="3">
+        <v>1107700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>2050700</v>
+      </c>
+      <c r="K26" s="3">
         <v>2587900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2291600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1876100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1631100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1121700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>995900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>579500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>312800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-243300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1006000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>465500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>851400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2245000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>739800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-590600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1309500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>739200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>438900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>294700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>509000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>797800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>188200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>434800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1732200</v>
+        <v>719300</v>
       </c>
       <c r="E27" s="3">
-        <v>1081100</v>
+        <v>1914500</v>
       </c>
       <c r="F27" s="3">
-        <v>1329400</v>
+        <v>1708200</v>
       </c>
       <c r="G27" s="3">
-        <v>1123300</v>
+        <v>1066200</v>
       </c>
       <c r="H27" s="3">
-        <v>2079500</v>
+        <v>1311000</v>
       </c>
       <c r="I27" s="3">
+        <v>1107700</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2050700</v>
+      </c>
+      <c r="K27" s="3">
         <v>2587900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2291600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1876100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1631100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1121700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>995900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>579500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>312800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-243300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1006000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>465500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>851400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2245000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>739800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-590600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1309500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>739200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>438900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>294700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>509000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>797800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>188200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>434800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>138900</v>
+        <v>150900</v>
       </c>
       <c r="E32" s="3">
-        <v>-205400</v>
+        <v>-225900</v>
       </c>
       <c r="F32" s="3">
-        <v>5900</v>
+        <v>137000</v>
       </c>
       <c r="G32" s="3">
-        <v>-285300</v>
+        <v>-202600</v>
       </c>
       <c r="H32" s="3">
-        <v>447100</v>
+        <v>5800</v>
       </c>
       <c r="I32" s="3">
+        <v>-281300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>440900</v>
+      </c>
+      <c r="K32" s="3">
         <v>252000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-128600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-104400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>215600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-406400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-182300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-478200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-176300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-355500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>877300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-104500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>143400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-114200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-131600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>422400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-281200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>21100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>249900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-90800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-343100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-494200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-57600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>59900</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1732200</v>
+        <v>719300</v>
       </c>
       <c r="E33" s="3">
-        <v>1081100</v>
+        <v>1914500</v>
       </c>
       <c r="F33" s="3">
-        <v>1329400</v>
+        <v>1708200</v>
       </c>
       <c r="G33" s="3">
-        <v>1123300</v>
+        <v>1066200</v>
       </c>
       <c r="H33" s="3">
-        <v>2079500</v>
+        <v>1311000</v>
       </c>
       <c r="I33" s="3">
+        <v>1107700</v>
+      </c>
+      <c r="J33" s="3">
+        <v>2050700</v>
+      </c>
+      <c r="K33" s="3">
         <v>2587900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2291600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1876100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1631100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1121700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>995900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>579500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>312800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-243300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1006000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>465500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>851400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2245000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>739800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-590600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1309500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>739200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>438900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>294700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>509000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>797800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>188200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>434800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1732200</v>
+        <v>719300</v>
       </c>
       <c r="E35" s="3">
-        <v>1081100</v>
+        <v>1914500</v>
       </c>
       <c r="F35" s="3">
-        <v>1329400</v>
+        <v>1708200</v>
       </c>
       <c r="G35" s="3">
-        <v>1123300</v>
+        <v>1066200</v>
       </c>
       <c r="H35" s="3">
-        <v>2079500</v>
+        <v>1311000</v>
       </c>
       <c r="I35" s="3">
+        <v>1107700</v>
+      </c>
+      <c r="J35" s="3">
+        <v>2050700</v>
+      </c>
+      <c r="K35" s="3">
         <v>2587900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2291600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1876100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1631100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1121700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>995900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>579500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>312800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-243300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1006000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>465500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>851400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2245000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>739800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-590600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1309500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>739200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>438900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>294700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>509000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>797800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>188200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>434800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,560 +3523,598 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>559000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>639100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>91100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>88900</v>
+      </c>
+      <c r="H41" s="3">
+        <v>67000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>670500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>411700</v>
+      </c>
+      <c r="K41" s="3">
+        <v>172200</v>
+      </c>
+      <c r="L41" s="3">
         <v>92400</v>
       </c>
-      <c r="E41" s="3">
-        <v>90200</v>
-      </c>
-      <c r="F41" s="3">
-        <v>68000</v>
-      </c>
-      <c r="G41" s="3">
-        <v>679900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>417500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>172200</v>
-      </c>
-      <c r="J41" s="3">
-        <v>92400</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>550800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>662200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>121500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>120100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>142400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>134200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>182800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>840500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>108400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>145900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>315600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>69300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>76900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>215100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>137000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>114400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>102000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>232200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>37200</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>14600</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>13100</v>
       </c>
       <c r="AF41" s="3">
         <v>14600</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>13100</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>14600</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>417500</v>
+        <v>437300</v>
       </c>
       <c r="E42" s="3">
-        <v>387200</v>
+        <v>382600</v>
       </c>
       <c r="F42" s="3">
-        <v>357700</v>
+        <v>411700</v>
       </c>
       <c r="G42" s="3">
-        <v>362800</v>
+        <v>381900</v>
       </c>
       <c r="H42" s="3">
-        <v>297800</v>
+        <v>352700</v>
       </c>
       <c r="I42" s="3">
+        <v>357800</v>
+      </c>
+      <c r="J42" s="3">
+        <v>293700</v>
+      </c>
+      <c r="K42" s="3">
         <v>271200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>289700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>228800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>226700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>339200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>305200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>236000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>208500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>215800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>174200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>382000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>470100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>433800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>422600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>398800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>478200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>560800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>587900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>664600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>660900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>619200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>626100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>701400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>464800</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3121500</v>
+        <v>2483600</v>
       </c>
       <c r="E43" s="3">
-        <v>2061800</v>
+        <v>2324000</v>
       </c>
       <c r="F43" s="3">
-        <v>2514000</v>
+        <v>3078300</v>
       </c>
       <c r="G43" s="3">
-        <v>2627100</v>
+        <v>2033200</v>
       </c>
       <c r="H43" s="3">
-        <v>2890900</v>
+        <v>2479200</v>
       </c>
       <c r="I43" s="3">
+        <v>2590700</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2850900</v>
+      </c>
+      <c r="K43" s="3">
         <v>3706000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3478400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2303300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2352600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2302700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2012700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1933600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1477300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1692700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1195900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1932000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1993900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1684400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1760600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>873700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1436700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1965500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2023500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1239100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1637300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1637100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>1755400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1441200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1606600</v>
+        <v>1678300</v>
       </c>
       <c r="E44" s="3">
-        <v>1452900</v>
+        <v>1482300</v>
       </c>
       <c r="F44" s="3">
-        <v>1418900</v>
+        <v>1584300</v>
       </c>
       <c r="G44" s="3">
-        <v>1341300</v>
+        <v>1432700</v>
       </c>
       <c r="H44" s="3">
-        <v>1356800</v>
+        <v>1399200</v>
       </c>
       <c r="I44" s="3">
+        <v>1322700</v>
+      </c>
+      <c r="J44" s="3">
+        <v>1338000</v>
+      </c>
+      <c r="K44" s="3">
         <v>1416600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1253300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1146100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>914800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>878000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>786900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>820200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>830300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>859300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>737700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>898200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>954200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>942900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>825200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>726800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>812400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>783700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>744500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>665300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>652700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>691400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>505500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>529300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>473200</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>314100</v>
+        <v>271100</v>
       </c>
       <c r="E45" s="3">
-        <v>410100</v>
+        <v>395000</v>
       </c>
       <c r="F45" s="3">
-        <v>226900</v>
+        <v>309700</v>
       </c>
       <c r="G45" s="3">
+        <v>404500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>223700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>201100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>316300</v>
+      </c>
+      <c r="K45" s="3">
+        <v>296300</v>
+      </c>
+      <c r="L45" s="3">
+        <v>218700</v>
+      </c>
+      <c r="M45" s="3">
+        <v>170300</v>
+      </c>
+      <c r="N45" s="3">
+        <v>257000</v>
+      </c>
+      <c r="O45" s="3">
+        <v>324700</v>
+      </c>
+      <c r="P45" s="3">
+        <v>284900</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>242200</v>
+      </c>
+      <c r="R45" s="3">
+        <v>443100</v>
+      </c>
+      <c r="S45" s="3">
+        <v>240900</v>
+      </c>
+      <c r="T45" s="3">
+        <v>335100</v>
+      </c>
+      <c r="U45" s="3">
+        <v>177800</v>
+      </c>
+      <c r="V45" s="3">
+        <v>314200</v>
+      </c>
+      <c r="W45" s="3">
+        <v>306900</v>
+      </c>
+      <c r="X45" s="3">
         <v>204000</v>
       </c>
-      <c r="H45" s="3">
-        <v>320700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>296300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>218700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>170300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>257000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>324700</v>
-      </c>
-      <c r="N45" s="3">
-        <v>284900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>242200</v>
-      </c>
-      <c r="P45" s="3">
-        <v>443100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>240900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>335100</v>
-      </c>
-      <c r="S45" s="3">
-        <v>177800</v>
-      </c>
-      <c r="T45" s="3">
-        <v>314200</v>
-      </c>
-      <c r="U45" s="3">
-        <v>306900</v>
-      </c>
-      <c r="V45" s="3">
-        <v>204000</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>222200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>258700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>297400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>198700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>189000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>282100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>266400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>398700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>331900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>320400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5552000</v>
+        <v>5429300</v>
       </c>
       <c r="E46" s="3">
-        <v>4402200</v>
+        <v>5223000</v>
       </c>
       <c r="F46" s="3">
-        <v>4585400</v>
+        <v>5475200</v>
       </c>
       <c r="G46" s="3">
-        <v>5215100</v>
+        <v>4341200</v>
       </c>
       <c r="H46" s="3">
-        <v>5283800</v>
+        <v>4522000</v>
       </c>
       <c r="I46" s="3">
+        <v>5142900</v>
+      </c>
+      <c r="J46" s="3">
+        <v>5210600</v>
+      </c>
+      <c r="K46" s="3">
         <v>5862400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5332600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4399200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4413300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3966100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3509800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3374300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3093400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3191500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3283400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3498400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3878300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3683600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3281700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2298500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3201100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3744400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3301700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3644400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3066900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3251500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3182000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3331000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>2714200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3940,156 +4149,168 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>401400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>429400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>520500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>536000</v>
       </c>
-      <c r="R47" s="3" t="s">
+      <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>508300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>587800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>620100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>641300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>668200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>627900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>641400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>627800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>596900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>557400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>519500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>504700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>496300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>499300</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>50447900</v>
+        <v>49485000</v>
       </c>
       <c r="E48" s="3">
-        <v>50723500</v>
+        <v>49735700</v>
       </c>
       <c r="F48" s="3">
-        <v>50566900</v>
+        <v>49749500</v>
       </c>
       <c r="G48" s="3">
-        <v>50644500</v>
+        <v>50021400</v>
       </c>
       <c r="H48" s="3">
-        <v>51613300</v>
+        <v>49866900</v>
       </c>
       <c r="I48" s="3">
+        <v>49943400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>50898800</v>
+      </c>
+      <c r="K48" s="3">
         <v>51560800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>51853500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>51942200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>50911800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>49876100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>50009900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>54033300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>52633700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>54504900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>55426200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>56456700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>60141800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>57872200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>52626400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>51142200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>49193300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>50788500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>50896900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>50458900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>50437300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>49826300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>40562500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>40940500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>41054200</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>394600</v>
+        <v>456900</v>
       </c>
       <c r="E52" s="3">
-        <v>416100</v>
+        <v>394300</v>
       </c>
       <c r="F52" s="3">
+        <v>389200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>410300</v>
+      </c>
+      <c r="H52" s="3">
+        <v>457700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>403000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>354200</v>
+      </c>
+      <c r="K52" s="3">
+        <v>340700</v>
+      </c>
+      <c r="L52" s="3">
         <v>464100</v>
       </c>
-      <c r="G52" s="3">
-        <v>408700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>359100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>340700</v>
-      </c>
-      <c r="J52" s="3">
-        <v>464100</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>418300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>445900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>418700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>412200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>407800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>276800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>423000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>992700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>445200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>499100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>437000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>392600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>353900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>276100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>290600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>288300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>272400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>256800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>276100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>262000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>287300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>258900</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>56394500</v>
+        <v>55371200</v>
       </c>
       <c r="E54" s="3">
-        <v>55541700</v>
+        <v>55353000</v>
       </c>
       <c r="F54" s="3">
-        <v>55616400</v>
+        <v>55613900</v>
       </c>
       <c r="G54" s="3">
-        <v>56268200</v>
+        <v>54772900</v>
       </c>
       <c r="H54" s="3">
-        <v>57256200</v>
+        <v>54846500</v>
       </c>
       <c r="I54" s="3">
+        <v>55489200</v>
+      </c>
+      <c r="J54" s="3">
+        <v>56463600</v>
+      </c>
+      <c r="K54" s="3">
         <v>57763900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>57650100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>56759700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>55771100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>54261000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>54333300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>58244800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>56524400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>58655400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>59702200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>60908600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>65107000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>62612900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>56942000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>54462800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>53298400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>55464800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>55114800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>54972600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>54318400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>53873400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>44511200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>45055200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>44526600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4967,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>912700</v>
+        <v>829300</v>
       </c>
       <c r="E57" s="3">
-        <v>827700</v>
+        <v>1033400</v>
       </c>
       <c r="F57" s="3">
-        <v>901600</v>
+        <v>900000</v>
       </c>
       <c r="G57" s="3">
-        <v>991000</v>
+        <v>816200</v>
       </c>
       <c r="H57" s="3">
-        <v>934800</v>
+        <v>889100</v>
       </c>
       <c r="I57" s="3">
+        <v>977300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>921900</v>
+      </c>
+      <c r="K57" s="3">
         <v>849800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>712400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>594500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>732600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>566300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>548900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>516100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>632500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>475600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>629400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>636200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>548800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>732800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>599700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>592900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>732500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>730200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>705400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>576800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>590900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>488200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>415600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>457100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>480900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1345000</v>
+        <v>1526000</v>
       </c>
       <c r="E58" s="3">
-        <v>1881500</v>
+        <v>931400</v>
       </c>
       <c r="F58" s="3">
-        <v>913400</v>
+        <v>1326300</v>
       </c>
       <c r="G58" s="3">
-        <v>478900</v>
+        <v>1855400</v>
       </c>
       <c r="H58" s="3">
-        <v>1154300</v>
+        <v>900700</v>
       </c>
       <c r="I58" s="3">
+        <v>472200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1138300</v>
+      </c>
+      <c r="K58" s="3">
         <v>1094400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2162300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>877300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>878500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1797900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1416100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1185400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>779700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1604800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2373100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2045900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3548300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3330700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1445700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>868400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>363300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>621800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>484800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1396900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1395400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1448200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>2403800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1392000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1611700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3839800</v>
+        <v>3828200</v>
       </c>
       <c r="E59" s="3">
-        <v>3623300</v>
+        <v>3453600</v>
       </c>
       <c r="F59" s="3">
-        <v>3730400</v>
+        <v>3786600</v>
       </c>
       <c r="G59" s="3">
-        <v>4923200</v>
+        <v>3573100</v>
       </c>
       <c r="H59" s="3">
-        <v>4654200</v>
+        <v>3678800</v>
       </c>
       <c r="I59" s="3">
+        <v>4855000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>4589700</v>
+      </c>
+      <c r="K59" s="3">
         <v>4940900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4272100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>4023100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3229600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2742500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2373600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2227600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1774000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1778200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1944600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2492600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2415000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2201400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2274000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2163000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2387900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2305000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2067900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2685900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2323400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2111300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1827600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2062700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1857600</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6097400</v>
+        <v>6183500</v>
       </c>
       <c r="E60" s="3">
-        <v>6332400</v>
+        <v>5418300</v>
       </c>
       <c r="F60" s="3">
-        <v>5545400</v>
+        <v>6013000</v>
       </c>
       <c r="G60" s="3">
-        <v>6393000</v>
+        <v>6244700</v>
       </c>
       <c r="H60" s="3">
-        <v>6743300</v>
+        <v>5468600</v>
       </c>
       <c r="I60" s="3">
+        <v>6304500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>6649900</v>
+      </c>
+      <c r="K60" s="3">
         <v>6885200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7146800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5495000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4840700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5106700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4338600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3929100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3186200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3858600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4947000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5174700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6512200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>6264900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4319500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3624300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3483800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3657100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>3258100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>4659500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>4309700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>4047800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>3911800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>3950200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8357200</v>
+        <v>7638100</v>
       </c>
       <c r="E61" s="3">
-        <v>8227200</v>
+        <v>8071700</v>
       </c>
       <c r="F61" s="3">
-        <v>9106600</v>
+        <v>8241500</v>
       </c>
       <c r="G61" s="3">
-        <v>9116900</v>
+        <v>8113300</v>
       </c>
       <c r="H61" s="3">
-        <v>9545500</v>
+        <v>8980500</v>
       </c>
       <c r="I61" s="3">
+        <v>8990700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>9413400</v>
+      </c>
+      <c r="K61" s="3">
         <v>9376300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>9264700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11174300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>12736300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>12630300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>14248200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>16721500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>17244000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>17783800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>16800500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>15905300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>16634100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>16797700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>15936000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>14827600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>13976400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>15485600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>16060000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>15316600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>15662600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>15874000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>10121400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>11518100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>11672500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12650800</v>
+        <v>12757700</v>
       </c>
       <c r="E62" s="3">
-        <v>12424600</v>
+        <v>12834900</v>
       </c>
       <c r="F62" s="3">
-        <v>12450500</v>
+        <v>12475600</v>
       </c>
       <c r="G62" s="3">
-        <v>12547300</v>
+        <v>12252600</v>
       </c>
       <c r="H62" s="3">
-        <v>12783000</v>
+        <v>12278100</v>
       </c>
       <c r="I62" s="3">
+        <v>12373600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>12606100</v>
+      </c>
+      <c r="K62" s="3">
         <v>12430600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>12794900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>12737900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>11878500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>11784900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>11713300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>12540200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>11434400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>11640000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>11852700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>12547200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>13114700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>12370300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>11846000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>11675900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>11571800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>11923400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>11687800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>11440000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>11023200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>10891500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>9479200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>9446200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>9203400</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27105400</v>
+        <v>26579300</v>
       </c>
       <c r="E66" s="3">
-        <v>26984200</v>
+        <v>26325000</v>
       </c>
       <c r="F66" s="3">
-        <v>27102500</v>
+        <v>26730200</v>
       </c>
       <c r="G66" s="3">
-        <v>28057200</v>
+        <v>26610700</v>
       </c>
       <c r="H66" s="3">
-        <v>29071900</v>
+        <v>26727300</v>
       </c>
       <c r="I66" s="3">
+        <v>27668800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>28669400</v>
+      </c>
+      <c r="K66" s="3">
         <v>28692000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>29206400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>29407100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>29455500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>29521800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>30300000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>33190800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>31864600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>33282400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>33600200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>33627200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>36261000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>35432900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>32101500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>30127700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>29032000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>31066100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>31005900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>31416100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>30995600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>30813300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>24247600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>24876100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>24826100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>21262200</v>
+        <v>20604200</v>
       </c>
       <c r="E72" s="3">
-        <v>20642200</v>
+        <v>21096100</v>
       </c>
       <c r="F72" s="3">
-        <v>20604500</v>
+        <v>20967900</v>
       </c>
       <c r="G72" s="3">
-        <v>20449300</v>
+        <v>20356500</v>
       </c>
       <c r="H72" s="3">
-        <v>20504800</v>
+        <v>20319300</v>
       </c>
       <c r="I72" s="3">
+        <v>20166200</v>
+      </c>
+      <c r="J72" s="3">
+        <v>20220900</v>
+      </c>
+      <c r="K72" s="3">
         <v>21388600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>20739000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>19825400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>18986600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>17639300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>17044100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>17615200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>17264700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>17746100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>18382500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>19822300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>21042900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>19767600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>17591900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>17146600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>17464500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>17309700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>17152300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>16828100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>16783400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>16523700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>16490100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>16536900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>16314900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29289100</v>
+        <v>28791900</v>
       </c>
       <c r="E76" s="3">
-        <v>28557500</v>
+        <v>29028000</v>
       </c>
       <c r="F76" s="3">
-        <v>28513900</v>
+        <v>28883700</v>
       </c>
       <c r="G76" s="3">
-        <v>28210900</v>
+        <v>28162200</v>
       </c>
       <c r="H76" s="3">
-        <v>28184300</v>
+        <v>28119200</v>
       </c>
       <c r="I76" s="3">
+        <v>27820400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>27794200</v>
+      </c>
+      <c r="K76" s="3">
         <v>29071900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>28443700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>27352600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>26315500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>24739200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>24033300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>25054000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>24659700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>25373000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>26102000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>27281400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>28846000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>27180000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>24840600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>24335100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>24266400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>24398700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>24108900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>23556500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>23322800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>23060100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>20263600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>20179100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>19700500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1732200</v>
+        <v>719300</v>
       </c>
       <c r="E81" s="3">
-        <v>1081100</v>
+        <v>1914500</v>
       </c>
       <c r="F81" s="3">
-        <v>1329400</v>
+        <v>1708200</v>
       </c>
       <c r="G81" s="3">
-        <v>1123300</v>
+        <v>1066200</v>
       </c>
       <c r="H81" s="3">
-        <v>2079500</v>
+        <v>1311000</v>
       </c>
       <c r="I81" s="3">
+        <v>1107700</v>
+      </c>
+      <c r="J81" s="3">
+        <v>2050700</v>
+      </c>
+      <c r="K81" s="3">
         <v>2587900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2291600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1876100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1631100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1121700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>995900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>579500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>312800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-243300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1006000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>465500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>851400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2245000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>739800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-590600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1309500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>739200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>438900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>294700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>509000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>797800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>188200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>434800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7200,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1135800</v>
+        <v>1117200</v>
       </c>
       <c r="E83" s="3">
-        <v>1032400</v>
+        <v>1502000</v>
       </c>
       <c r="F83" s="3">
-        <v>1047900</v>
+        <v>1120100</v>
       </c>
       <c r="G83" s="3">
-        <v>2312300</v>
+        <v>1018100</v>
       </c>
       <c r="H83" s="3">
-        <v>1074500</v>
+        <v>1033400</v>
       </c>
       <c r="I83" s="3">
+        <v>2280300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1059600</v>
+      </c>
+      <c r="K83" s="3">
         <v>1007200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1039800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1090600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1068100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1003800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1027700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1249600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1122400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1101000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1227300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1208500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1182200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1036500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>972300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1010700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>949100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>956000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>946300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1046400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>945900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>900500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>997900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>959500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2585000</v>
+        <v>2090100</v>
       </c>
       <c r="E89" s="3">
-        <v>2028500</v>
+        <v>3509000</v>
       </c>
       <c r="F89" s="3">
-        <v>957000</v>
+        <v>2549200</v>
       </c>
       <c r="G89" s="3">
-        <v>3358000</v>
+        <v>2000400</v>
       </c>
       <c r="H89" s="3">
-        <v>4506400</v>
+        <v>943700</v>
       </c>
       <c r="I89" s="3">
+        <v>3311500</v>
+      </c>
+      <c r="J89" s="3">
+        <v>4444000</v>
+      </c>
+      <c r="K89" s="3">
         <v>4357100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2108300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3488600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3177800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2126300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1834100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>982700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1586900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-275400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1353700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1913300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2087500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2268800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>766700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1063200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2646600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1967000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1858600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1070200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1876900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1213800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1283700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>964100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7922,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1113000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-975000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1108000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1569000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1257000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1135000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1388000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1554000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-957000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>2200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>1416700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1401400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-5500</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-2500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-29300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-25400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>72300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-215800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-42200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-618400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-493200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-816600</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-886000</v>
+        <v>-1014400</v>
       </c>
       <c r="E94" s="3">
-        <v>-1152800</v>
+        <v>-689400</v>
       </c>
       <c r="F94" s="3">
-        <v>-852100</v>
+        <v>-873800</v>
       </c>
       <c r="G94" s="3">
-        <v>-932600</v>
+        <v>-1136900</v>
       </c>
       <c r="H94" s="3">
-        <v>-834300</v>
+        <v>-840300</v>
       </c>
       <c r="I94" s="3">
+        <v>-919700</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-822800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-993900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-924500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1195700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-534100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-520000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-468600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-482800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-492900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-543800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-674100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-665800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-752800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-3540000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-792100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-793100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-919300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-856700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1030600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-799300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1458700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-6656200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-863500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-411000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-658400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,100 +8350,108 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-727200</v>
+        <v>-784100</v>
       </c>
       <c r="E96" s="3">
-        <v>-730900</v>
+        <v>-714200</v>
       </c>
       <c r="F96" s="3">
-        <v>-693200</v>
+        <v>-717100</v>
       </c>
       <c r="G96" s="3">
-        <v>-616300</v>
+        <v>-720700</v>
       </c>
       <c r="H96" s="3">
-        <v>-1871100</v>
+        <v>-683600</v>
       </c>
       <c r="I96" s="3">
+        <v>-607800</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-1845200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-643700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-509200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-408700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-413300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-402800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-363800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-388400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-384900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-393900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-348400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-346200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-370600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-356100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-310200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-309000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-297200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-309400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-252900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-249300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-248600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-227700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-195100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-193600</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8738,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1696700</v>
+        <v>-1155800</v>
       </c>
       <c r="E100" s="3">
-        <v>-853500</v>
+        <v>-2271500</v>
       </c>
       <c r="F100" s="3">
-        <v>-716800</v>
+        <v>-1673200</v>
       </c>
       <c r="G100" s="3">
-        <v>-2163000</v>
+        <v>-841700</v>
       </c>
       <c r="H100" s="3">
-        <v>-3426700</v>
+        <v>-706900</v>
       </c>
       <c r="I100" s="3">
+        <v>-2133100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-3379300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3283300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1641300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2403900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2105900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1604800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1378500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-492900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1138500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>161700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>51800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1276300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1518800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1515500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>16900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-418600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1644500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1087800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-816800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-401100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-223300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>5465500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-418700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-554700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>548000</v>
+      </c>
+      <c r="F102" s="3">
         <v>2200</v>
       </c>
-      <c r="E102" s="3">
-        <v>22200</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-611900</v>
-      </c>
       <c r="G102" s="3">
-        <v>262300</v>
+        <v>21900</v>
       </c>
       <c r="H102" s="3">
-        <v>245300</v>
+        <v>-603400</v>
       </c>
       <c r="I102" s="3">
+        <v>258700</v>
+      </c>
+      <c r="J102" s="3">
+        <v>241900</v>
+      </c>
+      <c r="K102" s="3">
         <v>79800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-457400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-111100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>537800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-13000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>7000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-44500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-657600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>731400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-28800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-184000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>244300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-8500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-148400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>82800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>22600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>11300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-130200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>195000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>23100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>CNQ</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6007900</v>
+        <v>6662500</v>
       </c>
       <c r="E8" s="3">
-        <v>6961800</v>
+        <v>6068500</v>
       </c>
       <c r="F8" s="3">
-        <v>7211100</v>
+        <v>7032100</v>
       </c>
       <c r="G8" s="3">
-        <v>5749900</v>
+        <v>7283800</v>
       </c>
       <c r="H8" s="3">
-        <v>6289200</v>
+        <v>5807900</v>
       </c>
       <c r="I8" s="3">
-        <v>7061000</v>
+        <v>6352600</v>
       </c>
       <c r="J8" s="3">
+        <v>7132200</v>
+      </c>
+      <c r="K8" s="3">
         <v>7620600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8479900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7890200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6820900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5711800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4719000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4779000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3882700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3452900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2253000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3531300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4600800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5106900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4410800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4040000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2817600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4286700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4480600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4120800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3872100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3323600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2910600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2797900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2656500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1793800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3236400</v>
+        <v>3411100</v>
       </c>
       <c r="E9" s="3">
-        <v>3210200</v>
+        <v>3269100</v>
       </c>
       <c r="F9" s="3">
-        <v>3161400</v>
+        <v>3242600</v>
       </c>
       <c r="G9" s="3">
-        <v>3309300</v>
+        <v>3193200</v>
       </c>
       <c r="H9" s="3">
-        <v>3278000</v>
+        <v>3342700</v>
       </c>
       <c r="I9" s="3">
-        <v>3578200</v>
+        <v>3311000</v>
       </c>
       <c r="J9" s="3">
+        <v>3614300</v>
+      </c>
+      <c r="K9" s="3">
         <v>3141700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3672000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3321800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2912600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2428100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2354100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2378700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2281800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1951100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1701300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2445200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2388900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2332900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2005500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1977700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1895900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1901000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2080700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2094300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2102400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1830800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1529400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1339800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1267600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1104700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2771500</v>
+        <v>3251400</v>
       </c>
       <c r="E10" s="3">
-        <v>3751700</v>
+        <v>2799400</v>
       </c>
       <c r="F10" s="3">
-        <v>4049700</v>
+        <v>3789500</v>
       </c>
       <c r="G10" s="3">
-        <v>2440600</v>
+        <v>4090600</v>
       </c>
       <c r="H10" s="3">
-        <v>3011200</v>
+        <v>2465200</v>
       </c>
       <c r="I10" s="3">
-        <v>3482700</v>
+        <v>3041600</v>
       </c>
       <c r="J10" s="3">
+        <v>3517900</v>
+      </c>
+      <c r="K10" s="3">
         <v>4479000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4807900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4568400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3908400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3283700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2364900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2400400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1600900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1501800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>551700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1086100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2211900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2774000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2405200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2062300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>921700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2385700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2399900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2026500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1769700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1492900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1381300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1458100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1389000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>689100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,19 +1338,22 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1341,35 +1361,35 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-354100</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>-167900</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1383,8 +1403,8 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1419,106 +1439,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1117200</v>
+        <v>1213800</v>
       </c>
       <c r="E15" s="3">
-        <v>1502000</v>
+        <v>1128500</v>
       </c>
       <c r="F15" s="3">
-        <v>1120100</v>
+        <v>1517100</v>
       </c>
       <c r="G15" s="3">
-        <v>1018100</v>
+        <v>1131400</v>
       </c>
       <c r="H15" s="3">
-        <v>1033400</v>
+        <v>1028300</v>
       </c>
       <c r="I15" s="3">
-        <v>2280300</v>
+        <v>1043800</v>
       </c>
       <c r="J15" s="3">
+        <v>2303300</v>
+      </c>
+      <c r="K15" s="3">
         <v>1059600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1007200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1039800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1090600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1068100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1003800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1027700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1249600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1122400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1101000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1227300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1208500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1182200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1036500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>972300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1010700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>949100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>956000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>946300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1046400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>945900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>900500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>997900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>959500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4730400</v>
+        <v>4778100</v>
       </c>
       <c r="E17" s="3">
-        <v>4906700</v>
+        <v>4778100</v>
       </c>
       <c r="F17" s="3">
-        <v>4644400</v>
+        <v>4956200</v>
       </c>
       <c r="G17" s="3">
-        <v>4531400</v>
+        <v>4691200</v>
       </c>
       <c r="H17" s="3">
-        <v>4503700</v>
+        <v>4577100</v>
       </c>
       <c r="I17" s="3">
-        <v>6229400</v>
+        <v>4549200</v>
       </c>
       <c r="J17" s="3">
+        <v>6292300</v>
+      </c>
+      <c r="K17" s="3">
         <v>4326600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4760600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4885500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4250400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3283700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3553200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3601600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3580900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3176200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2929400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3623100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3836000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3641200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3139600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3085400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2898200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2878400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3261100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3069900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3316900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2948600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2437300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2453000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2352300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2186400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1277500</v>
+        <v>1884400</v>
       </c>
       <c r="E18" s="3">
-        <v>2055100</v>
+        <v>1290400</v>
       </c>
       <c r="F18" s="3">
-        <v>2566700</v>
+        <v>2075800</v>
       </c>
       <c r="G18" s="3">
-        <v>1218500</v>
+        <v>2592600</v>
       </c>
       <c r="H18" s="3">
-        <v>1785500</v>
+        <v>1230800</v>
       </c>
       <c r="I18" s="3">
-        <v>831500</v>
+        <v>1803500</v>
       </c>
       <c r="J18" s="3">
+        <v>839900</v>
+      </c>
+      <c r="K18" s="3">
         <v>3294000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3719300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3004700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2570500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2428100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1165800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1177400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>301800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>276800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-676400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-91800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>764900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1465800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1271200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>954600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-80700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1408300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1219500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1050900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>555200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>375100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>473300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>344900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>304200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-392600</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-150900</v>
+        <v>-107500</v>
       </c>
       <c r="E20" s="3">
-        <v>225900</v>
+        <v>-152400</v>
       </c>
       <c r="F20" s="3">
-        <v>-137000</v>
+        <v>228200</v>
       </c>
       <c r="G20" s="3">
-        <v>202600</v>
+        <v>-138400</v>
       </c>
       <c r="H20" s="3">
-        <v>-5800</v>
+        <v>204600</v>
       </c>
       <c r="I20" s="3">
-        <v>281300</v>
+        <v>-5900</v>
       </c>
       <c r="J20" s="3">
+        <v>284100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-440900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-252000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>128600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>104400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-215600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>406400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>182300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>478200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>176300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>355500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-877300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>104500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-143400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>114200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>131600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-422400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>281200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-21100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-249900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>90800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>343100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>494200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>14600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>57600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-59900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2243900</v>
+        <v>2990800</v>
       </c>
       <c r="E21" s="3">
-        <v>3783000</v>
+        <v>2266500</v>
       </c>
       <c r="F21" s="3">
-        <v>3549800</v>
+        <v>3821100</v>
       </c>
       <c r="G21" s="3">
-        <v>2439200</v>
+        <v>3585600</v>
       </c>
       <c r="H21" s="3">
-        <v>2813000</v>
+        <v>2463800</v>
       </c>
       <c r="I21" s="3">
-        <v>3393100</v>
+        <v>2841400</v>
       </c>
       <c r="J21" s="3">
+        <v>3427300</v>
+      </c>
+      <c r="K21" s="3">
         <v>3912700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4474600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4173100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3765500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3280700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2576100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2387300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2029500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1575400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>780000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>258200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2077800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2504600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2421900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2058500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>507600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2638600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2154500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1747200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1692300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1664100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1868000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1357500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1321400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100600</v>
+        <v>116300</v>
       </c>
       <c r="E22" s="3">
-        <v>125300</v>
+        <v>101600</v>
       </c>
       <c r="F22" s="3">
-        <v>136300</v>
+        <v>126600</v>
       </c>
       <c r="G22" s="3">
-        <v>129700</v>
+        <v>137700</v>
       </c>
       <c r="H22" s="3">
-        <v>112200</v>
+        <v>131000</v>
       </c>
       <c r="I22" s="3">
-        <v>143600</v>
+        <v>113400</v>
       </c>
       <c r="J22" s="3">
+        <v>145000</v>
+      </c>
+      <c r="K22" s="3">
         <v>109300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>118200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>120500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>150300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>131900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>128000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>133800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>192700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>133400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>156200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>161700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>228400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>191500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>156200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>147000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>181100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>130800</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>143000</v>
       </c>
       <c r="AB22" s="3">
         <v>143000</v>
       </c>
       <c r="AC22" s="3">
+        <v>143000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>198000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>136200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>107900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>102900</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1026100</v>
+        <v>1660700</v>
       </c>
       <c r="E23" s="3">
-        <v>2155700</v>
+        <v>1036400</v>
       </c>
       <c r="F23" s="3">
-        <v>2293400</v>
+        <v>2177400</v>
       </c>
       <c r="G23" s="3">
-        <v>1291400</v>
+        <v>2316500</v>
       </c>
       <c r="H23" s="3">
-        <v>1667400</v>
+        <v>1304400</v>
       </c>
       <c r="I23" s="3">
-        <v>969300</v>
+        <v>1684200</v>
       </c>
       <c r="J23" s="3">
+        <v>979000</v>
+      </c>
+      <c r="K23" s="3">
         <v>2743800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3349100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3012900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2524600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2080700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1444300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1225900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>587300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>319700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-477100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1130800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>640900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1130800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1229200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>939200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-684200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1558800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1055400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>657900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>448000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>582000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>859600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>256600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>361800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-452500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>306800</v>
+        <v>398200</v>
       </c>
       <c r="E24" s="3">
-        <v>241200</v>
+        <v>309900</v>
       </c>
       <c r="F24" s="3">
-        <v>585200</v>
+        <v>243700</v>
       </c>
       <c r="G24" s="3">
-        <v>225200</v>
+        <v>591100</v>
       </c>
       <c r="H24" s="3">
-        <v>356400</v>
+        <v>227500</v>
       </c>
       <c r="I24" s="3">
-        <v>-138500</v>
+        <v>360000</v>
       </c>
       <c r="J24" s="3">
+        <v>-139900</v>
+      </c>
+      <c r="K24" s="3">
         <v>693100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>761200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>721300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>648600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>449600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>322600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>230000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-233900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-124800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>175400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>279400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1015900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>199400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-93600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>249300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>316200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>219100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>153300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>72900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>61800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>68400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-73000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>719300</v>
+        <v>1262400</v>
       </c>
       <c r="E26" s="3">
-        <v>1914500</v>
+        <v>726500</v>
       </c>
       <c r="F26" s="3">
-        <v>1708200</v>
+        <v>1933800</v>
       </c>
       <c r="G26" s="3">
-        <v>1066200</v>
+        <v>1725400</v>
       </c>
       <c r="H26" s="3">
-        <v>1311000</v>
+        <v>1076900</v>
       </c>
       <c r="I26" s="3">
-        <v>1107700</v>
+        <v>1324300</v>
       </c>
       <c r="J26" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="K26" s="3">
         <v>2050700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2587900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2291600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1876100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1631100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1121700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>995900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>579500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>312800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-243300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1006000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>465500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>851400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2245000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>739800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-590600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1309500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>739200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>438900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>294700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>509000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>797800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>188200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>434800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>719300</v>
+        <v>1262400</v>
       </c>
       <c r="E27" s="3">
-        <v>1914500</v>
+        <v>726500</v>
       </c>
       <c r="F27" s="3">
-        <v>1708200</v>
+        <v>1933800</v>
       </c>
       <c r="G27" s="3">
-        <v>1066200</v>
+        <v>1725400</v>
       </c>
       <c r="H27" s="3">
-        <v>1311000</v>
+        <v>1076900</v>
       </c>
       <c r="I27" s="3">
-        <v>1107700</v>
+        <v>1324300</v>
       </c>
       <c r="J27" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="K27" s="3">
         <v>2050700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2587900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2291600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1876100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1631100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1121700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>995900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>579500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>312800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-243300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1006000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>465500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>851400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2245000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>739800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-590600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1309500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>739200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>438900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>294700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>509000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>797800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>188200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>434800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>150900</v>
+        <v>107500</v>
       </c>
       <c r="E32" s="3">
-        <v>-225900</v>
+        <v>152400</v>
       </c>
       <c r="F32" s="3">
-        <v>137000</v>
+        <v>-228200</v>
       </c>
       <c r="G32" s="3">
-        <v>-202600</v>
+        <v>138400</v>
       </c>
       <c r="H32" s="3">
-        <v>5800</v>
+        <v>-204600</v>
       </c>
       <c r="I32" s="3">
-        <v>-281300</v>
+        <v>5900</v>
       </c>
       <c r="J32" s="3">
+        <v>-284100</v>
+      </c>
+      <c r="K32" s="3">
         <v>440900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>252000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-128600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-104400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>215600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-406400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-182300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-478200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-176300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-355500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>877300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-104500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>143400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-114200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-131600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>422400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-281200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>21100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>249900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-90800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-343100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-494200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-57600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>59900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>719300</v>
+        <v>1262400</v>
       </c>
       <c r="E33" s="3">
-        <v>1914500</v>
+        <v>726500</v>
       </c>
       <c r="F33" s="3">
-        <v>1708200</v>
+        <v>1933800</v>
       </c>
       <c r="G33" s="3">
-        <v>1066200</v>
+        <v>1725400</v>
       </c>
       <c r="H33" s="3">
-        <v>1311000</v>
+        <v>1076900</v>
       </c>
       <c r="I33" s="3">
-        <v>1107700</v>
+        <v>1324300</v>
       </c>
       <c r="J33" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="K33" s="3">
         <v>2050700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2587900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2291600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1876100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1631100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1121700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>995900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>579500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>312800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-243300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1006000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>465500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>851400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2245000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>739800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-590600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1309500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>739200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>438900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>294700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>509000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>797800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>188200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>434800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>719300</v>
+        <v>1262400</v>
       </c>
       <c r="E35" s="3">
-        <v>1914500</v>
+        <v>726500</v>
       </c>
       <c r="F35" s="3">
-        <v>1708200</v>
+        <v>1933800</v>
       </c>
       <c r="G35" s="3">
-        <v>1066200</v>
+        <v>1725400</v>
       </c>
       <c r="H35" s="3">
-        <v>1311000</v>
+        <v>1076900</v>
       </c>
       <c r="I35" s="3">
-        <v>1107700</v>
+        <v>1324300</v>
       </c>
       <c r="J35" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="K35" s="3">
         <v>2050700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2587900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2291600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1876100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1631100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1121700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>995900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>579500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>312800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-243300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1006000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>465500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>851400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2245000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>739800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-590600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1309500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>739200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>438900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>294700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>509000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>797800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>188200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>434800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,596 +3611,615 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>559000</v>
+        <v>673500</v>
       </c>
       <c r="E41" s="3">
-        <v>639100</v>
+        <v>564600</v>
       </c>
       <c r="F41" s="3">
-        <v>91100</v>
+        <v>645600</v>
       </c>
       <c r="G41" s="3">
-        <v>88900</v>
+        <v>92000</v>
       </c>
       <c r="H41" s="3">
-        <v>67000</v>
+        <v>89800</v>
       </c>
       <c r="I41" s="3">
-        <v>670500</v>
+        <v>67700</v>
       </c>
       <c r="J41" s="3">
+        <v>677200</v>
+      </c>
+      <c r="K41" s="3">
         <v>411700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>172200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>92400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>550800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>662200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>121500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>120100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>142400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>134200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>182800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>840500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>108400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>145900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>315600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>69300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>76900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>215100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>137000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>114400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>102000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>232200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>37200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>14600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>437300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>382600</v>
+        <v>441700</v>
       </c>
       <c r="F42" s="3">
-        <v>411700</v>
+        <v>386500</v>
       </c>
       <c r="G42" s="3">
-        <v>381900</v>
+        <v>415900</v>
       </c>
       <c r="H42" s="3">
-        <v>352700</v>
+        <v>385700</v>
       </c>
       <c r="I42" s="3">
-        <v>357800</v>
+        <v>356300</v>
       </c>
       <c r="J42" s="3">
+        <v>361400</v>
+      </c>
+      <c r="K42" s="3">
         <v>293700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>271200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>289700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>228800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>226700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>339200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>305200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>236000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>208500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>215800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>174200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>382000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>470100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>433800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>422600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>398800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>478200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>560800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>587900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>664600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>660900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>619200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>626100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>701400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>464800</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2483600</v>
+        <v>2688300</v>
       </c>
       <c r="E43" s="3">
-        <v>2324000</v>
+        <v>2508700</v>
       </c>
       <c r="F43" s="3">
-        <v>3078300</v>
+        <v>2347500</v>
       </c>
       <c r="G43" s="3">
-        <v>2033200</v>
+        <v>3109300</v>
       </c>
       <c r="H43" s="3">
-        <v>2479200</v>
+        <v>2053700</v>
       </c>
       <c r="I43" s="3">
-        <v>2590700</v>
+        <v>2504200</v>
       </c>
       <c r="J43" s="3">
+        <v>2616900</v>
+      </c>
+      <c r="K43" s="3">
         <v>2850900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3706000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3478400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2303300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2352600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2302700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2012700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1933600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1477300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1692700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1195900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1932000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1993900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1684400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1760600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>873700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1436700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1965500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2023500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1239100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1637300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1637100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1755400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1441200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1678300</v>
+        <v>1827800</v>
       </c>
       <c r="E44" s="3">
-        <v>1482300</v>
+        <v>1695300</v>
       </c>
       <c r="F44" s="3">
-        <v>1584300</v>
+        <v>1497200</v>
       </c>
       <c r="G44" s="3">
-        <v>1432700</v>
+        <v>1600300</v>
       </c>
       <c r="H44" s="3">
-        <v>1399200</v>
+        <v>1447200</v>
       </c>
       <c r="I44" s="3">
-        <v>1322700</v>
+        <v>1413300</v>
       </c>
       <c r="J44" s="3">
+        <v>1336000</v>
+      </c>
+      <c r="K44" s="3">
         <v>1338000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1416600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1253300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1146100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>914800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>878000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>786900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>820200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>830300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>859300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>737700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>898200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>954200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>942900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>825200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>726800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>812400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>783700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>744500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>665300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>652700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>691400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>505500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>529300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>473200</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>271100</v>
+        <v>279700</v>
       </c>
       <c r="E45" s="3">
-        <v>395000</v>
+        <v>273800</v>
       </c>
       <c r="F45" s="3">
-        <v>309700</v>
+        <v>399000</v>
       </c>
       <c r="G45" s="3">
-        <v>404500</v>
+        <v>312800</v>
       </c>
       <c r="H45" s="3">
-        <v>223700</v>
+        <v>408500</v>
       </c>
       <c r="I45" s="3">
-        <v>201100</v>
+        <v>226000</v>
       </c>
       <c r="J45" s="3">
+        <v>203200</v>
+      </c>
+      <c r="K45" s="3">
         <v>316300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>296300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>218700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>170300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>257000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>324700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>284900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>242200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>443100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>240900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>335100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>177800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>314200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>306900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>204000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>222200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>258700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>297400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>198700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>189000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>282100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>266400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>398700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>331900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>320400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5429300</v>
+        <v>5469300</v>
       </c>
       <c r="E46" s="3">
-        <v>5223000</v>
+        <v>5484000</v>
       </c>
       <c r="F46" s="3">
-        <v>5475200</v>
+        <v>5275700</v>
       </c>
       <c r="G46" s="3">
-        <v>4341200</v>
+        <v>5530400</v>
       </c>
       <c r="H46" s="3">
-        <v>4522000</v>
+        <v>4385000</v>
       </c>
       <c r="I46" s="3">
-        <v>5142900</v>
+        <v>4567600</v>
       </c>
       <c r="J46" s="3">
+        <v>5194700</v>
+      </c>
+      <c r="K46" s="3">
         <v>5210600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5862400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5332600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4399200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4413300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3966100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3509800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3374300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3093400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3191500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3283400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3498400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3878300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3683600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3281700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2298500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3201100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3744400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3301700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3644400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3066900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3251500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3182000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3331000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2714200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4155,162 +4260,168 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>401400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>429400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>520500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>536000</v>
       </c>
-      <c r="T47" s="3" t="s">
+      <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>508300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>587800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>620100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>641300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>668200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>627900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>641400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>627800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>596900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>557400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>519500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>504700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>496300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>499300</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>49485000</v>
+        <v>50028200</v>
       </c>
       <c r="E48" s="3">
-        <v>49735700</v>
+        <v>49984100</v>
       </c>
       <c r="F48" s="3">
-        <v>49749500</v>
+        <v>50237300</v>
       </c>
       <c r="G48" s="3">
-        <v>50021400</v>
+        <v>50251300</v>
       </c>
       <c r="H48" s="3">
-        <v>49866900</v>
+        <v>50525900</v>
       </c>
       <c r="I48" s="3">
-        <v>49943400</v>
+        <v>50369800</v>
       </c>
       <c r="J48" s="3">
+        <v>50447100</v>
+      </c>
+      <c r="K48" s="3">
         <v>50898800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51560800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51853500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51942200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50911800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49876100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50009900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>54033300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>52633700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>54504900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>55426200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>56456700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>60141800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>57872200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>52626400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>51142200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>49193300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>50788500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>50896900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>50458900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>50437300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>49826300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>40562500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>40940500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>41054200</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>456900</v>
+        <v>405600</v>
       </c>
       <c r="E52" s="3">
-        <v>394300</v>
+        <v>461500</v>
       </c>
       <c r="F52" s="3">
-        <v>389200</v>
+        <v>398200</v>
       </c>
       <c r="G52" s="3">
-        <v>410300</v>
+        <v>393100</v>
       </c>
       <c r="H52" s="3">
-        <v>457700</v>
+        <v>414400</v>
       </c>
       <c r="I52" s="3">
-        <v>403000</v>
+        <v>462300</v>
       </c>
       <c r="J52" s="3">
+        <v>407100</v>
+      </c>
+      <c r="K52" s="3">
         <v>354200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>340700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>464100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>418300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>445900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>418700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>412200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>407800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>276800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>423000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>992700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>445200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>499100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>437000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>392600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>353900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>276100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>290600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>288300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>272400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>256800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>276100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>262000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>287300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>258900</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>55371200</v>
+        <v>55903100</v>
       </c>
       <c r="E54" s="3">
-        <v>55353000</v>
+        <v>55929600</v>
       </c>
       <c r="F54" s="3">
-        <v>55613900</v>
+        <v>55911200</v>
       </c>
       <c r="G54" s="3">
-        <v>54772900</v>
+        <v>56174800</v>
       </c>
       <c r="H54" s="3">
-        <v>54846500</v>
+        <v>55325300</v>
       </c>
       <c r="I54" s="3">
-        <v>55489200</v>
+        <v>55399600</v>
       </c>
       <c r="J54" s="3">
+        <v>56048900</v>
+      </c>
+      <c r="K54" s="3">
         <v>56463600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>57763900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57650100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>56759700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>55771100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>54261000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54333300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58244800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>56524400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58655400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>59702200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>60908600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>65107000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>62612900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>56942000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>54462800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>53298400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>55464800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>55114800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>54972600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>54318400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>53873400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>44511200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>45055200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>44526600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>829300</v>
+        <v>1363300</v>
       </c>
       <c r="E57" s="3">
-        <v>1033400</v>
+        <v>837700</v>
       </c>
       <c r="F57" s="3">
-        <v>900000</v>
+        <v>1043800</v>
       </c>
       <c r="G57" s="3">
-        <v>816200</v>
+        <v>909100</v>
       </c>
       <c r="H57" s="3">
-        <v>889100</v>
+        <v>824400</v>
       </c>
       <c r="I57" s="3">
-        <v>977300</v>
+        <v>898100</v>
       </c>
       <c r="J57" s="3">
+        <v>987100</v>
+      </c>
+      <c r="K57" s="3">
         <v>921900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>849800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>712400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>594500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>732600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>566300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>548900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>516100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>632500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>475600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>629400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>636200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>548800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>732800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>599700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>592900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>732500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>730200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>705400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>576800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>590900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>488200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>415600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>457100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>480900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1526000</v>
+        <v>806800</v>
       </c>
       <c r="E58" s="3">
-        <v>931400</v>
+        <v>1541400</v>
       </c>
       <c r="F58" s="3">
-        <v>1326300</v>
+        <v>940700</v>
       </c>
       <c r="G58" s="3">
-        <v>1855400</v>
+        <v>1339700</v>
       </c>
       <c r="H58" s="3">
-        <v>900700</v>
+        <v>1874100</v>
       </c>
       <c r="I58" s="3">
-        <v>472200</v>
+        <v>909800</v>
       </c>
       <c r="J58" s="3">
+        <v>477000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1138300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1094400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2162300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>877300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>878500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1797900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1416100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1185400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>779700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1604800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2373100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2045900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3548300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3330700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1445700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>868400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>363300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>621800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>484800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1396900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1395400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1448200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2403800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1392000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1611700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3828200</v>
+        <v>4045700</v>
       </c>
       <c r="E59" s="3">
-        <v>3453600</v>
+        <v>3866800</v>
       </c>
       <c r="F59" s="3">
-        <v>3786600</v>
+        <v>3488400</v>
       </c>
       <c r="G59" s="3">
-        <v>3573100</v>
+        <v>3824800</v>
       </c>
       <c r="H59" s="3">
-        <v>3678800</v>
+        <v>3609100</v>
       </c>
       <c r="I59" s="3">
-        <v>4855000</v>
+        <v>3715900</v>
       </c>
       <c r="J59" s="3">
+        <v>4904000</v>
+      </c>
+      <c r="K59" s="3">
         <v>4589700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4940900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4272100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4023100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3229600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2742500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2373600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2227600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1774000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1778200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1944600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2492600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2415000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2201400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2274000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2163000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2387900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2305000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2067900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2685900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2323400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2111300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1827600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2062700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1857600</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6183500</v>
+        <v>6215700</v>
       </c>
       <c r="E60" s="3">
-        <v>5418300</v>
+        <v>6245900</v>
       </c>
       <c r="F60" s="3">
-        <v>6013000</v>
+        <v>5473000</v>
       </c>
       <c r="G60" s="3">
-        <v>6244700</v>
+        <v>6073600</v>
       </c>
       <c r="H60" s="3">
-        <v>5468600</v>
+        <v>6307700</v>
       </c>
       <c r="I60" s="3">
-        <v>6304500</v>
+        <v>5523800</v>
       </c>
       <c r="J60" s="3">
+        <v>6368100</v>
+      </c>
+      <c r="K60" s="3">
         <v>6649900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6885200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7146800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5495000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4840700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5106700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4338600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3929100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3186200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3858600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4947000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5174700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6512200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6264900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4319500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3624300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3483800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3657100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3258100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4659500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4309700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4047800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3911800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3950200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7638100</v>
+        <v>7803500</v>
       </c>
       <c r="E61" s="3">
-        <v>8071700</v>
+        <v>7715200</v>
       </c>
       <c r="F61" s="3">
-        <v>8241500</v>
+        <v>8153200</v>
       </c>
       <c r="G61" s="3">
-        <v>8113300</v>
+        <v>8324700</v>
       </c>
       <c r="H61" s="3">
-        <v>8980500</v>
+        <v>8195100</v>
       </c>
       <c r="I61" s="3">
-        <v>8990700</v>
+        <v>9071100</v>
       </c>
       <c r="J61" s="3">
+        <v>9081400</v>
+      </c>
+      <c r="K61" s="3">
         <v>9413400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9376300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9264700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11174300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12736300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12630300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14248200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16721500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>17244000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17783800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16800500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15905300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16634100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16797700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15936000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14827600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13976400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15485600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16060000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>15316600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>15662600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15874000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10121400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11518100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11672500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12757700</v>
+        <v>12830400</v>
       </c>
       <c r="E62" s="3">
-        <v>12834900</v>
+        <v>12886300</v>
       </c>
       <c r="F62" s="3">
-        <v>12475600</v>
+        <v>12964400</v>
       </c>
       <c r="G62" s="3">
-        <v>12252600</v>
+        <v>12601500</v>
       </c>
       <c r="H62" s="3">
-        <v>12278100</v>
+        <v>12376200</v>
       </c>
       <c r="I62" s="3">
-        <v>12373600</v>
+        <v>12402000</v>
       </c>
       <c r="J62" s="3">
+        <v>12498400</v>
+      </c>
+      <c r="K62" s="3">
         <v>12606100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12430600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12794900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12737900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11878500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11784900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11713300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12540200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11434400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11640000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11852700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12547200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13114700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12370300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11846000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11675900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11571800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11923400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11687800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11440000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11023200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10891500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9479200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9446200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9203400</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>26579300</v>
+        <v>26849600</v>
       </c>
       <c r="E66" s="3">
-        <v>26325000</v>
+        <v>26847400</v>
       </c>
       <c r="F66" s="3">
-        <v>26730200</v>
+        <v>26590500</v>
       </c>
       <c r="G66" s="3">
-        <v>26610700</v>
+        <v>26999800</v>
       </c>
       <c r="H66" s="3">
-        <v>26727300</v>
+        <v>26879100</v>
       </c>
       <c r="I66" s="3">
-        <v>27668800</v>
+        <v>26996800</v>
       </c>
       <c r="J66" s="3">
+        <v>27947900</v>
+      </c>
+      <c r="K66" s="3">
         <v>28669400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28692000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29206400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29407100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29455500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29521800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30300000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>33190800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31864600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33282400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33600200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33627200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>36261000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>35432900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>32101500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30127700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>29032000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>31066100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>31005900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>31416100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>30995600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>30813300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>24247600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24876100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24826100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>20604200</v>
+        <v>20734000</v>
       </c>
       <c r="E72" s="3">
-        <v>21096100</v>
+        <v>20812000</v>
       </c>
       <c r="F72" s="3">
-        <v>20967900</v>
+        <v>21308900</v>
       </c>
       <c r="G72" s="3">
-        <v>20356500</v>
+        <v>21179400</v>
       </c>
       <c r="H72" s="3">
-        <v>20319300</v>
+        <v>20561800</v>
       </c>
       <c r="I72" s="3">
-        <v>20166200</v>
+        <v>20524200</v>
       </c>
       <c r="J72" s="3">
+        <v>20369600</v>
+      </c>
+      <c r="K72" s="3">
         <v>20220900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21388600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20739000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19825400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18986600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17639300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17044100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17615200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17264700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17746100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18382500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19822300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>21042900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19767600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17591900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17146600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17464500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17309700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17152300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16828100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16783400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16523700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16490100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16536900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16314900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>28791900</v>
+        <v>29053500</v>
       </c>
       <c r="E76" s="3">
-        <v>29028000</v>
+        <v>29082200</v>
       </c>
       <c r="F76" s="3">
-        <v>28883700</v>
+        <v>29320700</v>
       </c>
       <c r="G76" s="3">
-        <v>28162200</v>
+        <v>29175000</v>
       </c>
       <c r="H76" s="3">
-        <v>28119200</v>
+        <v>28446200</v>
       </c>
       <c r="I76" s="3">
-        <v>27820400</v>
+        <v>28402800</v>
       </c>
       <c r="J76" s="3">
+        <v>28101000</v>
+      </c>
+      <c r="K76" s="3">
         <v>27794200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29071900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28443700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27352600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26315500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24739200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24033300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25054000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24659700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25373000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>26102000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>27281400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>28846000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>27180000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24840600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24335100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24266400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24398700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24108900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>23556500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>23322800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23060100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20263600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20179100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>19700500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>719300</v>
+        <v>1262400</v>
       </c>
       <c r="E81" s="3">
-        <v>1914500</v>
+        <v>726500</v>
       </c>
       <c r="F81" s="3">
-        <v>1708200</v>
+        <v>1933800</v>
       </c>
       <c r="G81" s="3">
-        <v>1066200</v>
+        <v>1725400</v>
       </c>
       <c r="H81" s="3">
-        <v>1311000</v>
+        <v>1076900</v>
       </c>
       <c r="I81" s="3">
-        <v>1107700</v>
+        <v>1324300</v>
       </c>
       <c r="J81" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="K81" s="3">
         <v>2050700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2587900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2291600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1876100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1631100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1121700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>995900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>579500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>312800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-243300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1006000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>465500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>851400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2245000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>739800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-590600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1309500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>739200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>438900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>294700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>509000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>797800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>188200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>434800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1117200</v>
+        <v>1213800</v>
       </c>
       <c r="E83" s="3">
-        <v>1502000</v>
+        <v>1128500</v>
       </c>
       <c r="F83" s="3">
-        <v>1120100</v>
+        <v>1517100</v>
       </c>
       <c r="G83" s="3">
-        <v>1018100</v>
+        <v>1131400</v>
       </c>
       <c r="H83" s="3">
-        <v>1033400</v>
+        <v>1028300</v>
       </c>
       <c r="I83" s="3">
-        <v>2280300</v>
+        <v>1043800</v>
       </c>
       <c r="J83" s="3">
+        <v>2303300</v>
+      </c>
+      <c r="K83" s="3">
         <v>1059600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1007200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1039800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1090600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1068100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1003800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1027700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1249600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1122400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1101000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1227300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1208500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1182200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1036500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>972300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1010700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>949100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>956000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>946300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1046400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>945900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>900500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>997900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>959500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2090100</v>
+        <v>3006300</v>
       </c>
       <c r="E89" s="3">
-        <v>3509000</v>
+        <v>2111200</v>
       </c>
       <c r="F89" s="3">
-        <v>2549200</v>
+        <v>3544400</v>
       </c>
       <c r="G89" s="3">
-        <v>2000400</v>
+        <v>2574900</v>
       </c>
       <c r="H89" s="3">
-        <v>943700</v>
+        <v>2020600</v>
       </c>
       <c r="I89" s="3">
-        <v>3311500</v>
+        <v>953300</v>
       </c>
       <c r="J89" s="3">
+        <v>3344900</v>
+      </c>
+      <c r="K89" s="3">
         <v>4444000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4357100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2108300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3488600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3177800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2126300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1834100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>982700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1586900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-275400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1353700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1913300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2087500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2268800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>766700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1063200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2646600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1967000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1858600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1070200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1876900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1213800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1283700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>964100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1621000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1113000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-975000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1108000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1569000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1257000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1135000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1388000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1554000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-957000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>2200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>1416700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1401400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5500</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-2500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-29300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>72300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-215800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-42200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-618400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-493200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-816600</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1014400</v>
+        <v>-747200</v>
       </c>
       <c r="E94" s="3">
-        <v>-689400</v>
+        <v>-1024700</v>
       </c>
       <c r="F94" s="3">
-        <v>-873800</v>
+        <v>-696400</v>
       </c>
       <c r="G94" s="3">
-        <v>-1136900</v>
+        <v>-882600</v>
       </c>
       <c r="H94" s="3">
-        <v>-840300</v>
+        <v>-1148300</v>
       </c>
       <c r="I94" s="3">
-        <v>-919700</v>
+        <v>-848700</v>
       </c>
       <c r="J94" s="3">
+        <v>-929000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-822800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-993900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-924500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1195700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-534100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-520000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-468600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-482800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-492900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-543800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-674100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-665800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-752800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3540000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-792100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-793100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-919300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-856700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1030600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-799300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1458700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6656200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-863500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-411000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-658400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,106 +8585,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-784100</v>
+        <v>-828100</v>
       </c>
       <c r="E96" s="3">
-        <v>-714200</v>
+        <v>-792100</v>
       </c>
       <c r="F96" s="3">
-        <v>-717100</v>
+        <v>-721400</v>
       </c>
       <c r="G96" s="3">
-        <v>-720700</v>
+        <v>-724300</v>
       </c>
       <c r="H96" s="3">
-        <v>-683600</v>
+        <v>-728000</v>
       </c>
       <c r="I96" s="3">
-        <v>-607800</v>
+        <v>-690500</v>
       </c>
       <c r="J96" s="3">
+        <v>-613900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1845200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-643700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-509200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-408700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-413300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-402800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-363800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-388400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-384900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-393900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-348400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-346200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-370600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-356100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-310200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-309000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-297200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-309400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-252900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-249300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-248600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-227700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-195100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-193600</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1155800</v>
+        <v>-2150200</v>
       </c>
       <c r="E100" s="3">
-        <v>-2271500</v>
+        <v>-1167500</v>
       </c>
       <c r="F100" s="3">
-        <v>-1673200</v>
+        <v>-2294500</v>
       </c>
       <c r="G100" s="3">
-        <v>-841700</v>
+        <v>-1690100</v>
       </c>
       <c r="H100" s="3">
-        <v>-706900</v>
+        <v>-850200</v>
       </c>
       <c r="I100" s="3">
-        <v>-2133100</v>
+        <v>-714000</v>
       </c>
       <c r="J100" s="3">
+        <v>-2154600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3379300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3283300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1641300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2403900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2105900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1604800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1378500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-492900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1138500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>161700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>51800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1276300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1518800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1515500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>16900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-418600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1644500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1087800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-816800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-401100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-223300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>5465500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-418700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-554700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-80200</v>
+        <v>108900</v>
       </c>
       <c r="E102" s="3">
-        <v>548000</v>
+        <v>-81000</v>
       </c>
       <c r="F102" s="3">
+        <v>553600</v>
+      </c>
+      <c r="G102" s="3">
         <v>2200</v>
       </c>
-      <c r="G102" s="3">
-        <v>21900</v>
-      </c>
       <c r="H102" s="3">
-        <v>-603400</v>
+        <v>22100</v>
       </c>
       <c r="I102" s="3">
-        <v>258700</v>
+        <v>-609500</v>
       </c>
       <c r="J102" s="3">
+        <v>261300</v>
+      </c>
+      <c r="K102" s="3">
         <v>241900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>79800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-457400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-111100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>537800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-44500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-657600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>731400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-28800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-184000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>244300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-148400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>82800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>22600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-130200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>195000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>23100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>CNQ</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6662500</v>
+        <v>6582800</v>
       </c>
       <c r="E8" s="3">
-        <v>6068500</v>
+        <v>6613100</v>
       </c>
       <c r="F8" s="3">
-        <v>7032100</v>
+        <v>6088100</v>
       </c>
       <c r="G8" s="3">
-        <v>7283800</v>
+        <v>7233700</v>
       </c>
       <c r="H8" s="3">
-        <v>5807900</v>
+        <v>7314700</v>
       </c>
       <c r="I8" s="3">
-        <v>6352600</v>
+        <v>5958300</v>
       </c>
       <c r="J8" s="3">
+        <v>6378400</v>
+      </c>
+      <c r="K8" s="3">
         <v>7132200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7620600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8479900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7890200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6820900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5711800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4719000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4779000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3882700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3452900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2253000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3531300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4600800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5106900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4410800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4040000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2817600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4286700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4480600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4120800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3872100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3323600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2910600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2797900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2656500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1793800</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3411100</v>
+        <v>3178500</v>
       </c>
       <c r="E9" s="3">
-        <v>3269100</v>
+        <v>3385800</v>
       </c>
       <c r="F9" s="3">
-        <v>3242600</v>
+        <v>3279600</v>
       </c>
       <c r="G9" s="3">
-        <v>3193200</v>
+        <v>3335500</v>
       </c>
       <c r="H9" s="3">
-        <v>3342700</v>
+        <v>3206800</v>
       </c>
       <c r="I9" s="3">
-        <v>3311000</v>
+        <v>3429200</v>
       </c>
       <c r="J9" s="3">
+        <v>3324400</v>
+      </c>
+      <c r="K9" s="3">
         <v>3614300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3141700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3672000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3321800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2912600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2428100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2354100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2378700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2281800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1951100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1701300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2445200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2388900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2332900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2005500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1977700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1895900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1901000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2080700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2094300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2102400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1830800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1529400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1339800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1267600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1104700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3251400</v>
+        <v>3404300</v>
       </c>
       <c r="E10" s="3">
-        <v>2799400</v>
+        <v>3227300</v>
       </c>
       <c r="F10" s="3">
-        <v>3789500</v>
+        <v>2808500</v>
       </c>
       <c r="G10" s="3">
-        <v>4090600</v>
+        <v>3898100</v>
       </c>
       <c r="H10" s="3">
-        <v>2465200</v>
+        <v>4107900</v>
       </c>
       <c r="I10" s="3">
-        <v>3041600</v>
+        <v>2529100</v>
       </c>
       <c r="J10" s="3">
+        <v>3053900</v>
+      </c>
+      <c r="K10" s="3">
         <v>3517900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4479000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4807900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4568400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3908400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3283700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2364900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2400400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1600900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1501800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>551700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1086100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2211900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2774000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2405200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2062300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>921700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2385700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2399900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2026500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1769700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1492900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1381300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1458100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1389000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>689100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,58 +1358,61 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>18300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+        <v>-59800</v>
+      </c>
+      <c r="G14" s="3">
+        <v>25700</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-34000</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-354100</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>-167900</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1406,8 +1426,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1442,109 +1462,115 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1213800</v>
+        <v>1182900</v>
       </c>
       <c r="E15" s="3">
-        <v>1128500</v>
+        <v>1204800</v>
       </c>
       <c r="F15" s="3">
-        <v>1517100</v>
+        <v>1132100</v>
       </c>
       <c r="G15" s="3">
-        <v>1131400</v>
+        <v>1560600</v>
       </c>
       <c r="H15" s="3">
-        <v>1028300</v>
+        <v>1136200</v>
       </c>
       <c r="I15" s="3">
-        <v>1043800</v>
+        <v>1055000</v>
       </c>
       <c r="J15" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="K15" s="3">
         <v>2303300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1059600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1007200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1039800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1090600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1068100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1003800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1027700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1249600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1122400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1101000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1227300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1208500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1182200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1036500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>972300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1010700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>949100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>956000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>946300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1046400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>945900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>900500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>997900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>959500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4778100</v>
+        <v>4493100</v>
       </c>
       <c r="E17" s="3">
-        <v>4778100</v>
+        <v>4744800</v>
       </c>
       <c r="F17" s="3">
-        <v>4956200</v>
+        <v>4795700</v>
       </c>
       <c r="G17" s="3">
-        <v>4691200</v>
+        <v>5103600</v>
       </c>
       <c r="H17" s="3">
-        <v>4577100</v>
+        <v>4711100</v>
       </c>
       <c r="I17" s="3">
-        <v>4549200</v>
+        <v>4693400</v>
       </c>
       <c r="J17" s="3">
+        <v>4582400</v>
+      </c>
+      <c r="K17" s="3">
         <v>6292300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4326600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4760600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4885500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4250400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3283700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3553200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3601600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3580900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3176200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2929400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3623100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3836000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3641200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3139600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3085400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2898200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2878400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3261100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3069900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3316900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2948600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2437300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2453000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2352300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2186400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1884400</v>
+        <v>2089600</v>
       </c>
       <c r="E18" s="3">
-        <v>1290400</v>
+        <v>1868300</v>
       </c>
       <c r="F18" s="3">
-        <v>2075800</v>
+        <v>1292400</v>
       </c>
       <c r="G18" s="3">
-        <v>2592600</v>
+        <v>2130000</v>
       </c>
       <c r="H18" s="3">
-        <v>1230800</v>
+        <v>2603600</v>
       </c>
       <c r="I18" s="3">
-        <v>1803500</v>
+        <v>1264900</v>
       </c>
       <c r="J18" s="3">
+        <v>1796000</v>
+      </c>
+      <c r="K18" s="3">
         <v>839900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3294000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3719300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3004700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2570500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2428100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1165800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1177400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>301800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>276800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-676400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-91800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>764900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1465800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1271200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>954600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-80700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1408300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1219500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1050900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>555200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>375100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>473300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>344900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>304200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-392600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-107500</v>
+        <v>-103600</v>
       </c>
       <c r="E20" s="3">
-        <v>-152400</v>
+        <v>86200</v>
       </c>
       <c r="F20" s="3">
-        <v>228200</v>
+        <v>210500</v>
       </c>
       <c r="G20" s="3">
-        <v>-138400</v>
+        <v>-224100</v>
       </c>
       <c r="H20" s="3">
-        <v>204600</v>
+        <v>175900</v>
       </c>
       <c r="I20" s="3">
-        <v>-5900</v>
+        <v>-171400</v>
       </c>
       <c r="J20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="K20" s="3">
         <v>284100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-440900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-252000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>128600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>104400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-215600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>406400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>182300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>478200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>176300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>355500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-877300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>104500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-143400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>114200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>131600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-422400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>281200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-21100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-249900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>90800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>343100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>494200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>14600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>57600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-59900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2990800</v>
+        <v>3376100</v>
       </c>
       <c r="E21" s="3">
-        <v>2266500</v>
+        <v>2986900</v>
       </c>
       <c r="F21" s="3">
-        <v>3821100</v>
+        <v>2214000</v>
       </c>
       <c r="G21" s="3">
-        <v>3585600</v>
+        <v>3914800</v>
       </c>
       <c r="H21" s="3">
-        <v>2463800</v>
+        <v>3563900</v>
       </c>
       <c r="I21" s="3">
-        <v>2841400</v>
+        <v>2491300</v>
       </c>
       <c r="J21" s="3">
+        <v>2853600</v>
+      </c>
+      <c r="K21" s="3">
         <v>3427300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3912700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4474600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4173100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3765500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3280700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2576100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2387300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2029500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1575400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>780000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>258200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2077800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2504600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2421900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2058500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>507600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2638600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2154500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1747200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1692300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1664100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1868000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1357500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1321400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>116300</v>
+        <v>117700</v>
       </c>
       <c r="E22" s="3">
-        <v>101600</v>
+        <v>120600</v>
       </c>
       <c r="F22" s="3">
-        <v>126600</v>
+        <v>118200</v>
       </c>
       <c r="G22" s="3">
-        <v>137700</v>
+        <v>128700</v>
       </c>
       <c r="H22" s="3">
-        <v>131000</v>
+        <v>135300</v>
       </c>
       <c r="I22" s="3">
-        <v>113400</v>
+        <v>132200</v>
       </c>
       <c r="J22" s="3">
+        <v>120500</v>
+      </c>
+      <c r="K22" s="3">
         <v>145000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>109300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>118200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>120500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>150300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>131900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>128000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>133800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>192700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>133400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>156200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>161700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>228400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>191500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>156200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>147000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>181100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>130800</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>143000</v>
       </c>
       <c r="AC22" s="3">
         <v>143000</v>
       </c>
       <c r="AD22" s="3">
+        <v>143000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>198000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>136200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>107900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>102900</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1660700</v>
+        <v>2079300</v>
       </c>
       <c r="E23" s="3">
-        <v>1036400</v>
+        <v>1648300</v>
       </c>
       <c r="F23" s="3">
-        <v>2177400</v>
+        <v>1039800</v>
       </c>
       <c r="G23" s="3">
-        <v>2316500</v>
+        <v>2239800</v>
       </c>
       <c r="H23" s="3">
-        <v>1304400</v>
+        <v>2326400</v>
       </c>
       <c r="I23" s="3">
-        <v>1684200</v>
+        <v>1338200</v>
       </c>
       <c r="J23" s="3">
+        <v>1691000</v>
+      </c>
+      <c r="K23" s="3">
         <v>979000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2743800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3349100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3012900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2524600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2080700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1444300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1225900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>587300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>319700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-477100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1130800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>640900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1130800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1229200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>939200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-684200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1558800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1055400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>657900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>448000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>582000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>859600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>256600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>361800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-452500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>398200</v>
+        <v>401900</v>
       </c>
       <c r="E24" s="3">
-        <v>309900</v>
+        <v>395300</v>
       </c>
       <c r="F24" s="3">
-        <v>243700</v>
+        <v>310900</v>
       </c>
       <c r="G24" s="3">
-        <v>591100</v>
+        <v>250600</v>
       </c>
       <c r="H24" s="3">
-        <v>227500</v>
+        <v>593600</v>
       </c>
       <c r="I24" s="3">
-        <v>360000</v>
+        <v>233300</v>
       </c>
       <c r="J24" s="3">
+        <v>361400</v>
+      </c>
+      <c r="K24" s="3">
         <v>-139900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>693100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>761200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>721300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>648600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>449600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>322600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>230000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-233900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-124800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>175400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>279400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1015900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>199400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-93600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>249300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>316200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>219100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>153300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>72900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>61800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>68400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-73000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1262400</v>
+        <v>1677300</v>
       </c>
       <c r="E26" s="3">
-        <v>726500</v>
+        <v>1253100</v>
       </c>
       <c r="F26" s="3">
-        <v>1933800</v>
+        <v>728900</v>
       </c>
       <c r="G26" s="3">
-        <v>1725400</v>
+        <v>1989200</v>
       </c>
       <c r="H26" s="3">
-        <v>1076900</v>
+        <v>1732800</v>
       </c>
       <c r="I26" s="3">
-        <v>1324300</v>
+        <v>1104800</v>
       </c>
       <c r="J26" s="3">
+        <v>1329600</v>
+      </c>
+      <c r="K26" s="3">
         <v>1118900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2050700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2587900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2291600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1876100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1631100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1121700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>995900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>579500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>312800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-243300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1006000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>465500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>851400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2245000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>739800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-590600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1309500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>739200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>438900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>294700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>509000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>797800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>188200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>434800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1262400</v>
+        <v>1677300</v>
       </c>
       <c r="E27" s="3">
-        <v>726500</v>
+        <v>1253100</v>
       </c>
       <c r="F27" s="3">
-        <v>1933800</v>
+        <v>728900</v>
       </c>
       <c r="G27" s="3">
-        <v>1725400</v>
+        <v>1989200</v>
       </c>
       <c r="H27" s="3">
-        <v>1076900</v>
+        <v>1732800</v>
       </c>
       <c r="I27" s="3">
-        <v>1324300</v>
+        <v>1104800</v>
       </c>
       <c r="J27" s="3">
+        <v>1329600</v>
+      </c>
+      <c r="K27" s="3">
         <v>1118900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2050700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2587900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2291600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1876100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1631100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1121700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>995900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>579500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>312800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-243300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1006000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>465500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>851400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2245000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>739800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-590600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1309500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>739200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>438900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>294700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>509000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>797800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>188200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>434800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>107500</v>
+        <v>103600</v>
       </c>
       <c r="E32" s="3">
-        <v>152400</v>
+        <v>-86200</v>
       </c>
       <c r="F32" s="3">
-        <v>-228200</v>
+        <v>-210500</v>
       </c>
       <c r="G32" s="3">
-        <v>138400</v>
+        <v>224100</v>
       </c>
       <c r="H32" s="3">
-        <v>-204600</v>
+        <v>-175900</v>
       </c>
       <c r="I32" s="3">
-        <v>5900</v>
+        <v>171400</v>
       </c>
       <c r="J32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-284100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>440900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>252000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-128600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-104400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>215600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-406400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-182300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-478200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-176300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-355500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>877300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-104500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>143400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-114200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-131600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>422400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-281200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>21100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>249900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-90800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-343100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-494200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-57600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>59900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1262400</v>
+        <v>1677300</v>
       </c>
       <c r="E33" s="3">
-        <v>726500</v>
+        <v>1253100</v>
       </c>
       <c r="F33" s="3">
-        <v>1933800</v>
+        <v>728900</v>
       </c>
       <c r="G33" s="3">
-        <v>1725400</v>
+        <v>1989200</v>
       </c>
       <c r="H33" s="3">
-        <v>1076900</v>
+        <v>1732800</v>
       </c>
       <c r="I33" s="3">
-        <v>1324300</v>
+        <v>1104800</v>
       </c>
       <c r="J33" s="3">
+        <v>1329600</v>
+      </c>
+      <c r="K33" s="3">
         <v>1118900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2050700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2587900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2291600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1876100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1631100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1121700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>995900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>579500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>312800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-243300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1006000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>465500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>851400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2245000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>739800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-590600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1309500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>739200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>438900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>294700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>509000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>797800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>188200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>434800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1262400</v>
+        <v>1677300</v>
       </c>
       <c r="E35" s="3">
-        <v>726500</v>
+        <v>1253100</v>
       </c>
       <c r="F35" s="3">
-        <v>1933800</v>
+        <v>728900</v>
       </c>
       <c r="G35" s="3">
-        <v>1725400</v>
+        <v>1989200</v>
       </c>
       <c r="H35" s="3">
-        <v>1076900</v>
+        <v>1732800</v>
       </c>
       <c r="I35" s="3">
-        <v>1324300</v>
+        <v>1104800</v>
       </c>
       <c r="J35" s="3">
+        <v>1329600</v>
+      </c>
+      <c r="K35" s="3">
         <v>1118900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2050700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2587900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2291600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1876100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1631100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1121700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>995900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>579500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>312800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-243300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1006000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>465500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>851400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2245000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>739800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-590600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1309500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>739200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>438900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>294700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>509000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>797800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>188200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>434800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>673500</v>
+        <v>533700</v>
       </c>
       <c r="E41" s="3">
-        <v>564600</v>
+        <v>668500</v>
       </c>
       <c r="F41" s="3">
-        <v>645600</v>
+        <v>566400</v>
       </c>
       <c r="G41" s="3">
-        <v>92000</v>
+        <v>664100</v>
       </c>
       <c r="H41" s="3">
-        <v>89800</v>
+        <v>92400</v>
       </c>
       <c r="I41" s="3">
-        <v>67700</v>
+        <v>92100</v>
       </c>
       <c r="J41" s="3">
+        <v>68000</v>
+      </c>
+      <c r="K41" s="3">
         <v>677200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>411700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>172200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>92400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>550800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>662200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>121500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>120100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>142400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>134200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>182800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>840500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>108400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>145900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>315600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>69300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>76900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>215100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>137000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>114400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>102000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>232200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>37200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>14600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,527 +3812,542 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>441700</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>386500</v>
+        <v>443100</v>
       </c>
       <c r="G42" s="3">
-        <v>415900</v>
+        <v>406600</v>
       </c>
       <c r="H42" s="3">
-        <v>385700</v>
+        <v>417700</v>
       </c>
       <c r="I42" s="3">
-        <v>356300</v>
+        <v>395700</v>
       </c>
       <c r="J42" s="3">
+        <v>357700</v>
+      </c>
+      <c r="K42" s="3">
         <v>361400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>293700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>271200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>289700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>228800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>226700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>339200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>305200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>236000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>208500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>215800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>174200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>382000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>470100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>433800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>422600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>398800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>478200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>560800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>587900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>664600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>660900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>619200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>626100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>701400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>464800</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2688300</v>
+        <v>2294700</v>
       </c>
       <c r="E43" s="3">
-        <v>2508700</v>
+        <v>2668300</v>
       </c>
       <c r="F43" s="3">
-        <v>2347500</v>
+        <v>2516800</v>
       </c>
       <c r="G43" s="3">
-        <v>3109300</v>
+        <v>2414800</v>
       </c>
       <c r="H43" s="3">
-        <v>2053700</v>
+        <v>3122500</v>
       </c>
       <c r="I43" s="3">
-        <v>2504200</v>
+        <v>2106900</v>
       </c>
       <c r="J43" s="3">
+        <v>2514400</v>
+      </c>
+      <c r="K43" s="3">
         <v>2616900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2850900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3706000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3478400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2303300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2352600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2302700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2012700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1933600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1477300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1692700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1195900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1932000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1993900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1684400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1760600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>873700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1436700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1965500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2023500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1239100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1637300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1637100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1755400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1441200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1827800</v>
+        <v>1873500</v>
       </c>
       <c r="E44" s="3">
-        <v>1695300</v>
+        <v>1814200</v>
       </c>
       <c r="F44" s="3">
-        <v>1497200</v>
+        <v>1700700</v>
       </c>
       <c r="G44" s="3">
-        <v>1600300</v>
+        <v>1540200</v>
       </c>
       <c r="H44" s="3">
-        <v>1447200</v>
+        <v>1607100</v>
       </c>
       <c r="I44" s="3">
-        <v>1413300</v>
+        <v>1484700</v>
       </c>
       <c r="J44" s="3">
+        <v>1419100</v>
+      </c>
+      <c r="K44" s="3">
         <v>1336000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1338000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1416600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1253300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1146100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>914800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>878000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>786900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>820200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>830300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>859300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>737700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>898200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>954200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>942900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>825200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>726800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>812400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>783700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>744500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>665300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>652700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>691400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>505500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>529300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>473200</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>279700</v>
+        <v>49600</v>
       </c>
       <c r="E45" s="3">
-        <v>273800</v>
+        <v>57700</v>
       </c>
       <c r="F45" s="3">
-        <v>399000</v>
+        <v>51000</v>
       </c>
       <c r="G45" s="3">
-        <v>312800</v>
+        <v>44700</v>
       </c>
       <c r="H45" s="3">
-        <v>408500</v>
+        <v>37700</v>
       </c>
       <c r="I45" s="3">
-        <v>226000</v>
+        <v>35500</v>
       </c>
       <c r="J45" s="3">
+        <v>48000</v>
+      </c>
+      <c r="K45" s="3">
         <v>203200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>316300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>296300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>218700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>170300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>257000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>324700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>284900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>242200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>443100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>240900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>335100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>177800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>314200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>306900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>204000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>222200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>258700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>297400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>198700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>189000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>282100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>266400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>398700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>331900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>320400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5469300</v>
+        <v>5015000</v>
       </c>
       <c r="E46" s="3">
-        <v>5484000</v>
+        <v>5428700</v>
       </c>
       <c r="F46" s="3">
-        <v>5275700</v>
+        <v>5501700</v>
       </c>
       <c r="G46" s="3">
-        <v>5530400</v>
+        <v>5427000</v>
       </c>
       <c r="H46" s="3">
-        <v>4385000</v>
+        <v>5553900</v>
       </c>
       <c r="I46" s="3">
-        <v>4567600</v>
+        <v>4498600</v>
       </c>
       <c r="J46" s="3">
+        <v>4586100</v>
+      </c>
+      <c r="K46" s="3">
         <v>5194700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5210600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5862400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5332600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4399200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4413300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3966100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3509800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3374300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3093400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3191500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3283400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3498400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3878300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3683600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3281700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2298500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3201100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3744400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3301700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3644400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3066900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3251500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3182000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3331000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2714200</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4263,165 +4368,171 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>401400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>429400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>520500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>536000</v>
       </c>
-      <c r="U47" s="3" t="s">
+      <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>508300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>587800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>620100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>641300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>668200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>627900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>641400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>627800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>596900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>557400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>519500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>504700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>496300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>499300</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>50028200</v>
+        <v>50129900</v>
       </c>
       <c r="E48" s="3">
-        <v>49984100</v>
+        <v>49657000</v>
       </c>
       <c r="F48" s="3">
-        <v>50237300</v>
+        <v>50145500</v>
       </c>
       <c r="G48" s="3">
-        <v>50251300</v>
+        <v>51677600</v>
       </c>
       <c r="H48" s="3">
-        <v>50525900</v>
+        <v>50464600</v>
       </c>
       <c r="I48" s="3">
-        <v>50369800</v>
+        <v>51834300</v>
       </c>
       <c r="J48" s="3">
+        <v>50573900</v>
+      </c>
+      <c r="K48" s="3">
         <v>50447100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50898800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51560800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51853500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51942200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50911800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49876100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50009900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>54033300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>52633700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>54504900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>55426200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>56456700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>60141800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>57872200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>52626400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>51142200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>49193300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>50788500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>50896900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>50458900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>50437300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>49826300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>40562500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>40940500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>41054200</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>405600</v>
+        <v>430800</v>
       </c>
       <c r="E52" s="3">
-        <v>461500</v>
+        <v>402600</v>
       </c>
       <c r="F52" s="3">
-        <v>398200</v>
+        <v>463000</v>
       </c>
       <c r="G52" s="3">
-        <v>393100</v>
+        <v>408900</v>
       </c>
       <c r="H52" s="3">
-        <v>414400</v>
+        <v>394800</v>
       </c>
       <c r="I52" s="3">
-        <v>462300</v>
+        <v>425200</v>
       </c>
       <c r="J52" s="3">
+        <v>464200</v>
+      </c>
+      <c r="K52" s="3">
         <v>407100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>354200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>340700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>464100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>418300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>445900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>418700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>412200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>407800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>276800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>423000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>992700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>445200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>499100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>437000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>392600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>353900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>276100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>290600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>288300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>272400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>256800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>276100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>262000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>287300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>258900</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>55903100</v>
+        <v>55576400</v>
       </c>
       <c r="E54" s="3">
-        <v>55929600</v>
+        <v>55488300</v>
       </c>
       <c r="F54" s="3">
-        <v>55911200</v>
+        <v>56110200</v>
       </c>
       <c r="G54" s="3">
-        <v>56174800</v>
+        <v>57514200</v>
       </c>
       <c r="H54" s="3">
-        <v>55325300</v>
+        <v>56413200</v>
       </c>
       <c r="I54" s="3">
-        <v>55399600</v>
+        <v>56758000</v>
       </c>
       <c r="J54" s="3">
+        <v>55624100</v>
+      </c>
+      <c r="K54" s="3">
         <v>56048900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56463600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57763900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57650100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>56759700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>55771100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>54261000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>54333300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58244800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>56524400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58655400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>59702200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>60908600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>65107000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>62612900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>56942000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>54462800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>53298400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>55464800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>55114800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>54972600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>54318400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>53873400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>44511200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>45055200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>44526600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1363300</v>
+        <v>852700</v>
       </c>
       <c r="E57" s="3">
-        <v>837700</v>
+        <v>1353200</v>
       </c>
       <c r="F57" s="3">
-        <v>1043800</v>
+        <v>840400</v>
       </c>
       <c r="G57" s="3">
-        <v>909100</v>
+        <v>1073700</v>
       </c>
       <c r="H57" s="3">
-        <v>824400</v>
+        <v>913000</v>
       </c>
       <c r="I57" s="3">
-        <v>898100</v>
+        <v>845800</v>
       </c>
       <c r="J57" s="3">
+        <v>901700</v>
+      </c>
+      <c r="K57" s="3">
         <v>987100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>921900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>849800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>712400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>594500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>732600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>566300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>548900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>516100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>632500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>475600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>629400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>636200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>548800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>732800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>599700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>592900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>732500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>730200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>705400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>576800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>590900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>488200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>415600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>457100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>480900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>806800</v>
+        <v>1389400</v>
       </c>
       <c r="E58" s="3">
-        <v>1541400</v>
+        <v>800800</v>
       </c>
       <c r="F58" s="3">
-        <v>940700</v>
+        <v>1546400</v>
       </c>
       <c r="G58" s="3">
-        <v>1339700</v>
+        <v>967700</v>
       </c>
       <c r="H58" s="3">
-        <v>1874100</v>
+        <v>1345400</v>
       </c>
       <c r="I58" s="3">
-        <v>909800</v>
+        <v>1922700</v>
       </c>
       <c r="J58" s="3">
+        <v>913500</v>
+      </c>
+      <c r="K58" s="3">
         <v>477000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1138300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1094400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2162300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>877300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>878500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1797900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1416100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1185400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>779700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1604800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2373100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2045900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3548300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3330700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1445700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>868400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>363300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>621800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>484800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1396900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1395400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1448200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2403800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1392000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1611700</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4045700</v>
+        <v>596600</v>
       </c>
       <c r="E59" s="3">
-        <v>3866800</v>
+        <v>578700</v>
       </c>
       <c r="F59" s="3">
-        <v>3488400</v>
+        <v>508800</v>
       </c>
       <c r="G59" s="3">
-        <v>3824800</v>
+        <v>505100</v>
       </c>
       <c r="H59" s="3">
-        <v>3609100</v>
+        <v>422100</v>
       </c>
       <c r="I59" s="3">
-        <v>3715900</v>
+        <v>404000</v>
       </c>
       <c r="J59" s="3">
+        <v>484800</v>
+      </c>
+      <c r="K59" s="3">
         <v>4904000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4589700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4940900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4272100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4023100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3229600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2742500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2373600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2227600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1774000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1778200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1944600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2492600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2415000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2201400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2274000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2163000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2387900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2305000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2067900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2685900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2323400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2111300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1827600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2062700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1857600</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6215700</v>
+        <v>5942500</v>
       </c>
       <c r="E60" s="3">
-        <v>6245900</v>
+        <v>6169600</v>
       </c>
       <c r="F60" s="3">
-        <v>5473000</v>
+        <v>6266100</v>
       </c>
       <c r="G60" s="3">
-        <v>6073600</v>
+        <v>5629900</v>
       </c>
       <c r="H60" s="3">
-        <v>6307700</v>
+        <v>6099400</v>
       </c>
       <c r="I60" s="3">
-        <v>5523800</v>
+        <v>6471100</v>
       </c>
       <c r="J60" s="3">
+        <v>5546200</v>
+      </c>
+      <c r="K60" s="3">
         <v>6368100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6649900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6885200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7146800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5495000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4840700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5106700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4338600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3929100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3186200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3858600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4947000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5174700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6512200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6264900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4319500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3624300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3483800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3657100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3258100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4659500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4309700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4047800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3911800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3950200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7803500</v>
+        <v>7135700</v>
       </c>
       <c r="E61" s="3">
-        <v>7715200</v>
+        <v>7745600</v>
       </c>
       <c r="F61" s="3">
-        <v>8153200</v>
+        <v>7740100</v>
       </c>
       <c r="G61" s="3">
-        <v>8324700</v>
+        <v>8386900</v>
       </c>
       <c r="H61" s="3">
-        <v>8195100</v>
+        <v>8360000</v>
       </c>
       <c r="I61" s="3">
-        <v>9071100</v>
+        <v>8407300</v>
       </c>
       <c r="J61" s="3">
+        <v>9107800</v>
+      </c>
+      <c r="K61" s="3">
         <v>9081400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9413400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9376300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9264700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11174300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12736300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12630300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14248200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16721500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17244000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17783800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16800500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15905300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16634100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16797700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15936000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14827600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13976400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15485600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>16060000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>15316600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15662600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>15874000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10121400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11518100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11672500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12830400</v>
+        <v>5297000</v>
       </c>
       <c r="E62" s="3">
-        <v>12886300</v>
+        <v>5284800</v>
       </c>
       <c r="F62" s="3">
-        <v>12964400</v>
+        <v>5406500</v>
       </c>
       <c r="G62" s="3">
-        <v>12601500</v>
+        <v>5625300</v>
       </c>
       <c r="H62" s="3">
-        <v>12376200</v>
+        <v>5010500</v>
       </c>
       <c r="I62" s="3">
-        <v>12402000</v>
+        <v>5031700</v>
       </c>
       <c r="J62" s="3">
+        <v>4954900</v>
+      </c>
+      <c r="K62" s="3">
         <v>12498400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12606100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12430600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12794900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12737900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11878500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11784900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11713300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12540200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11434400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11640000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11852700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12547200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13114700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12370300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11846000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11675900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11571800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11923400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11687800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11440000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11023200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>10891500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9479200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9446200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9203400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>26849600</v>
+        <v>26043900</v>
       </c>
       <c r="E66" s="3">
-        <v>26847400</v>
+        <v>26650300</v>
       </c>
       <c r="F66" s="3">
-        <v>26590500</v>
+        <v>26934100</v>
       </c>
       <c r="G66" s="3">
-        <v>26999800</v>
+        <v>27352900</v>
       </c>
       <c r="H66" s="3">
-        <v>26879100</v>
+        <v>27114400</v>
       </c>
       <c r="I66" s="3">
-        <v>26996800</v>
+        <v>27575100</v>
       </c>
       <c r="J66" s="3">
+        <v>27106200</v>
+      </c>
+      <c r="K66" s="3">
         <v>27947900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28669400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28692000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29206400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29407100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29455500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29521800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30300000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33190800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31864600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33282400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33600200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33627200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>36261000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>35432900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32101500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>30127700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>29032000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>31066100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>31005900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>31416100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>30995600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>30813300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>24247600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24876100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24826100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>20734000</v>
+        <v>21205100</v>
       </c>
       <c r="E72" s="3">
-        <v>20812000</v>
+        <v>20580100</v>
       </c>
       <c r="F72" s="3">
-        <v>21308900</v>
+        <v>20879200</v>
       </c>
       <c r="G72" s="3">
-        <v>21179400</v>
+        <v>21919800</v>
       </c>
       <c r="H72" s="3">
-        <v>20561800</v>
+        <v>21269300</v>
       </c>
       <c r="I72" s="3">
-        <v>20524200</v>
+        <v>21094200</v>
       </c>
       <c r="J72" s="3">
+        <v>20607400</v>
+      </c>
+      <c r="K72" s="3">
         <v>20369600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20220900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21388600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20739000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19825400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18986600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17639300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17044100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17615200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17264700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17746100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18382500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19822300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>21042900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19767600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17591900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17146600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17464500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17309700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17152300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16828100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16783400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16523700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16490100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16536900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16314900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29053500</v>
+        <v>29532600</v>
       </c>
       <c r="E76" s="3">
-        <v>29082200</v>
+        <v>28837900</v>
       </c>
       <c r="F76" s="3">
-        <v>29320700</v>
+        <v>29176100</v>
       </c>
       <c r="G76" s="3">
-        <v>29175000</v>
+        <v>30161400</v>
       </c>
       <c r="H76" s="3">
-        <v>28446200</v>
+        <v>29298800</v>
       </c>
       <c r="I76" s="3">
-        <v>28402800</v>
+        <v>29182900</v>
       </c>
       <c r="J76" s="3">
+        <v>28517900</v>
+      </c>
+      <c r="K76" s="3">
         <v>28101000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27794200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29071900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28443700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27352600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26315500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24739200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24033300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>25054000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24659700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25373000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>26102000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>27281400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>28846000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>27180000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24840600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24335100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24266400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24398700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24108900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>23556500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23322800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23060100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20263600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20179100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>19700500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1262400</v>
+        <v>1677300</v>
       </c>
       <c r="E81" s="3">
-        <v>726500</v>
+        <v>1253100</v>
       </c>
       <c r="F81" s="3">
-        <v>1933800</v>
+        <v>728900</v>
       </c>
       <c r="G81" s="3">
-        <v>1725400</v>
+        <v>1989200</v>
       </c>
       <c r="H81" s="3">
-        <v>1076900</v>
+        <v>1732800</v>
       </c>
       <c r="I81" s="3">
-        <v>1324300</v>
+        <v>1104800</v>
       </c>
       <c r="J81" s="3">
+        <v>1329600</v>
+      </c>
+      <c r="K81" s="3">
         <v>1118900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2050700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2587900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2291600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1876100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1631100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1121700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>995900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>579500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>312800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-243300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1006000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>465500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>851400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2245000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>739800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-590600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1309500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>739200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>438900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>294700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>509000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>797800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>188200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>434800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1213800</v>
+        <v>1136200</v>
       </c>
       <c r="E83" s="3">
-        <v>1128500</v>
+        <v>1055000</v>
       </c>
       <c r="F83" s="3">
-        <v>1517100</v>
+        <v>1048000</v>
       </c>
       <c r="G83" s="3">
-        <v>1131400</v>
+        <v>1115000</v>
       </c>
       <c r="H83" s="3">
-        <v>1028300</v>
+        <v>1059000</v>
       </c>
       <c r="I83" s="3">
-        <v>1043800</v>
+        <v>1058200</v>
       </c>
       <c r="J83" s="3">
+        <v>1127000</v>
+      </c>
+      <c r="K83" s="3">
         <v>2303300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1059600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1007200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1039800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1090600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1068100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1003800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1027700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1249600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1122400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1101000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1227300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1208500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1182200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1036500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>972300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1010700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>949100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>956000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>946300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1046400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>945900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>900500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>997900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>959500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3006300</v>
+        <v>2222100</v>
       </c>
       <c r="E89" s="3">
-        <v>2111200</v>
+        <v>2984000</v>
       </c>
       <c r="F89" s="3">
-        <v>3544400</v>
+        <v>2118000</v>
       </c>
       <c r="G89" s="3">
-        <v>2574900</v>
+        <v>3646000</v>
       </c>
       <c r="H89" s="3">
-        <v>2020600</v>
+        <v>2585800</v>
       </c>
       <c r="I89" s="3">
-        <v>953300</v>
+        <v>2072900</v>
       </c>
       <c r="J89" s="3">
+        <v>957100</v>
+      </c>
+      <c r="K89" s="3">
         <v>3344900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4444000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4357100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2108300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3488600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3177800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2126300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1834100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>982700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1586900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-275400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1353700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1913300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2087500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2268800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>766700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1063200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2646600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1967000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1858600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1070200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1876900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1213800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1283700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>964100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1621000</v>
+        <v>-998600</v>
       </c>
       <c r="E91" s="3">
-        <v>-1113000</v>
+        <v>-1187300</v>
       </c>
       <c r="F91" s="3">
-        <v>-975000</v>
+        <v>-821900</v>
       </c>
       <c r="G91" s="3">
-        <v>-1108000</v>
+        <v>-738300</v>
       </c>
       <c r="H91" s="3">
-        <v>-1569000</v>
+        <v>-821300</v>
       </c>
       <c r="I91" s="3">
-        <v>-1257000</v>
+        <v>-1184900</v>
       </c>
       <c r="J91" s="3">
+        <v>-929000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1135000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1388000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1554000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-957000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>2200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>1416700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1401400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5500</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-2500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-29300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-25400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>72300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-215800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-42200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-618400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-493200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-816600</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-747200</v>
+        <v>-943000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1024700</v>
+        <v>-741600</v>
       </c>
       <c r="F94" s="3">
-        <v>-696400</v>
+        <v>-1028000</v>
       </c>
       <c r="G94" s="3">
-        <v>-882600</v>
+        <v>-716300</v>
       </c>
       <c r="H94" s="3">
-        <v>-1148300</v>
+        <v>-886300</v>
       </c>
       <c r="I94" s="3">
-        <v>-848700</v>
+        <v>-1178100</v>
       </c>
       <c r="J94" s="3">
+        <v>-852200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-929000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-822800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-993900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-924500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1195700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-534100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-520000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-468600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-482800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-492900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-543800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-674100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-665800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-752800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3540000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-792100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-793100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-919300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-856700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1030600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-799300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1458700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6656200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-863500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-411000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-658400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8819,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-828100</v>
+        <v>827600</v>
       </c>
       <c r="E96" s="3">
-        <v>-792100</v>
+        <v>822000</v>
       </c>
       <c r="F96" s="3">
-        <v>-721400</v>
+        <v>794600</v>
       </c>
       <c r="G96" s="3">
-        <v>-724300</v>
+        <v>742100</v>
       </c>
       <c r="H96" s="3">
-        <v>-728000</v>
+        <v>727400</v>
       </c>
       <c r="I96" s="3">
-        <v>-690500</v>
+        <v>746900</v>
       </c>
       <c r="J96" s="3">
+        <v>693300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-613900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1845200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-643700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-509200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-408700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-413300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-402800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-363800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-388400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-384900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-393900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-348400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-346200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-370600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-356100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-310200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-309000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-297200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-309400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-252900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-249300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-248600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-227700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-195100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-193600</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,132 +9233,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2150200</v>
+        <v>-1422700</v>
       </c>
       <c r="E100" s="3">
-        <v>-1167500</v>
+        <v>-2134200</v>
       </c>
       <c r="F100" s="3">
-        <v>-2294500</v>
+        <v>-1171200</v>
       </c>
       <c r="G100" s="3">
-        <v>-1690100</v>
+        <v>-2360200</v>
       </c>
       <c r="H100" s="3">
-        <v>-850200</v>
+        <v>-1697300</v>
       </c>
       <c r="I100" s="3">
-        <v>-714000</v>
+        <v>-872200</v>
       </c>
       <c r="J100" s="3">
+        <v>-716900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-2154600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3379300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3283300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1641300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2403900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2105900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1604800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1378500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-492900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1138500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>161700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>51800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1276300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1518800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1515500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>16900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-418600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1644500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1087800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-816800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-401100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-223300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>5465500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-418700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-554700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>108900</v>
+        <v>-143600</v>
       </c>
       <c r="E102" s="3">
-        <v>-81000</v>
+        <v>108100</v>
       </c>
       <c r="F102" s="3">
-        <v>553600</v>
+        <v>-81200</v>
       </c>
       <c r="G102" s="3">
+        <v>569400</v>
+      </c>
+      <c r="H102" s="3">
         <v>2200</v>
       </c>
-      <c r="H102" s="3">
-        <v>22100</v>
-      </c>
       <c r="I102" s="3">
-        <v>-609500</v>
+        <v>22700</v>
       </c>
       <c r="J102" s="3">
+        <v>-612000</v>
+      </c>
+      <c r="K102" s="3">
         <v>261300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>241900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>79800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-457400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-111100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>537800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-44500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-657600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>731400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-28800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-184000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>244300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-148400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>82800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>22600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>11300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-130200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>195000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>23100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>CNQ</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6580300</v>
+      </c>
+      <c r="E8" s="3">
         <v>6582800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6613100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6088100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7233700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7314700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5958300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6378400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7132200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7620600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8479900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7890200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6820900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5711800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4719000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4779000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3882700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3452900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2253000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3531300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4600800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5106900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4410800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4040000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2817600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4286700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4480600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4120800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3872100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3323600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2910600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2797900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2656500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1793800</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3272100</v>
+      </c>
+      <c r="E9" s="3">
         <v>3178500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3385800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3279600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3335500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3206800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3429200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3324400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3614300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3141700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3672000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3321800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2912600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2428100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2354100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2378700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2281800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1951100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1701300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2445200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2388900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2332900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2005500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1977700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1895900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1901000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2080700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2094300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2102400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1830800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1529400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1339800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1267600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1104700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3308200</v>
+      </c>
+      <c r="E10" s="3">
         <v>3404300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3227300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2808500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3898100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4107900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2529100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3053900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3517900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4479000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4807900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4568400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3908400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3283700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2364900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2400400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1600900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1501800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>551700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1086100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2211900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2774000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2405200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2062300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>921700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2385700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2399900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2026500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1769700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1492900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1381300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1458100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1389000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>689100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,61 +1377,64 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>18300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-59800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>25700</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-34000</v>
       </c>
       <c r="I14" s="3">
         <v>-34000</v>
       </c>
       <c r="J14" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-354100</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>-167900</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1429,8 +1448,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1465,112 +1484,118 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1321200</v>
+      </c>
+      <c r="E15" s="3">
         <v>1182900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1204800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1132100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1560600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1136200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1055000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1048000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2303300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1059600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1007200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1039800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1090600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1068100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1003800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1027700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1249600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1122400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1101000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1227300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1208500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1182200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1036500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>972300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1010700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>949100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>956000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>946300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1046400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>945900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>900500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>997900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>959500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4780200</v>
+      </c>
+      <c r="E17" s="3">
         <v>4493100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4744800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4795700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5103600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4711100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4693400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4582400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6292300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4326600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4760600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4885500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4250400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3283700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3553200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3601600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3580900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3176200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2929400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3623100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3836000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3641200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3139600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3085400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2898200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2878400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3261100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3069900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3316900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2948600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2437300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2453000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2352300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2186400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1800100</v>
+      </c>
+      <c r="E18" s="3">
         <v>2089600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1868300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1292400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2130000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2603600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1264900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1796000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>839900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3294000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3719300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3004700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2570500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2428100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1165800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1177400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>301800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>276800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-676400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-91800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>764900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1465800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1271200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>954600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-80700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1408300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1219500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1050900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>555200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>375100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>473300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>344900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>304200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-392600</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>599100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-103600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>86200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>210500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-224100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>175900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-171400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>284100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-440900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-252000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>128600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>104400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-215600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>406400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>182300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>478200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>176300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>355500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-877300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>104500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-143400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>114200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>131600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-422400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>281200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-21100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-249900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>90800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>343100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>494200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>14600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>57600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-59900</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2522200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3376100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2986900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2214000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3914800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3563900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2491300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2853600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3427300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3912700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4474600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4173100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3765500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3280700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2576100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2387300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2029500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1575400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>780000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>258200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2077800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2504600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2421900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2058500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>507600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2638600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2154500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1747200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1692300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1664100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1868000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1357500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1321400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>131400</v>
+      </c>
+      <c r="E22" s="3">
         <v>117700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>120600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>118200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>128700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>135300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>132200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>120500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>145000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>109300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>118200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>120500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>150300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>131900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>128000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>133800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>192700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>133400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>156200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>161700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>228400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>191500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>156200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>147000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>181100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>130800</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>143000</v>
       </c>
       <c r="AD22" s="3">
         <v>143000</v>
       </c>
       <c r="AE22" s="3">
+        <v>143000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>198000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>136200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>107900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>102900</v>
-      </c>
-      <c r="AI22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1102300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2079300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1648300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1039800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2239800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2326400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1338200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1691000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>979000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2743800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3349100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3012900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2524600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2080700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1444300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1225900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>587300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>319700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-477100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1130800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>640900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1130800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1229200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>939200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-684200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1558800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1055400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>657900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>448000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>582000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>859600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>256600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>361800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-452500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>311400</v>
+      </c>
+      <c r="E24" s="3">
         <v>401900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>395300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>310900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>250600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>593600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>233300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>361400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-139900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>693100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>761200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>721300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>648600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>449600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>322600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>230000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-233900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-124800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>175400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>279400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1015900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>199400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-93600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>249300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>316200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>219100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>153300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>72900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>61800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>68400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-73000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>790900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1677300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1253100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>728900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1989200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1732800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1104800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1329600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1118900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2050700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2587900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2291600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1876100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1631100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1121700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>995900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>579500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>312800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-243300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1006000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>465500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>851400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2245000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>739800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-590600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1309500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>739200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>438900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>294700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>509000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>797800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>188200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>434800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>790900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1677300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1253100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>728900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1989200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1732800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1104800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1329600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1118900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2050700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2587900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2291600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1876100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1631100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1121700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>995900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>579500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>312800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-243300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1006000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>465500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>851400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2245000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>739800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-590600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1309500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>739200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>438900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>294700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>509000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>797800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>188200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>434800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-599100</v>
+      </c>
+      <c r="E32" s="3">
         <v>103600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-86200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-210500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>224100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-175900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>171400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-284100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>440900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>252000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-128600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-104400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>215600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-406400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-182300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-478200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-176300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-355500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>877300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-104500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>143400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-114200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-131600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>422400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-281200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>21100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>249900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-90800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-343100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-494200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-57600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>59900</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>790900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1677300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1253100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>728900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1989200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1732800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1104800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1329600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1118900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2050700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2587900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2291600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1876100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1631100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1121700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>995900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>579500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>312800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-243300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1006000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>465500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>851400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2245000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>739800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-590600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1309500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>739200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>438900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>294700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>509000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>797800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>188200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>434800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>790900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1677300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1253100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>728900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1989200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1732800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1104800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1329600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1118900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2050700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2587900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2291600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1876100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1631100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1121700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>995900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>579500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>312800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-243300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1006000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>465500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>851400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2245000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>739800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-590600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1309500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>739200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>438900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>294700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>509000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>797800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>188200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>434800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E41" s="3">
         <v>533700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>668500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>566400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>664100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>92400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>68000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>677200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>411700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>172200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>550800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>662200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>121500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>120100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>142400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>134200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>182800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>840500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>108400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>145900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>315600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>69300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>76900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>215100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>137000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>114400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>102000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>232200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>37200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3815,533 +3904,548 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>443100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>406600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>417700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>395700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>357700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>361400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>293700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>271200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>289700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>228800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>226700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>339200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>305200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>236000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>208500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>215800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>174200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>382000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>470100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>433800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>422600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>398800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>478200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>560800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>587900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>664600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>660900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>619200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>626100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>701400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>464800</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2867600</v>
+      </c>
+      <c r="E43" s="3">
         <v>2294700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2668300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2516800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2414800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3122500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2106900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2514400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2616900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2850900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3706000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3478400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2303300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2352600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2302700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2012700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1933600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1477300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1692700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1195900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1932000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1993900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1684400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1760600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>873700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1436700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1965500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2023500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1239100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1637300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1637100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1755400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1441200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1941100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1873500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1814200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1700700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1540200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1607100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1484700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1419100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1336000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1338000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1416600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1253300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1146100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>914800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>878000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>786900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>820200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>830300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>859300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>737700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>898200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>954200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>942900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>825200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>726800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>812400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>783700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>744500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>665300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>652700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>691400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>505500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>529300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>473200</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E45" s="3">
         <v>49600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>57700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>51000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>44700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>203200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>316300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>296300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>218700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>170300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>257000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>324700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>284900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>242200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>443100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>240900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>335100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>177800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>314200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>306900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>204000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>222200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>258700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>297400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>198700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>189000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>282100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>266400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>398700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>331900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>320400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5146500</v>
+      </c>
+      <c r="E46" s="3">
         <v>5015000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5428700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5501700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5427000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5553900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4498600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4586100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5194700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5210600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5862400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5332600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4399200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4413300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3966100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3509800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3374300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3093400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3191500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3283400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3498400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3878300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3683600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3281700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2298500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3201100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3744400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3301700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3644400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3066900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3251500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3182000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3331000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2714200</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>700</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>800</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -4349,8 +4453,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4371,168 +4475,174 @@
         <v>0</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>401400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>429400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>520500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>536000</v>
       </c>
-      <c r="V47" s="3" t="s">
+      <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>508300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>587800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>620100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>641300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>668200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>627900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>641400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>627800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>596900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>557400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>519500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>504700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>496300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>499300</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53747500</v>
+      </c>
+      <c r="E48" s="3">
         <v>50129900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>49657000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50145500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>51677600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50464600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>51834300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50573900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50447100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50898800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51560800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51853500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>51942200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50911800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49876100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50009900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>54033300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>52633700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>54504900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>55426200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>56456700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>60141800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>57872200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>52626400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>51142200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>49193300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>50788500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>50896900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>50458900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>50437300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>49826300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>40562500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>40940500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>41054200</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>430900</v>
+      </c>
+      <c r="E52" s="3">
         <v>430800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>402600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>463000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>408900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>394800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>425200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>464200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>407100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>354200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>340700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>464100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>418300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>445900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>418700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>412200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>407800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>276800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>423000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>992700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>445200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>499100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>437000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>392600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>353900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>276100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>290600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>288300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>272400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>256800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>276100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>262000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>287300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>258900</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59324900</v>
+      </c>
+      <c r="E54" s="3">
         <v>55576400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>55488300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>56110200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>57514200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56413200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>56758000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>55624100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56048900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>56463600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57763900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57650100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>56759700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>55771100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>54261000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>54333300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58244800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>56524400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58655400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>59702200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>60908600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>65107000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>62612900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>56942000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>54462800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>53298400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>55464800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>55114800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>54972600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>54318400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>53873400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>44511200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>45055200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>44526600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>749900</v>
+      </c>
+      <c r="E57" s="3">
         <v>852700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1353200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>840400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1073700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>913000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>845800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>901700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>987100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>921900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>849800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>712400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>594500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>732600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>566300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>548900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>516100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>632500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>475600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>629400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>636200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>548800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>732800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>599700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>592900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>732500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>730200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>705400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>576800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>590900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>488200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>415600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>457100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>480900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1845200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1389400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>800800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1546400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>967700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1345400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1922700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>913500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>477000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1138300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1094400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2162300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>877300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>878500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1797900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1416100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1185400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>779700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1604800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2373100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2045900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3548300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3330700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1445700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>868400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>363300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>621800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>484800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1396900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1395400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1448200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2403800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1392000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1611700</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>631800</v>
+      </c>
+      <c r="E59" s="3">
         <v>596600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>578700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>508800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>505100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>422100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>404000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>484800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4904000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4589700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4940900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4272100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4023100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3229600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2742500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2373600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2227600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1774000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1778200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1944600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2492600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2415000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2201400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2274000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2163000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2387900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2305000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2067900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2685900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2323400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2111300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1827600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2062700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1857600</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6693600</v>
+      </c>
+      <c r="E60" s="3">
         <v>5942500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6169600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6266100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5629900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6099400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6471100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5546200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6368100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6649900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6885200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7146800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5495000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4840700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5106700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4338600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3929100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3186200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3858600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4947000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5174700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6512200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6264900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4319500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3624300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3483800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3657100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3258100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4659500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4309700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4047800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3911800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3950200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12251500</v>
+      </c>
+      <c r="E61" s="3">
         <v>7135700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7745600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7740100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8386900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8360000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8407300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9107800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9081400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9413400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9376300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9264700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11174300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12736300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12630300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14248200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16721500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17244000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17783800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16800500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15905300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16634100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16797700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15936000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14827600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13976400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>15485600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16060000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15316600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>15662600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>15874000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10121400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11518100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11672500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5624700</v>
+      </c>
+      <c r="E62" s="3">
         <v>5297000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5284800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5406500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5625300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5010500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5031700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4954900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12498400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12606100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12430600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12794900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12737900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11878500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11784900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11713300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12540200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11434400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11640000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11852700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12547200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13114700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12370300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11846000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11675900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11571800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11923400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11687800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11440000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11023200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10891500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9479200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9446200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9203400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31894400</v>
+      </c>
+      <c r="E66" s="3">
         <v>26043900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26650300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26934100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27352900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27114400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27575100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27106200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27947900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28669400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28692000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29206400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29407100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29455500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29521800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30300000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33190800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31864600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33282400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33600200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33627200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>36261000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>35432900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>32101500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>30127700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>29032000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>31066100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>31005900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>31416100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>30995600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>30813300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>24247600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24876100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>24826100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19531700</v>
+      </c>
+      <c r="E72" s="3">
         <v>21205100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20580100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20879200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21919800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21269300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21094200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20607400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20369600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20220900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21388600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20739000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19825400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18986600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17639300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17044100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17615200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17264700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17746100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18382500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19822300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>21042900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19767600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17591900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17146600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17464500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17309700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17152300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>16828100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16783400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16523700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16490100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16536900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16314900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27430400</v>
+      </c>
+      <c r="E76" s="3">
         <v>29532600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>28837900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>29176100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>30161400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29298800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>29182900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>28517900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28101000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27794200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>29071900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28443700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27352600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26315500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24739200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24033300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25054000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24659700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25373000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>26102000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>27281400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>28846000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>27180000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24840600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24335100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24266400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24398700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24108900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>23556500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23322800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23060100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20263600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20179100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>19700500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>790900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1677300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1253100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>728900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1989200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1732800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1104800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1329600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1118900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2050700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2587900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2291600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1876100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1631100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1121700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>995900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>579500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>312800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-243300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1006000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>465500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>851400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2245000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>739800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-590600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1309500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>739200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>438900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>294700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>509000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>797800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>188200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>434800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1230500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1136200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1055000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1048000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1115000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1059000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1058200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1127000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2303300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1059600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1007200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1039800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1090600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1068100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1003800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1027700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1249600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1122400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1101000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1227300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1208500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1182200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1036500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>972300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1010700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>949100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>956000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>946300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1046400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>945900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>900500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>997900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>959500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2385300</v>
+      </c>
+      <c r="E89" s="3">
         <v>2222100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2984000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2118000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3646000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2585800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2072900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>957100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3344900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4444000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4357100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2108300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3488600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3177800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2126300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1834100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>982700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1586900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-275400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1353700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1913300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2087500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2268800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>766700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1063200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2646600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1967000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1858600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1070200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1876900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1213800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1283700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>964100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-903500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-998600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1187300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-821900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-738300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-821300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1184900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-929000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1135000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1388000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1554000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-957000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>2200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>1416700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1401400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5500</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-29300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-25400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>72300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-215800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-42200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-618400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-493200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-816600</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7237800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-943000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-741600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1028000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-716300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-886300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1178100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-852200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-929000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-822800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-993900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-924500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1195700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-534100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-520000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-468600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-482800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-492900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-543800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-674100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-665800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-752800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3540000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-792100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-793100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-919300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-856700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1030600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-799300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1458700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6656200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-863500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-411000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-658400</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,112 +9052,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>771500</v>
+      </c>
+      <c r="E96" s="3">
         <v>827600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>822000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>794600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>742100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>727400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>746900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>693300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-613900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1845200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-643700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-509200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-408700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-413300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-402800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-363800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-388400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-384900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-393900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-348400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-346200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-370600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-356100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-310200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-309000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-297200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-309400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-252900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-249300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-248600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-227700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-195100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-193600</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9478,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4442500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1422700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2134200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1171200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2360200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1697300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-872200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-716900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2154600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3379300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3283300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1641300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2403900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2105900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1604800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1378500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-492900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1138500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>161700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>51800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1276300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1518800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1515500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>16900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-418600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1644500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1087800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-816800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-401100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-223300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>5465500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-418700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-554700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-410100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-143600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>108100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-81200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>569400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-612000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>261300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>241900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>79800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-457400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-111100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>537800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-44500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-657600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>731400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-28800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-184000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>244300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-148400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>82800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>11300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-130200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>195000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>23100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>CNQ</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7610500</v>
+      </c>
+      <c r="E8" s="3">
         <v>6580300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6582800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6613100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6088100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7233700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7314700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5958300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6378400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7132200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7620600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8479900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7890200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6820900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5711800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4719000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4779000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3882700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3452900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2253000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3531300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4600800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5106900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4410800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4040000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2817600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4286700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4480600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4120800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3872100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3323600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2910600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2797900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2656500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1793800</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3834800</v>
+      </c>
+      <c r="E9" s="3">
         <v>3272100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3178500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3385800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3279600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3335500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3206800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3429200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3324400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3614300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3141700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3672000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3321800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2912600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2428100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2354100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2378700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2281800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1951100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1701300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2445200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2388900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2332900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2005500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1977700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1895900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1901000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2080700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2094300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2102400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1830800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1529400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1339800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1267600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1104700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3775700</v>
+      </c>
+      <c r="E10" s="3">
         <v>3308200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3404300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3227300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2808500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3898100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4107900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2529100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3053900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3517900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4479000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4807900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4568400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3908400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3283700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2364900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2400400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1600900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1501800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>551700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1086100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2211900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2774000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2405200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2062300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>921700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2385700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2399900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2026500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1769700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1492900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1381300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1458100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1389000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>689100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,64 +1397,67 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>18300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-59800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>25700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-34000</v>
       </c>
       <c r="J14" s="3">
         <v>-34000</v>
       </c>
       <c r="K14" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-354100</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>-167900</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1451,8 +1471,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1487,115 +1507,121 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1301000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1321200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1182900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1204800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1132100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1560600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1136200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1055000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1048000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2303300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1059600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1007200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1039800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1090600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1068100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1003800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1027700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1249600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1122400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1101000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1227300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1208500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1182200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1036500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>972300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1010700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>949100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>956000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>946300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1046400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>945900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>900500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>997900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>959500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5314600</v>
+      </c>
+      <c r="E17" s="3">
         <v>4780200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4493100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4744800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4795700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5103600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4711100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4693400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4582400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6292300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4326600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4760600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4885500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4250400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3283700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3553200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3601600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3580900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3176200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2929400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3623100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3836000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3641200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3139600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3085400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2898200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2878400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3261100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3069900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3316900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2948600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2437300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2453000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2352300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2186400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2295900</v>
+      </c>
+      <c r="E18" s="3">
         <v>1800100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2089600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1868300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1292400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2130000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2603600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1264900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1796000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>839900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3294000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3719300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3004700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2570500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2428100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1165800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1177400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>301800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>276800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-676400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-91800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>764900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1465800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1271200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>954600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-80700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1408300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1219500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1050900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>555200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>375100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>473300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>344900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>304200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-392600</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E20" s="3">
         <v>599100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-103600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>86200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>210500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-224100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>175900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-171400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>284100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-440900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-252000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>128600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>104400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-215600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>406400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>182300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>478200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>176300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>355500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-877300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>104500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-143400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>114200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>131600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-422400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>281200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-21100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-249900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>90800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>343100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>494200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>14600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>57600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-59900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3635200</v>
+      </c>
+      <c r="E21" s="3">
         <v>2522200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3376100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2986900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2214000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3914800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3563900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2491300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2853600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3427300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3912700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4474600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4173100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3765500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3280700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2576100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2387300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2029500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1575400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>780000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>258200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2077800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2504600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2421900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2058500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>507600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2638600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2154500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1747200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1692300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1664100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1868000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1357500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1321400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>183700</v>
+      </c>
+      <c r="E22" s="3">
         <v>131400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>117700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>120600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>118200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>128700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>135300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>132200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>120500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>145000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>109300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>118200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>120500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>150300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>131900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>128000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>133800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>192700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>133400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>156200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>161700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>228400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>191500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>156200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>147000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>181100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>130800</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>143000</v>
       </c>
       <c r="AE22" s="3">
         <v>143000</v>
       </c>
       <c r="AF22" s="3">
+        <v>143000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>198000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>136200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>107900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>102900</v>
-      </c>
-      <c r="AJ22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2154700</v>
+      </c>
+      <c r="E23" s="3">
         <v>1102300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2079300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1648300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1039800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2239800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2326400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1338200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1691000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>979000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2743800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3349100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3012900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2524600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2080700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1444300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1225900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>587300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>319700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-477100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1130800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>640900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1130800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1229200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>939200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-684200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1558800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1055400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>657900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>448000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>582000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>859600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>256600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>361800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-452500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>444600</v>
+      </c>
+      <c r="E24" s="3">
         <v>311400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>401900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>395300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>310900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>250600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>593600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>233300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>361400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-139900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>693100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>761200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>721300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>648600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>449600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>322600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>230000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-233900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-124800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>175400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>279400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1015900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>199400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-93600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>249300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>316200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>219100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>153300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>72900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>61800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>68400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-73000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E26" s="3">
         <v>790900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1677300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1253100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>728900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1989200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1732800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1104800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1329600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1118900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2050700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2587900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2291600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1876100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1631100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1121700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>995900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>579500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>312800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-243300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1006000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>465500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>851400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2245000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>739800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-590600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1309500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>739200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>438900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>294700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>509000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>797800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>188200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>434800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E27" s="3">
         <v>790900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1677300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1253100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>728900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1989200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1732800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1104800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1329600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1118900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2050700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2587900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2291600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1876100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1631100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1121700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>995900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>579500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>312800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-243300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1006000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>465500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>851400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2245000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>739800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-590600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1309500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>739200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>438900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>294700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>509000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>797800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>188200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>434800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-599100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>103600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-86200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-210500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>224100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-175900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>171400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-284100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>440900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>252000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-128600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-104400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>215600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-406400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-182300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-478200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-176300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-355500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>877300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-104500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>143400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-114200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-131600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>422400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-281200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>21100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>249900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-90800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-343100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-494200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-57600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>59900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E33" s="3">
         <v>790900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1677300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1253100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>728900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1989200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1732800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1104800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1329600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1118900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2050700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2587900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2291600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1876100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1631100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1121700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>995900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>579500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>312800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-243300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1006000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>465500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>851400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2245000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>739800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-590600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1309500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>739200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>438900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>294700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>509000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>797800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>188200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>434800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E35" s="3">
         <v>790900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1677300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1253100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>728900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1989200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1732800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1104800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1329600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1118900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2050700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2587900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2291600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1876100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1631100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1121700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>995900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>579500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>312800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-243300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1006000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>465500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>851400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2245000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>739800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-590600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1309500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>739200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>438900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>294700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>509000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>797800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>188200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>434800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E41" s="3">
         <v>91000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>533700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>668500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>566400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>664100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>677200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>411700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>172200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>92400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>550800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>662200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>121500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>120100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>142400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>134200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>182800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>840500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>108400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>145900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>315600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>69300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>76900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>215100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>137000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>114400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>102000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>232200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>37200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>13100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3901,551 +3991,566 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>443100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>406600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>417700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>395700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>357700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>361400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>293700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>271200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>289700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>228800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>226700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>339200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>305200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>236000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>208500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>215800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>174200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>382000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>470100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>433800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>422600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>398800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>478200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>560800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>587900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>664600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>660900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>619200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>626100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>701400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>464800</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2685500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2867600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2294700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2668300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2516800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2414800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3122500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2106900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2514400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2616900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2850900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3706000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3478400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2303300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2352600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2302700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2012700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1933600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1477300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1692700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1195900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1932000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1993900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1684400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1760600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>873700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1436700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1965500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2023500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1239100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1637300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1637100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1755400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1441200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1872900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1941100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1873500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1814200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1700700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1540200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1607100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1484700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1419100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1336000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1338000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1416600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1253300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1146100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>914800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>878000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>786900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>820200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>830300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>859300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>737700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>898200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>954200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>942900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>825200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>726800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>812400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>783700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>744500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>665300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>652700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>691400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>505500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>529300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>473200</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>52800</v>
+        <v>66800</v>
       </c>
       <c r="E45" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F45" s="3">
         <v>49600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>57700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>51000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>44700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>35500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>203200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>316300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>296300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>218700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>170300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>257000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>324700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>284900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>242200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>443100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>240900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>335100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>177800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>314200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>306900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>204000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>222200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>258700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>297400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>198700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>189000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>282100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>266400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>398700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>331900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>320400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5032900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5146500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5015000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5428700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5501700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5427000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5553900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4498600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4586100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5194700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5210600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5862400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5332600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4399200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4413300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3966100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3509800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3374300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3093400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3191500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3283400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3498400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3878300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3683600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3281700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2298500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3201100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3744400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3301700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3644400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3066900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3251500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3182000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3331000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2714200</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>700</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>800</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -4456,8 +4561,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4478,171 +4583,177 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>401400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>429400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>520500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>536000</v>
       </c>
-      <c r="W47" s="3" t="s">
+      <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>508300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>587800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>620100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>641300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>668200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>627900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>641400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>627800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>596900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>557400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>519500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>504700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>496300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>499300</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53456000</v>
+      </c>
+      <c r="E48" s="3">
         <v>53747500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>50129900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>49657000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50145500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>51677600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50464600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>51834300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50573900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50447100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50898800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51560800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>51853500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>51942200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50911800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>49876100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>50009900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>54033300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>52633700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>54504900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>55426200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>56456700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>60141800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>57872200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>52626400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>51142200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>49193300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>50788500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>50896900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>50458900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>50437300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>49826300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>40562500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>40940500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>41054200</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>518300</v>
+      </c>
+      <c r="E52" s="3">
         <v>430900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>430800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>402600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>463000</v>
       </c>
-      <c r="H52" s="3">
-        <v>408900</v>
-      </c>
       <c r="I52" s="3">
+        <v>409700</v>
+      </c>
+      <c r="J52" s="3">
         <v>394800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>425200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>464200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>407100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>354200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>340700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>464100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>418300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>445900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>418700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>412200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>407800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>276800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>423000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>992700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>445200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>499100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>437000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>392600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>353900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>276100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>290600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>288300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>272400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>256800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>276100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>262000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>287300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>258900</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59007200</v>
+      </c>
+      <c r="E54" s="3">
         <v>59324900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>55576400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>55488300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>56110200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>57514200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>56413200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56758000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>55624100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>56048900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>56463600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>57763900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57650100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>56759700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>55771100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>54261000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>54333300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58244800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>56524400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58655400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59702200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>60908600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>65107000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>62612900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>56942000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>54462800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>53298400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>55464800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>55114800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>54972600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>54318400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>53873400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>44511200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>45055200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>44526600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>825800</v>
+      </c>
+      <c r="E57" s="3">
         <v>749900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>852700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1353200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>840400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1073700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>913000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>845800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>901700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>987100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>921900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>849800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>712400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>594500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>732600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>566300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>548900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>516100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>632500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>475600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>629400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>636200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>548800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>732800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>599700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>592900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>732500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>730200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>705400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>576800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>590900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>488200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>415600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>457100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>480900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1171600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1845200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1389400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>800800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1546400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>967700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1345400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1922700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>913500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>477000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1138300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1094400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2162300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>877300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>878500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1797900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1416100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1185400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>779700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1604800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2373100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2045900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3548300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3330700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1445700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>868400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>363300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>621800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>484800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1396900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1395400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1448200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2403800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1392000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1611700</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>673500</v>
+      </c>
+      <c r="E59" s="3">
         <v>631800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>596600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>578700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>508800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>505100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>422100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>404000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>484800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4904000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4589700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4940900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4272100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4023100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3229600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2742500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2373600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2227600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1774000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1778200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1944600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2492600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2415000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2201400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2274000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2163000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2387900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2305000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2067900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2685900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2323400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2111300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1827600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2062700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1857600</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6013100</v>
+      </c>
+      <c r="E60" s="3">
         <v>6693600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5942500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6169600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6266100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5629900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6099400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6471100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5546200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6368100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6649900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6885200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7146800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5495000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4840700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5106700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4338600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3929100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3186200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3858600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4947000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5174700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6512200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6264900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4319500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3624300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3483800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3657100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3258100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4659500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4309700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4047800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3911800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3950200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11931700</v>
+      </c>
+      <c r="E61" s="3">
         <v>12251500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7135700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7745600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7740100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8386900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8360000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8407300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9107800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9081400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9413400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9376300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9264700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11174300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12736300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12630300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14248200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16721500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17244000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17783800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16800500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15905300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16634100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16797700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15936000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14827600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13976400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>15485600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16060000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>15316600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>15662600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15874000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10121400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11518100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11672500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5501800</v>
+      </c>
+      <c r="E62" s="3">
         <v>5624700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5297000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5284800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5406500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5625300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5010500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5031700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4954900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12498400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12606100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12430600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12794900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12737900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11878500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11784900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11713300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12540200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11434400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11640000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11852700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12547200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13114700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12370300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11846000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11675900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11571800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11923400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11687800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11440000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11023200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>10891500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9479200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9446200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9203400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>30868600</v>
+      </c>
+      <c r="E66" s="3">
         <v>31894400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26043900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26650300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26934100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27352900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27114400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27575100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27106200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27947900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28669400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28692000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29206400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29407100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29455500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29521800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30300000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33190800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31864600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33282400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33600200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>33627200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>36261000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>35432900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>32101500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>30127700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>29032000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>31066100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>31005900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>31416100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>30995600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>30813300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>24247600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>24876100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>24826100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20103000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19531700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21205100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20580100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20879200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21919800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21269300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21094200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20607400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20369600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20220900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21388600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20739000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19825400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18986600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17639300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17044100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17615200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17264700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17746100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18382500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19822300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>21042900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19767600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17591900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17146600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17464500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17309700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17152300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16828100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16783400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16523700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16490100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16536900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>16314900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28138600</v>
+      </c>
+      <c r="E76" s="3">
         <v>27430400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>29532600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>28837900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>29176100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>30161400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>29298800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29182900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28517900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28101000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27794200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>29071900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28443700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27352600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26315500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24739200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24033300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25054000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>24659700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>25373000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26102000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>27281400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>28846000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>27180000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24840600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24335100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24266400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24398700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>24108900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23556500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23322800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23060100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20263600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20179100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>19700500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E81" s="3">
         <v>790900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1677300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1253100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>728900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1989200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1732800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1104800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1329600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1118900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2050700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2587900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2291600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1876100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1631100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1121700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>995900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>579500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>312800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-243300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1006000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>465500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>851400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2245000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>739800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-590600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1309500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>739200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>438900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>294700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>509000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>797800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>188200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>434800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1132100</v>
+      </c>
+      <c r="E83" s="3">
         <v>1230500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1136200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1055000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1048000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1115000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1059000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1058200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1127000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2303300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1059600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1007200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1039800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1090600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1068100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1003800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1027700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1249600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1122400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1101000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1227300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1208500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1182200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1036500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>972300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1010700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>949100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>956000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>946300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1046400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>945900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>900500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>997900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>959500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2980500</v>
+      </c>
+      <c r="E89" s="3">
         <v>2385300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2222100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2984000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2118000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3646000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2585800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2072900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>957100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3344900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4444000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4357100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2108300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3488600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3177800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2126300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1834100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>982700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1586900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-275400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1353700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1913300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2087500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2268800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>766700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1063200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2646600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1967000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1858600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1070200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1876900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1213800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1283700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>964100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-906500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-903500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-998600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1187300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-821900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-738300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-821300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1184900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-929000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1135000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1388000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1554000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-957000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>2200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>1416700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1401400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5500</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-29300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-25400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>72300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-215800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-42200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-618400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-493200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-816600</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-912800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7237800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-943000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-741600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1028000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-716300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-886300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1178100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-852200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-929000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-822800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-993900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-924500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1195700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-534100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-520000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-468600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-482800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-492900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-543800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-674100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-665800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-752800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3540000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-792100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-793100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-919300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-856700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1030600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-799300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1458700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6656200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-863500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-411000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-658400</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,115 +9286,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>823700</v>
+      </c>
+      <c r="E96" s="3">
         <v>771500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>827600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>822000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>794600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>742100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>727400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>746900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>693300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-613900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1845200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-643700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-509200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-408700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-413300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-402800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-363800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-388400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-384900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-393900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-348400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-346200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-370600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-356100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-310200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-309000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-297200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-309400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-252900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-249300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-248600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-227700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-195100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-193600</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,115 +9724,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2094100</v>
+      </c>
+      <c r="E100" s="3">
         <v>4442500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1422700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2134200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1171200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2360200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1697300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-872200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-716900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2154600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3379300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3283300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1641300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2403900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2105900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1604800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1378500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-492900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1138500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>161700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>51800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1276300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1518800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1515500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>16900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-418600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1644500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1087800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-816800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-401100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-223300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>5465500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-418700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-554700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-410100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-143600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>108100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-81200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>569400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-612000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>261300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>241900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>79800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-457400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-111100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>537800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-44500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-657600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>731400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-28800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-184000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>244300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-148400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>82800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>22600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>11300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-130200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>195000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>23100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>CNQ</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6377500</v>
+      </c>
+      <c r="E8" s="3">
         <v>7610500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6580300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6582800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6613100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6088100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7233700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7314700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5958300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6378400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7132200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7620600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8479900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7890200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6820900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5711800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4719000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4779000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3882700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3452900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2253000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3531300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4600800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5106900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4410800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4040000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2817600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4286700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4480600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4120800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3872100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3323600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2910600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2797900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2656500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1793800</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3390400</v>
+      </c>
+      <c r="E9" s="3">
         <v>3834800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3272100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3178500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3385800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3279600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3335500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3206800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3429200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3324400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3614300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3141700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3672000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3321800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2912600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2428100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2354100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2378700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2281800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1951100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1701300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2445200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2388900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2332900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2005500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1977700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1895900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1901000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2080700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2094300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2102400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1830800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1529400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1339800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1267600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1104700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2987100</v>
+      </c>
+      <c r="E10" s="3">
         <v>3775700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3308200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3404300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3227300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2808500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3898100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4107900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2529100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3053900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3517900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4479000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4807900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4568400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3908400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3283700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2364900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2400400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1600900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1501800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>551700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1086100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2211900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2774000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2405200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2062300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>921700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2385700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2399900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2026500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1769700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1492900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1381300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1458100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1389000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>689100</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,67 +1417,70 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>18300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-59800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>25700</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-34000</v>
       </c>
       <c r="K14" s="3">
         <v>-34000</v>
       </c>
       <c r="L14" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-354100</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>-167900</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1474,8 +1494,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1510,118 +1530,124 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1294100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1301000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1321200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1182900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1204800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1132100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1560600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1136200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1055000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1048000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2303300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1059600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1007200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1039800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1090600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1068100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1003800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1027700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1249600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1122400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1101000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1227300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1208500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1182200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1036500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>972300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1010700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>949100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>956000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>946300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>1046400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>945900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>900500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>997900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>959500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4867800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5314600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4780200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4493100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4744800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4795700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5103600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4711100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4693400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4582400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6292300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4326600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4760600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4885500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4250400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3283700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3553200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3601600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3580900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3176200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2929400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3623100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3836000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3641200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3139600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3085400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2898200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2878400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3261100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3069900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3316900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2948600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2437300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2453000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2352300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2186400</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1509700</v>
+      </c>
+      <c r="E18" s="3">
         <v>2295900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1800100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2089600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1868300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1292400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2130000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2603600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1264900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1796000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>839900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3294000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3719300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3004700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2570500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2428100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1165800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1177400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>301800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>276800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-676400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-91800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>764900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1465800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1271200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>954600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-80700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1408300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1219500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1050900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>555200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>375100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>473300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>344900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>304200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-392600</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-665800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-38300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>599100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-103600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>86200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>210500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-224100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>175900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-171400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>284100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-440900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-252000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>128600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>104400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-215600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>406400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>182300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>478200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>176300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>355500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-877300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>104500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-143400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>114200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>131600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-422400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>281200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-21100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-249900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>90800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>343100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>494200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>14600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>57600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-59900</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3469600</v>
+      </c>
+      <c r="E21" s="3">
         <v>3635200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2522200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3376100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2986900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2214000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3914800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3563900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2491300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2853600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3427300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3912700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4474600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4173100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3765500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3280700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2576100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2387300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2029500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1575400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>780000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>258200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2077800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2504600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2421900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2058500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>507600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2638600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2154500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1747200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1692300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1664100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1868000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1357500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1321400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>179600</v>
+      </c>
+      <c r="E22" s="3">
         <v>183700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>131400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>117700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>120600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>118200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>128700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>135300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>132200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>120500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>145000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>109300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>118200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>120500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>150300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>131900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>128000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>133800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>192700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>133400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>156200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>161700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>228400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>191500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>156200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>147000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>181100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>130800</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>143000</v>
       </c>
       <c r="AF22" s="3">
         <v>143000</v>
       </c>
       <c r="AG22" s="3">
+        <v>143000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>198000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>136200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>107900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>102900</v>
-      </c>
-      <c r="AK22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2059600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2154700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1102300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2079300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1648300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1039800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2239800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2326400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1338200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1691000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>979000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2743800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3349100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3012900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2524600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2080700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1444300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1225900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>587300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>319700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-477100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1130800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>640900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1130800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1229200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>939200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-684200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1558800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1055400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>657900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>448000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>582000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>859600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>256600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>361800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-452500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>256600</v>
+      </c>
+      <c r="E24" s="3">
         <v>444600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>311400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>401900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>395300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>310900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>250600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>593600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>233300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>361400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-139900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>693100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>761200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>721300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>648600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>449600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>322600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>230000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-233900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-124800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>175400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>279400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1015900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>199400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-93600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>249300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>316200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>219100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>153300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>72900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>61800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>68400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-73000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1803000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1710100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>790900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1677300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1253100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>728900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1989200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1732800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1104800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1329600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1118900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2050700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2587900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2291600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1876100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1631100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1121700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>995900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>579500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>312800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-243300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1006000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>465500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>851400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2245000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>739800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-590600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1309500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>739200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>438900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>294700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>509000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>797800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>188200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>434800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1803000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1710100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>790900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1677300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1253100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>728900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1989200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1732800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1104800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1329600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1118900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2050700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2587900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2291600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1876100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1631100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1121700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>995900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>579500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>312800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-243300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1006000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>465500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>851400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2245000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>739800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-590600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1309500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>739200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>438900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>294700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>509000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>797800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>188200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>434800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>665800</v>
+      </c>
+      <c r="E32" s="3">
         <v>38300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-599100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>103600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-86200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-210500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>224100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-175900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>171400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-284100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>440900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>252000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-128600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-104400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>215600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-406400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-182300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-478200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-176300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-355500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>877300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-104500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>143400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-114200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-131600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>422400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-281200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>21100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>249900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-90800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-343100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-494200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-57600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>59900</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1803000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1710100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>790900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1677300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1253100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>728900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1989200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1732800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1104800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1329600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1118900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2050700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2587900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2291600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1876100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1631100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1121700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>995900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>579500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>312800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-243300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1006000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>465500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>851400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2245000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>739800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-590600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1309500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>739200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>438900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>294700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>509000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>797800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>188200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>434800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1803000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1710100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>790900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1677300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1253100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>728900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1989200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1732800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1104800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1329600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1118900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2050700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2587900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2291600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1876100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1631100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1121700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>995900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>579500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>312800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-243300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1006000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>465500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>851400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2245000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>739800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-590600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1309500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>739200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>438900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>294700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>509000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>797800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>188200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>434800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E41" s="3">
         <v>64700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>91000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>533700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>668500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>566400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>664100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>92100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>677200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>411700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>172200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>92400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>550800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>662200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>121500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>120100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>142400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>134200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>182800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>840500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>108400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>145900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>315600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>69300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>76900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>215100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>137000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>114400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>102000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>232200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>37200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>13100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3991,549 +4081,564 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>4900</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>443100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>406600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>417700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>395700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>357700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>361400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>293700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>271200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>289700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>228800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>226700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>339200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>305200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>236000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>208500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>215800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>174200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>382000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>470100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>433800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>422600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>398800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>478200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>560800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>587900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>664600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>660900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>619200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>626100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>701400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>464800</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2858100</v>
+      </c>
+      <c r="E43" s="3">
         <v>2685500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2867600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2294700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2668300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2516800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2414800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3122500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2106900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2514400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2616900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2850900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3706000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3478400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2303300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2352600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2302700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2012700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1933600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1477300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1692700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1195900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1932000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1993900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1684400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1760600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>873700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1436700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1965500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2023500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1239100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1637300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1637100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1755400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1441200</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1955500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1872900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1941100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1873500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1814200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1700700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1540200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1607100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1484700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1419100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1336000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1338000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1416600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1253300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1146100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>914800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>878000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>786900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>820200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>830300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>859300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>737700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>898200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>954200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>942900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>825200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>726800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>812400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>783700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>744500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>665300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>652700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>691400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>505500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>529300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>473200</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E45" s="3">
         <v>66800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>49600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>57700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>51000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>203200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>316300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>296300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>218700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>170300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>257000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>324700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>284900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>242200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>443100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>240900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>335100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>177800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>314200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>306900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>204000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>222200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>258700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>297400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>198700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>189000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>282100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>266400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>398700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>331900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>320400</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5312100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5032900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5146500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5015000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5428700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5501700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5427000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5553900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4498600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4586100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5194700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5210600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5862400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5332600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4399200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4413300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3966100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3509800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3374300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3093400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3191500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3283400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3498400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3878300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3683600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3281700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2298500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3201100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3744400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3301700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3644400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3066900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3251500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3182000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3331000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2714200</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4543,11 +4648,11 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>700</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4586,174 +4691,180 @@
         <v>0</v>
       </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
         <v>401400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>429400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>520500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>536000</v>
       </c>
-      <c r="X47" s="3" t="s">
+      <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>508300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>587800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>620100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>641300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>668200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>627900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>641400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>627800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>596900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>557400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>519500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>504700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>496300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>499300</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>56676600</v>
+      </c>
+      <c r="E48" s="3">
         <v>53456000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53747500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50129900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>49657000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50145500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>51677600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50464600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51834300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50573900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50447100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50898800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>51560800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>51853500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>51942200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50911800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49876100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>50009900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>54033300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>52633700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>54504900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>55426200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>56456700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>60141800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>57872200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>52626400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>51142200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>49193300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>50788500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>50896900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>50458900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>50437300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>49826300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>40562500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>40940500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>41054200</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>530800</v>
+      </c>
+      <c r="E52" s="3">
         <v>518300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>430900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>430800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>402600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>463000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>409700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>394800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>425200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>464200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>407100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>354200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>340700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>464100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>418300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>445900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>418700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>412200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>407800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>276800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>423000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>992700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>445200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>499100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>437000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>392600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>353900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>276100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>290600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>288300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>272400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>256800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>276100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>262000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>287300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>258900</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62519600</v>
+      </c>
+      <c r="E54" s="3">
         <v>59007200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>59324900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>55576400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>55488300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56110200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>57514200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56413200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56758000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>55624100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>56048900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>56463600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57763900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57650100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>56759700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>55771100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>54261000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>54333300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58244800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>56524400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58655400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>59702200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60908600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>65107000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>62612900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>56942000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>54462800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>53298400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>55464800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55114800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>54972600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>54318400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>53873400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>44511200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>45055200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>44526600</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>850500</v>
+      </c>
+      <c r="E57" s="3">
         <v>825800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>749900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>852700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1353200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>840400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1073700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>913000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>845800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>901700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>987100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>921900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>849800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>712400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>594500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>732600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>566300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>548900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>516100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>632500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>475600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>629400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>636200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>548800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>732800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>599700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>592900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>732500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>730200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>705400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>576800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>590900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>488200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>415600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>457100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>480900</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1179000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1171600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1845200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1389400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>800800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1546400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>967700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1345400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1922700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>913500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>477000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1138300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1094400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2162300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>877300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>878500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1797900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1416100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1185400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>779700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1604800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2373100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2045900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3548300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3330700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1445700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>868400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>363300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>621800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>484800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1396900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1395400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1448200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2403800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1392000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1611700</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>909900</v>
+      </c>
+      <c r="E59" s="3">
         <v>673500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>631800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>596600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>578700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>508800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>505100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>422100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>404000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>484800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4904000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4589700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4940900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4272100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4023100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3229600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2742500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2373600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2227600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1774000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1778200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1944600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2492600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2415000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2201400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2274000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2163000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2387900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2305000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2067900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2685900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2323400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2111300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1827600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2062700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1857600</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6241800</v>
+      </c>
+      <c r="E60" s="3">
         <v>6013100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6693600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5942500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6169600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6266100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5629900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6099400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6471100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5546200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6368100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6649900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6885200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7146800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5495000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4840700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5106700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4338600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3929100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3186200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3858600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4947000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5174700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6512200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6264900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4319500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3624300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3483800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3657100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3258100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4659500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4309700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4047800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3911800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3950200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12356800</v>
+      </c>
+      <c r="E61" s="3">
         <v>11931700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12251500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7135700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7745600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7740100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8386900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8360000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8407300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9107800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9081400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9413400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9376300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9264700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11174300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12736300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12630300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14248200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16721500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17244000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>17783800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16800500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15905300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16634100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16797700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15936000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14827600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13976400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15485600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16060000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>15316600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15662600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>15874000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10121400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11518100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>11672500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5906000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5501800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5624700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5297000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5284800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5406500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5625300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5010500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5031700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4954900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12498400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12606100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12430600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12794900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12737900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11878500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11784900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11713300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>12540200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11434400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11640000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11852700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12547200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13114700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12370300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11846000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11675900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11571800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11923400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11687800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11440000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11023200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>10891500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9479200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9446200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>9203400</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32239400</v>
+      </c>
+      <c r="E66" s="3">
         <v>30868600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31894400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26043900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26650300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26934100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27352900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27114400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27575100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27106200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27947900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28669400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28692000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29206400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29407100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29455500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29521800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30300000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33190800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>31864600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33282400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>33600200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>33627200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>36261000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>35432900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>32101500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>30127700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>29032000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>31066100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>31005900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>31416100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>30995600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>30813300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>24247600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>24876100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>24826100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21856300</v>
+      </c>
+      <c r="E72" s="3">
         <v>20103000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19531700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21205100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20580100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20879200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21919800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21269300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21094200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20607400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20369600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20220900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21388600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20739000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19825400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18986600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17639300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17044100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17615200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17264700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>17746100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18382500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19822300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21042900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19767600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17591900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17146600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17464500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17309700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>17152300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16828100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16783400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16523700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>16490100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>16536900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>16314900</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30280200</v>
+      </c>
+      <c r="E76" s="3">
         <v>28138600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27430400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>29532600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>28837900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29176100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30161400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29298800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29182900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28517900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28101000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27794200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>29071900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28443700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>27352600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26315500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>24739200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24033300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25054000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24659700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>25373000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>26102000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>27281400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>28846000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>27180000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>24840600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24335100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24266400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>24398700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24108900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23556500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23322800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>23060100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20263600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20179100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>19700500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1803000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1710100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>790900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1677300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1253100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>728900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1989200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1732800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1104800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1329600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1118900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2050700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2587900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2291600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1876100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1631100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1121700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>995900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>579500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>312800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-243300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1006000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>465500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>851400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2245000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>739800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-590600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1309500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>739200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>438900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>294700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>509000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>797800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>188200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>434800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1204800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1132100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1230500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1136200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1055000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1048000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1115000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1059000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1058200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1127000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2303300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1059600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1007200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1039800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1090600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1068100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1003800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1027700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1249600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1122400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1101000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1227300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1208500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1182200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1036500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>972300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1010700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>949100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>956000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>946300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1046400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>945900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>900500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>997900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>959500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2283200</v>
+      </c>
+      <c r="E89" s="3">
         <v>2980500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2385300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2222100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2984000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2118000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3646000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2585800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2072900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>957100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3344900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4444000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4357100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2108300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3488600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3177800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2126300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1834100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>982700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1586900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-275400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1353700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1913300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2087500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2268800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>766700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1063200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2646600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1967000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1858600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1070200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1876900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1213800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1283700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>964100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1404100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-906500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-903500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-998600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1187300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-821900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-738300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-821300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1184900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-929000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1135000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1388000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1554000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-957000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>2200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>1416700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1401400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-29300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-25400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>72300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-215800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-42200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-618400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-493200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-816600</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1423200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-912800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7237800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-943000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-741600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1028000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-716300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-886300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1178100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-852200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-929000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-822800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-993900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-924500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1195700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-534100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-520000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-468600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-482800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-492900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-543800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-674100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-665800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-752800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3540000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-792100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-793100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-919300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-856700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1030600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-799300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1458700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-6656200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-863500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-411000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-658400</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,118 +9520,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>904100</v>
+      </c>
+      <c r="E96" s="3">
         <v>823700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>771500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>827600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>822000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>794600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>742100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>727400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>746900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>693300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-613900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1845200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-643700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-509200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-408700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-413300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-402800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-363800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-388400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-384900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-393900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-348400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-346200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-370600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-356100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-310200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-309000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-297200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-309400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-252900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-249300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-248600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-227700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-195100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-193600</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,118 +9970,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-853500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2094100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4442500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1422700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2134200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1171200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2360200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1697300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-872200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-716900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2154600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3379300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3283300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1641300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2403900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2105900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1604800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1378500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-492900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1138500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>161700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>51800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1276300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1518800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1515500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>16900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-418600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1644500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1087800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-816800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-401100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-223300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>5465500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-418700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-554700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-410100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-143600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>108100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-81200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>569400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-612000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>261300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>241900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>79800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-457400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-111100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>537800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>7000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-44500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-657600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>731400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-28800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-184000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>244300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-148400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>82800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>22600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>11300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-130200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>195000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>CNQ</t>
   </si>
@@ -656,518 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7744300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7008100</v>
+      </c>
+      <c r="F8" s="3">
         <v>6831800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6377500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>7610500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>6580300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>6582800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6613100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>6088100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>7233700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>7314700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5958300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>6378400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>7132200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>7620600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8479900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>7890200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>6820900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5711800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4719000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4779000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3882700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3452900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2253000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3531300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4600800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5106900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>4410800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4040000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2817600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4286700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>4480600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>4120800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>3872100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>3323600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>2910600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>2797900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>2656500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>1793800</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3844200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3595600</v>
+      </c>
+      <c r="F9" s="3">
         <v>3525800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3390400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3834800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3272100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3178500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3385800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3279600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3335500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3206800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3429200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3324400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3614300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3141700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3672000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3321800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2912600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2428100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2354100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2378700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2281800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1951100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1701300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2445200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2388900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2332900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2005500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1977700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1895900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1901000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>2080700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>2094300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>2102400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>1830800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>1529400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>1339800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>1267600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>1104700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3900100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3412500</v>
+      </c>
+      <c r="F10" s="3">
         <v>3306100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2987100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>3775700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3308200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3404300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3227300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2808500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3898100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>4107900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2529100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3053900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>3517900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>4479000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4807900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4568400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3908400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>3283700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2364900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2400400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1600900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1501800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>551700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1086100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2211900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2774000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2405200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2062300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>921700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2385700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>2399900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>2026500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1769700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1492900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1381300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1458100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1389000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>689100</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1233,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1351,14 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1473,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1449,67 +1488,67 @@
         <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-58700</v>
+        <v>-3638600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-58700</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>18300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-59800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>25700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-34000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-34000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-354100</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-167900</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>-167900</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1520,11 +1559,11 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1556,124 +1595,136 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1344700</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1851000</v>
+      </c>
+      <c r="F15" s="3">
         <v>2305300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1294100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1301000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1321200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1182900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1204800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1132100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1560600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>1136200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>1055000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>1048000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>2303300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1059600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>1007200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1039800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>1090600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>1068100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>1003800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>1027700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>1249600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1122400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>1101000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>1227300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>1208500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>1182200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>1036500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>972300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>1010700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>949100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>956000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>946300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>1046400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>945900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>900500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>997900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>959500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1762,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6057900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5637700</v>
+      </c>
+      <c r="F17" s="3">
         <v>6169900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4867800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5314600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4780200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4493100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4744800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4795700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5103600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4711100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4693400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4582400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6292300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4326600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4760600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4885500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4250400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3283700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3553200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3601600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3580900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3176200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2929400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3623100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3836000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3641200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3139600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3085400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2898200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2878400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>3261100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>3069900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>3316900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>2948600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>2437300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>2453000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>2352300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>2186400</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1686400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1370400</v>
+      </c>
+      <c r="F18" s="3">
         <v>661900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1509700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2295900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1800100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2089600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1868300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1292400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2130000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2603600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1264900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1796000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>839900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3294000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>3719300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>3004700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>2570500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2428100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1165800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1177400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>301800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>276800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-676400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-91800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>764900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1465800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1271200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>954600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-80700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>1408300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1219500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>1050900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>555200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>375100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>473300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>344900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>304200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-392600</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,588 +2050,620 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>219200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-164100</v>
+      </c>
+      <c r="F20" s="3">
         <v>245500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-665800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-38300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>599100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-103600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>86200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>210500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-224100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>175900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-171400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-9600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>284100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-440900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-252000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>128600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>104400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-215600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>406400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>182300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>478200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>176300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>355500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-877300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>104500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-143400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>114200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>131600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-422400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>281200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-21100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-249900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>90800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>343100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>494200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>14600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>57600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>-59900</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2811900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3385600</v>
+      </c>
+      <c r="F21" s="3">
         <v>2721700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3469600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3635200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2522200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3376100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2986900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2214000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3914800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3563900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2491300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2853600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3427300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3912700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>4474600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>4173100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>3765500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3280700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2576100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2387300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>2029500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1575400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>780000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>258200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>2077800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2504600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>2421900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>2058500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>507600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>2638600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>2154500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>1747200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>1692300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>1664100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>1868000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1357500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>1321400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>227800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>191800</v>
+      </c>
+      <c r="F22" s="3">
         <v>191700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>179600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>183700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>131400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>117700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>120600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>118200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>128700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>135300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>132200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>120500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>145000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>109300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>118200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>120500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>150300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>131900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>128000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>133800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>192700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>133400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>156200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>161700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>228400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>191500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>156200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>147000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>181100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>130800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>143000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>143000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>198000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>136200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>107900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>102900</v>
       </c>
-      <c r="AM22" s="3" t="s">
+      <c r="AO22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AP22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1239400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4994500</v>
+      </c>
+      <c r="F23" s="3">
         <v>349600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2059600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2154700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1102300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2079300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1648300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1039800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2239800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2326400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1338200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1691000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>979000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2743800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3349100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>3012900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2524600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2080700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1444300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1225900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>587300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>319700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-477100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1130800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>640900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1130800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>1229200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>939200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-684200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>1558800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>1055400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>657900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>448000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>582000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>859600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>256600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>361800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>-452500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1126800</v>
+      </c>
+      <c r="F24" s="3">
         <v>-81100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>256600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>444600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>311400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>401900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>395300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>310900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>250600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>593600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>233300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>361400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-139900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>693100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>761200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>721300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>648600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>449600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>322600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>230000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>7700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>6900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-233900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-124800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>175400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>279400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-1015900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>199400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-93600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>249300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>316200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>219100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>153300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>72900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>61800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>68400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>-73000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2778,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>965700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3867600</v>
+      </c>
+      <c r="F26" s="3">
         <v>430800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1803000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1710100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>790900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1677300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1253100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>728900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1989200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1732800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1104800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1329600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1118900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2050700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2587900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2291600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1876100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1631100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1121700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>995900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>579500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>312800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-243300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>465500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>851400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>2245000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>739800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-590600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>1309500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>739200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>438900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>294700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>509000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>797800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>188200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>434800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>965700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3867600</v>
+      </c>
+      <c r="F27" s="3">
         <v>430800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1803000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1710100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>790900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1677300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1253100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>728900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1989200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1732800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1104800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1329600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1118900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2050700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2587900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2291600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1876100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1631100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1121700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>995900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>579500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>312800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-243300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>465500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>851400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2245000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>739800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-590600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>1309500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>739200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>438900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>294700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>509000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>797800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>188200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>434800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3510,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-219200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>164100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-245500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>665800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>38300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-599100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>103600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-86200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-210500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>224100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-175900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>171400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>9600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-284100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>440900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>252000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-128600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-104400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>215600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-406400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-182300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-478200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-176300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-355500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>877300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-104500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>143400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-114200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-131600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>422400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-281200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>21100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>249900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-90800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-343100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-494200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-57600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>59900</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>965700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3867600</v>
+      </c>
+      <c r="F33" s="3">
         <v>430800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1803000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1710100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>790900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1677300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1253100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>728900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1989200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1732800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1104800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1329600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1118900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2050700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2587900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2291600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1876100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1631100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1121700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>995900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>579500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>312800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-243300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>465500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>851400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2245000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>739800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-590600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>1309500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>739200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>438900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>294700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>509000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>797800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>188200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>434800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3876,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>965700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3867600</v>
+      </c>
+      <c r="F35" s="3">
         <v>430800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1803000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1710100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>790900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1677300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1253100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>728900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1989200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1732800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1104800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1329600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1118900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2050700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2587900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2291600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1876100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1631100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1121700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>995900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>579500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>312800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-243300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>465500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>851400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2245000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>739800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-590600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>1309500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>739200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>438900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>294700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>509000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>797800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>188200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>434800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4217,132 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>578900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>490800</v>
+      </c>
+      <c r="F41" s="3">
         <v>81100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>74800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>64700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>91000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>533700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>668500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>566400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>664100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>92400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>92100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>68000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>677200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>411700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>172200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>92400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>550800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>662200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>121500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>120100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>142400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>134200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>182800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>840500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>108400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>145900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>315600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>69300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>76900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>215100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>137000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>114400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>102000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>232200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>37200</v>
-      </c>
-      <c r="AL41" s="3">
-        <v>14600</v>
-      </c>
-      <c r="AM41" s="3">
-        <v>13100</v>
       </c>
       <c r="AN41" s="3">
         <v>14600</v>
       </c>
+      <c r="AO41" s="3">
+        <v>13100</v>
+      </c>
+      <c r="AP41" s="3">
+        <v>14600</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4177,573 +4356,603 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>4900</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>443100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>406600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>417700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>395700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>357700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>361400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>293700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>271200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>289700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>228800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>226700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>339200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>305200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>236000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>208500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>215800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>174200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>382000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>470100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>433800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>422600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>398800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>478200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>560800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>587900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>664600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>660900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>619200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>626100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>701400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>464800</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3759700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2916600</v>
+      </c>
+      <c r="F43" s="3">
         <v>2688700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2858100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2685500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2867600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2294700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2668300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2516800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2414800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3122500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2106900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2514400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2616900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2850900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3706000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3478400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2303300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2352600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2302700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2012700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1933600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1477300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1692700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1195900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1932000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1993900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1684400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>1760600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>873700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1436700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1965500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>2023500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>1239100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>1637300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>1637100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>1755400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>1441200</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2092600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1911600</v>
+      </c>
+      <c r="F44" s="3">
         <v>1988000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1955500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1872900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1941100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1873500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1814200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1700700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1540200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1607100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1484700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1419100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1336000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1338000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1416600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1253300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1146100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>914800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>878000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>786900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>820200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>830300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>859300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>737700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>898200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>954200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>942900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>825200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>726800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>812400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>783700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>744500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>665300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>652700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>691400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>505500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>529300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>473200</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>51100</v>
+      </c>
+      <c r="F45" s="3">
         <v>62500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>71900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>66800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>48000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>49600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>57700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>51000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>44700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>37700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>35500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>48000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>203200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>316300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>296300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>218700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>170300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>257000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>324700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>284900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>242200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>443100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>240900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>335100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>177800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>314200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>306900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>204000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>222200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>258700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>297400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>198700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>189000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>282100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>266400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>398700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>331900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>320400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6710600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5589600</v>
+      </c>
+      <c r="F46" s="3">
         <v>5155500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5312100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5032900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5146500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5015000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5428700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5501700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5427000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5553900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4498600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4586100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5194700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5210600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5862400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5332600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4399200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4413300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3966100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3509800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3374300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3093400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3191500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3283400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3498400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3878300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3683600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3281700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>2298500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3201100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>3744400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>3301700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>3644400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>3066900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>3251500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>3182000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>3331000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>2714200</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4759,14 +4968,14 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>700</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>700</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -4780,11 +4989,11 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4802,180 +5011,192 @@
         <v>0</v>
       </c>
       <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
         <v>401400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>429400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>520500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>536000</v>
       </c>
-      <c r="Z47" s="3" t="s">
+      <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>508300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>587800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>620100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>641300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>668200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>627900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>641400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>627800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>596900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>557400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>519500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>504700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>496300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>499300</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>60030400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>60751100</v>
+      </c>
+      <c r="F48" s="3">
         <v>55611000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>56676600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>53456000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>53747500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>50129900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>49657000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>50145500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>51677600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>50464600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>51834300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>50573900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>50447100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>50898800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>51560800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>51853500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>51942200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>50911800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>49876100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>50009900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>54033300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>52633700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>54504900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>55426200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>56456700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>60141800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>57872200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>52626400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>51142200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>49193300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>50788500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>50896900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>50458900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>50437300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>49826300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>40562500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>40940500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>41054200</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5090,8 +5311,14 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5555,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>634700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>633800</v>
+      </c>
+      <c r="F52" s="3">
         <v>680600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>530800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>518300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>430900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>430800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>402600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>463000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>409700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>394800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>425200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>464200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>407100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>354200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>340700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>464100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>418300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>445900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>418700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>412200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>407800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>276800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>423000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>992700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>445200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>499100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>437000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>392600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>353900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>276100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>290600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>288300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>272400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>256800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>276100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>262000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>287300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>258900</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>67375700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>66974400</v>
+      </c>
+      <c r="F54" s="3">
         <v>61447100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>62519600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>59007200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>59324900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>55576400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>55488300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>56110200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>57514200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>56413200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>56758000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>55624100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>56048900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>56463600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>57763900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>57650100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>56759700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>55771100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>54261000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>54333300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>58244800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>56524400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>58655400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>59702200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>60908600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>65107000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>62612900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>56942000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>54462800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>53298400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>55464800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>55114800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>54972600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>54318400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>53873400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>44511200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>45055200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>44526600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +6013,742 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1133400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>805900</v>
+      </c>
+      <c r="F57" s="3">
         <v>952000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>850500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>825800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>749900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>852700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1353200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>840400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1073700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>913000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>845800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>901700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>987100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>921900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>849800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>712400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>594500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>732600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>566300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>548900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>516100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>632500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>475600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>629400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>636200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>548800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>732800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>599700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>592900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>732500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>730200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>705400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>576800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>590900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>488200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>415600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>457100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>480900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>577400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>593700</v>
+      </c>
+      <c r="F58" s="3">
         <v>756000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1179000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1171600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1845200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1389400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>800800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1546400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>967700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1345400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1922700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>913500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>477000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1138300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1094400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2162300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>877300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>878500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1797900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1416100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1185400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>779700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1604800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2373100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2045900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3548300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3330700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1445700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>868400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>363300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>621800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>484800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>1396900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>1395400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>1448200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>2403800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>1392000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>1611700</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1089700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1150200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1048200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>909900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>673500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>631800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>596600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>578700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>508800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>505100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>422100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>404000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>484800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4904000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4589700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4940900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4272100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4023100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>3229600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2742500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2373600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2227600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1774000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1778200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1944600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>2492600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2415000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2201400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>2274000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2163000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>2387900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>2305000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>2067900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>2685900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>2323400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>2111300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>1827600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>2062700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>1857600</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6819500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5880600</v>
+      </c>
+      <c r="F60" s="3">
         <v>5968200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6241800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6013100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6693600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5942500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6169600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6266100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5629900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6099400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6471100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5546200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>6368100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6649900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6885200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>7146800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5495000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4840700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5106700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4338600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3929100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3186200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3858600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>4947000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>5174700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>6512200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>6264900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>4319500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>3624300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>3483800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>3657100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>3258100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>4659500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>4309700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>4047800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>3911800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>3950200</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13765000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>13790900</v>
+      </c>
+      <c r="F61" s="3">
         <v>12682300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>12356800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11931700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>12251500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7135700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7745600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7740100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8386900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8360000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8407300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9107800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9081400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9413400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>9376300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9264700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>11174300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>12736300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>12630300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>14248200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>16721500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>17244000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>17783800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>16800500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>15905300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>16634100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>16797700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>15936000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>14827600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>13976400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>15485600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>16060000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>15316600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>15662600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>15874000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>10121400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>11518100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>11672500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6868200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6712000</v>
+      </c>
+      <c r="F62" s="3">
         <v>6571200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>5906000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5501800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5624700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5297000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5284800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>5406500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5625300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5010500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5031700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4954900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>12498400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>12606100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>12430600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>12794900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>12737900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>11878500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>11784900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>11713300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>12540200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>11434400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>11640000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>11852700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>12547200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>13114700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>12370300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>11846000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>11675900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>11571800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>11923400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>11687800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>11440000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>11023200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>10891500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>9479200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>9446200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>9203400</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35396800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>34617000</v>
+      </c>
+      <c r="F66" s="3">
         <v>32398800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>32239400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>30868600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>31894400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>26043900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>26650300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>26934100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>27352900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>27114400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>27575100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>27106200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>27947900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>28669400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>28692000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>29206400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>29407100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>29455500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>29521800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>30300000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>33190800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>31864600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>33282400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>33600200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>33627200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>36261000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>35432900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>32101500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>30127700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>29032000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>31066100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>31005900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>31416100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>30995600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>30813300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>24247600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>24876100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>24826100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7761,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23275300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>23868100</v>
+      </c>
+      <c r="F72" s="3">
         <v>20754700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>21856300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>20103000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>19531700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>21205100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>20580100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>20879200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>21919800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>21269300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>21094200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>20607400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>20369600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>20220900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>21388600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>20739000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>19825400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>18986600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>17639300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>17044100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>17615200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>17264700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>17746100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>18382500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>19822300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>21042900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>19767600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>17591900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>17146600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>17464500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>17309700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>17152300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>16828100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>16783400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>16523700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>16490100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>16536900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>16314900</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31978900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>32357500</v>
+      </c>
+      <c r="F76" s="3">
         <v>29048200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>30280200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>28138600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>27430400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>29532600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>28837900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>29176100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>30161400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>29298800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>29182900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>28517900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>28101000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>27794200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>29071900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>28443700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>27352600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>26315500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>24739200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>24033300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>25054000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>24659700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>25373000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>26102000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>27281400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>28846000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>27180000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>24840600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>24335100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>24266400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>24398700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>24108900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>23556500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>23322800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>23060100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>20263600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>20179100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>19700500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8493,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>965700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3867600</v>
+      </c>
+      <c r="F81" s="3">
         <v>430800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1803000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1710100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>790900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1677300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1253100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>728900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1989200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1732800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1104800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1329600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1118900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2050700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2587900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2291600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1876100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1631100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1121700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>995900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>579500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>312800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-243300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1006000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>465500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>851400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2245000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>739800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-590600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>1309500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>739200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>438900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>294700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>509000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>797800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>188200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>434800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>-250400</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8790,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1301000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1210000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1182900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1204800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1132100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1230500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1136200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1055000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1048000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1115000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1059000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1058200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1127000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>2303300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1059600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1007200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1039800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1090600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1068100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1003800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1027700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1249600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1122400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1101000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1227300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1208500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1182200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>1036500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>972300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>1010700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>949100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>956000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>946300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>1046400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>945900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>900500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>997900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>959500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>934200</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2351200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2748100</v>
+      </c>
+      <c r="F89" s="3">
         <v>2828700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2283200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2980500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2385300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2222100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2984000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2118000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>3646000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2585800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2072900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>957100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>3344900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4444000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>4357100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2108300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>3488600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>3177800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2126300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1834100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>982700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1586900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-275400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1353700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1913300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>2087500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2268800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>766700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>1063200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>2646600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>1967000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>1858600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>1070200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>1876900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>1213800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>1283700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>964100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9688,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1560300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1056800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1524900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1404100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-906500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-903500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-998600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1187300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-821900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-738300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-821300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1184900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-929000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1135000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1388000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1554000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-957000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>1416700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1401400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-29300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-25400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>72300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-215800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-42200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-618400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-493200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-816600</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10050,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1396300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-875200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1603900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1423200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-912800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-7237800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-943000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-741600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1028000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-716300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-886300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1178100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-852200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-929000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-822800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-993900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-924500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1195700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-534100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-520000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-468600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-482800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-492900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-543800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-674100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-665800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-752800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-3540000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-792100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-793100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-919300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-856700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-1030600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-799300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-1458700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-6656200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-863500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-411000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-658400</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,124 +10220,132 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>876900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>894200</v>
+      </c>
+      <c r="F96" s="3">
         <v>881600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>904100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>823700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>771500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>827600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>822000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>794600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>742100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>727400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>746900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>693300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-613900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-1845200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-643700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-509200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-408700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-413300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-402800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-363800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-388400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-384900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-393900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-348400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-346200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-370600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-356100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-310200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-309000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-297200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-309400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-252900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-249300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-248600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-227700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-195100</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-193600</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,124 +10704,136 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-889800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1464500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1216900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-853500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2094100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4442500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1422700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2134200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1171200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2360200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1697300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-872200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-716900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2154600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-3379300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-3283300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1641300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2403900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2105900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1604800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1378500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-492900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1138500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>161700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>51800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1276300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1518800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>1515500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>16900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-418600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-1644500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-1087800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-816800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-401100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-223300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>5465500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-418700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-554700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,11 +10870,11 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10451,120 +10948,132 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>408400</v>
+      </c>
+      <c r="F102" s="3">
         <v>7900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>6600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-26400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-410100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-143600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>108100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-81200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>569400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>22700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-612000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>261300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>241900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>79800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-457400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-111100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>537800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-13000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>7000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-44500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-657600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>731400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-28800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-184000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>244300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-148400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>82800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>22600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>11300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-130200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>195000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>23100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>1500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-3800</v>
       </c>
     </row>
